--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-99.82999999999993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.09071e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-59.81</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6376404494381592</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5165341812400905</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.265190365190394</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.696681922196772</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.63707276303212</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.968x + -19007.552</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.305487546816426e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2417.965521357722</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000068e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8168320739197017</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-76.97999999999979</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.18587e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-61.546</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2971524288107054</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7575289575289127</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.881240768094066</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.580922431865992</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.92801880106893</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.061x + -15991.101</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.015821897910493e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2301.573766587481</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.817210022386449</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-62.08000000000015</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.21315e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-62.14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6701257861634687</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9975552968567982</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.393843594010008</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.334776264591477</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81.66510725083067</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 6.826x + -13168.147</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.862163991411075e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2261.126882389999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.817328364569441</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-61.15000000000009</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.22833e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.485</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5620027434841786</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.210056497175135</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.645073108709474</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.859163818038425</v>
+      </c>
+      <c r="K5" t="n">
+        <v>81.30848418582072</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 6.542x + -12429.988</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.451102402535445e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2232.736037910744</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8174367910607843</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-63.92000000000007</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.24531e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-62.851</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9558252427183097</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.418530351437592</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.099649941656921</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.049861687413649</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80.85566924505827</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.212x + -11647.801</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.297928399771804e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2205.440712058308</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000003472e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8176202860466265</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-52.77999999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.26186e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.182</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.335465116279018</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9635294117646016</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.513490725126441</v>
+      </c>
+      <c r="I7" t="n">
+        <v>755.3242105263836</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.862280872829913</v>
+      </c>
+      <c r="K7" t="n">
+        <v>79.02287130917607</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.156x + -9436.253</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>125.3025939566045</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2209.799804394665</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.231638106498333e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8117667617960486</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-43.41000000000008</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.27694e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-63.485</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.305555555555213</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.339294117647086</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.393704006541225</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.334842519685082</v>
+      </c>
+      <c r="K8" t="n">
+        <v>76.28232249545654</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 4.097x + -7251.209</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.774349664341948e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2152.559998539048</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8181090089039726</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-43.94000000000005</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.29332e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.805</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.503048780487412</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.152461538461491</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.639688715953254</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.952630670523457</v>
+      </c>
+      <c r="K9" t="n">
+        <v>76.11669083330794</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 4.046x + -7088.804</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.944182475079335e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2127.274118260848</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8183901725500929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-43.53999999999996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.30992e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-64.126</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001965601965592399</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5176600441500913</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.448847262248051</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1120.314197530886</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.461960130828181</v>
+      </c>
+      <c r="K10" t="n">
+        <v>73.98840073679317</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 3.485x + -5966.943</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.396965877691165e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2102.88909854987</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8186983673655126</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-39.28999999999996</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.32542e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-64.408</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5159292035399017</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.885692068429163</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.619616519174046</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16502.60454546017</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.439550785471499</v>
+      </c>
+      <c r="K11" t="n">
+        <v>69.93700535867382</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 2.738x + -4505.987</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.433486849496139e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2079.65642336472</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8189941214962757</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-30.91999999999985</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.33962e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-64.666</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6072796934865594</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.91385281385291</v>
+      </c>
+      <c r="H12" t="n">
+        <v>522.1587982832361</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.128762805358507</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.272716693170258</v>
+      </c>
+      <c r="K12" t="n">
+        <v>50.63635627834223</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 1.219x + -1616.933</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.784480943215926e-12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2057.527191636916</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8193086481249999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-31.24000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.35429e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-64.961</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3901176470588205</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5634146341463008</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.938660578386608</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.57931049535379</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50.34960190914557</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 1.207x + -1602.722</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.011136158609636e-11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2035.811585040424</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8196316094150542</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-27.74000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.36847e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-65.262</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.04594127806563606</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4100746268656913</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.233734939758915</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.146382381884076</v>
+      </c>
+      <c r="K14" t="n">
+        <v>28.04471875508875</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 0.533x + -390.128</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.305616843956753e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2014.774469124145</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8199528728551371</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-14.77999999999997</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.38341e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-65.515</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4403153153152414</v>
+      </c>
+      <c r="G15" t="n">
+        <v>865.2611764706293</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.635428571428569</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.302306425041181</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.689574515194247</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-68.79314964519257</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = -2.577x + 5268.739</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.163205638417968e-11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1994.147219145599</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8202790426016185</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-16.70000000000005</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.39545e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-65.777</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.09896480331262744</v>
+      </c>
+      <c r="G16" t="n">
+        <v>682.1659259258889</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.27651515151463</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.476094570928323</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.974838535065031</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-62.86804767742596</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = -1.951x + 4066.303</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.176327724613628e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1973.157681957575</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8206022729769485</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-5.819999999999936</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.40946e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-66.051</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.323415977961259</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.291428571428577</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.551027397260216</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.168787640018143</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-78.39695937242601</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = -4.870x + 9217.453</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.157181690796733e-12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1952.948415790365</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8209299096788133</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-6.590000000000146</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.42359e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-66.30500000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.07055335968377502</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.110351562499998</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.212186788154648</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.164308476413271</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-76.25317310947334</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = -4.088x + 7715.603</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.66133114213418e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1932.629378412675</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000102e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8212643456604716</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-2.079999999999927</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.43612e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-66.569</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1776.058173076901</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.02544031311154667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7716312056737723</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.869265536723112</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.312381655834283</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-78.77424625186011</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = -5.038x + 9281.968</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.445087443522884e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1912.442615431743</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000669e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8215986142005532</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4.970000000000027</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.45046e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-66.864</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1326086956521597</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8270479134467421</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.436050955413843</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.521247892074185</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.854858554066007</v>
+      </c>
+      <c r="K20" t="n">
+        <v>74.98267765672875</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 3.728x + -6081.930</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.633609001397241e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1891.887281090243</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8219455825502736</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.6400000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.46242e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-67.111</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3775238095237933</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8143750000000557</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.300742115027954</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.224183006535814</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.336423597400287</v>
+      </c>
+      <c r="K21" t="n">
+        <v>74.44158083602571</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 3.592x + -5784.175</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.706330029905297e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1871.62320880451</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000204e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8222885947173718</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>13.3599999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.47565e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-67.371</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.061904761904809</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.385057471264362</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.945255474452626</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.618134715025692</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.917683002882264</v>
+      </c>
+      <c r="K22" t="n">
+        <v>75.30292114361427</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 3.813x + -6100.369</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.837006812737307e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1851.003755098749</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8226451432599715</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-263.0700000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.74941e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-50.76</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>14.31272237605167</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.16452626865906</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.785x + -25281.559</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.868591856394237e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2873.051711335656</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000338e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8167954678996261</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-143.1900000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.06186e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-55.863</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>24.86816400349119</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.8553839247722</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.800x + -31411.764</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.386941090141653e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2576.664866082346</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000031913e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8176372014494299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-118.27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.12655e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-57.638</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0568383658969819</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.884408602150504</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.590213299874558</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.231161266836523</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.02398593840023</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.485x + -25036.399</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.67126040680553e-13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2500.221549416978</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8177944184019432</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-93.33999999999969</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.14783e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-58.64</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>10.82771692946659</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.92742135131648</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.266x + -24126.267</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.589610258755812e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2459.790101126679</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8178713931785201</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-76.90999999999985</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.16504e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-59.358</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>3.605843934693717</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.07790794279029</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.640x + -20255.639</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.359960949912924e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2426.847221845132</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8179900902547043</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-74.12999999999965</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.17977e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-59.958</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05108695652174629</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8838156484458758</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.80767085076704</v>
+      </c>
+      <c r="I7" t="n">
+        <v>431.6069796954685</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.327464258841156</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.02287756366351</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.171x + -16838.398</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.760370553760807e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2396.315984342618</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8181250873035871</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-60.10000000000036</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.195e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-60.465</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.63012528882994</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.797x + -13700.943</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.846590310715652e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2366.057565798163</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000005845e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.818312761072743</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-61.01999999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.2094e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-60.931</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3912152269399652</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8622699386503391</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.92730654761915</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.875473741202016</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.90383505785877</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.246x + -12385.145</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.821215079699915e-13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2336.223801284917</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.818528385163658</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-44.8599999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.22689e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-61.402</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>73.92006560510514</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 3.469x + -6457.358</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.885640927781418e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2308.217256683847</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000305e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8187564695416385</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-53.12000000000012</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.23942e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-61.771</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001533742331278218</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.57278195488721</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.229681429681473</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2144.093902438646</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.868411749411718</v>
+      </c>
+      <c r="K11" t="n">
+        <v>78.28458178914315</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 4.822x + -9193.046</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.555662023802641e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2280.936781745298</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8190014781508426</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-204.7799999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.10092e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-55.355</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2514180024660839</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6165171898355895</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.376092544987198</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.740621156211487</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60.34913681484709</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.0078829532745</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.448x + -25270.975</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.309946678020667e-13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2485.610650043614</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8167342242464068</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-133.04</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.21803e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-58.328</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1888551165147031</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.852417582417607</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.722464261402293</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.151264044943887</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.44063142246873</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.540x + -26112.598</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.073045540896301e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2372.172733323586</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8170490155736816</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-108.3900000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.24336e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-59.42</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2587179487179455</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.1512315270935</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.782717770034861</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.381811432813535</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.26229246737196</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.066x + -24600.018</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.824996657782406e-13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2331.549221204692</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.817120919156286</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-99.22999999999979</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.26052e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.111</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2081632653060857</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5652366863905042</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.784381778741892</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.263569682151629</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.63861690599957</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.656x + -21330.647</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.555386667669817e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2299.858461579325</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001449e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8172209515700588</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-81.45000000000005</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.27741e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-60.661</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1256465517241314</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.627245949926214</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.083797054009655</v>
+      </c>
+      <c r="I6" t="n">
+        <v>171.6967708867249</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.468534932221158</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.47579681114158</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.340x + -20424.201</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.109190749550578e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2270.18104004765</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001782e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8173996952703181</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-71.59000000000015</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.29345e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.114</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>1.489958471674933</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.12649034663309</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.721x + -18922.248</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.549341362568593e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2241.100628829656</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8176183870949866</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-69.77000000000021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.30995e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-61.559</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4861850443599199</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7768056968464074</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.944799405646406</v>
+      </c>
+      <c r="I8" t="n">
+        <v>468.7793342579591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.923371964679976</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.35567793304396</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 8.585x + -16423.551</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.402424305082267e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2212.917017104517</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000056e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8178760123260773</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-68.56999999999994</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.32603e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-61.957</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4308762169680136</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.298639455782133</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.408739255014039</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.560752386299837</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>82.87607870025458</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 8.001x + -15080.722</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.053972134084737e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2186.593551621414</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8181415408158662</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-56.64999999999986</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.34092e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.344</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5121330724071017</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.291359593392545</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.046991622239052</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.066016949152591</v>
+      </c>
+      <c r="K10" t="n">
+        <v>81.62960740627466</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 6.796x + -12558.127</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.260525917041039e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2162.173723793554</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000203e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8184015568674078</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-55.8900000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.35646e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-62.692</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6437499999998734</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6625931445603584</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.420709570957189</v>
+      </c>
+      <c r="I11" t="n">
+        <v>447.2802069857748</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.083921834091353</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.64484665020996</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 6.070x + -11034.925</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.567745128575015e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2138.299674143591</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8186827246611407</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-56.93000000000006</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.36976e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-63.003</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1546551724137936</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2388203017832695</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.386949924127521</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.98369065849927</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>80.25023565861777</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 5.820x + -10454.226</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.389039415977951e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2115.391337621069</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000225e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8189838946749735</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-37.25999999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.3863e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-63.37</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3950391644908563</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.396853625170928</v>
+      </c>
+      <c r="H13" t="n">
+        <v>559.0311501597982</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.70965476887078</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.99060317460327</v>
+      </c>
+      <c r="K13" t="n">
+        <v>69.02407399548717</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 2.608x + -4258.023</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.155813984957102e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2092.927651858601</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.81930686553524</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-44.46000000000004</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.40057e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-63.625</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1488778054862764</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3365432098765073</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.035224839400389</v>
+      </c>
+      <c r="I14" t="n">
+        <v>632.1379061371605</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.617272773975338</v>
+      </c>
+      <c r="K14" t="n">
+        <v>75.9714115717095</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 4.002x + -6855.007</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.822896123862566e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2071.226138550229</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8196027443072182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-30.53999999999996</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.41422e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-63.926</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.120076481835704</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.372352941176593</v>
+      </c>
+      <c r="H15" t="n">
+        <v>21928.76875007322</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.114602960968979</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.277387594355332</v>
+      </c>
+      <c r="K15" t="n">
+        <v>43.8615558925129</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 0.961x + -1115.675</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.04175754828238e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2050.369855721834</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8199163450473048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-35.28999999999996</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.42764e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-64.227</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1874003189792677</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4128161888701668</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9775429326287423</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.797422298877806</v>
+      </c>
+      <c r="K16" t="n">
+        <v>63.04135340473545</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 1.966x + -3000.044</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.892824235530616e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2029.181306073275</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8202251617307426</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-29.54000000000019</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.4415e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-64.51600000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2428160919540046</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8942184154175432</v>
+      </c>
+      <c r="H17" t="n">
+        <v>407.2284730195304</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.712903225806429</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.912226717717449</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45.43448501065251</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 1.015x + -1248.499</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.240231171114659e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2008.1894650394</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8205317402125414</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-13.74000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.45598e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-64.80200000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.221767241379039</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1013.37600000013</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.571525096525088</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.122997946612007</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.203778429934081</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-72.92742366345705</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = -3.256x + 6505.741</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>465.5936907559623</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1743.016283833224</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.988629627763726e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8104549672848965</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-21.32000000000016</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.46799e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-65.047</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1480769230769218</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.929367088607466</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3171.006249999553</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.000237247923998</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.125782004698159</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-30.26983426558344</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = -0.584x + 1616.698</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.787366203060401e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1967.176560805307</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.821172340440002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-11.02999999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.48343e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-65.33</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6420886075950309</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7121.86799999687</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.64834437086085</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.581578947368499</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.444519231348877</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-74.38969936980901</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = -3.579x + 6905.370</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.102194484601837e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1947.229307023899</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8214865399228338</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-9.689999999999827</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.49556e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-65.568</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1822134387351736</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.154888888888864</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.437760416666724</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.566605033009353</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-76.43617560078853</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = -4.145x + 7829.007</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.799349272414639e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1927.511229689941</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8218035756252783</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-6.049999999999955</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.50962e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-65.88200000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3931818181817581</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.002539682539694</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.312389380530971</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.442711439445589</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-76.73571255951464</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = -4.242x + 7876.848</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.579989602858862e-12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1907.721475918999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8221280741698642</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-292.1700000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.88254e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-50.613</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>12.43674644283627</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.68508640050176</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.036x + -21927.340</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.531754418550794e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2682.331075286985</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8183122528011395</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-166.9500000000003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.20864e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-56.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>20.03131900592901</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.49846534058848</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.702x + -27183.681</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.567543483768303e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2418.552936682619</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.819074510111525</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-132.9700000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.26903e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-57.982</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1135964912280912</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6118768328445769</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.302312138728322</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.163583252190833</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.51621400089732</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.00571262187555</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.443x + -23542.616</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.414655296836617e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2351.00434950218</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001422e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8192163352940676</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-102.9400000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.29217e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-59.097</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2300300300300309</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8684115523465604</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.861916461916429</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.298701298701271</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.95371298669677</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.325x + -22889.888</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.074252383869141e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2311.64343558264</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000516e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8193185792260768</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-86.97000000000025</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.30891e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-59.927</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1373152709359659</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.059462616822412</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.067324388318875</v>
+      </c>
+      <c r="I6" t="n">
+        <v>147.1462370437064</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.033891108891233</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.39779243039936</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.195x + -20227.348</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.219845479983952e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2277.875356554868</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001422e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8194427593292148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-80.40000000000009</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.32649e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-60.588</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1846153846153714</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6113573407201842</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.08202396804274</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.372947368420997</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.36981504542359</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.603x + -16713.459</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.954266480573372e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2245.355227051818</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8196257578649878</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-69.32000000000016</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.34175e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-61.166</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2578014184396784</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.036601307189489</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.851376146789074</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.626985040276252</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>82.67269415750867</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 7.777x + -14842.733</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.495896350373366e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2214.379935668665</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000007262e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8198366291058186</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-64.16000000000008</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.35994e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-61.656</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2242158092848061</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.272301425661841</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.173502722323061</v>
+      </c>
+      <c r="I9" t="n">
+        <v>259.9384319753958</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.474772542807293</v>
+      </c>
+      <c r="K9" t="n">
+        <v>81.59169219635113</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.765x + -12651.224</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.516199958612458e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2184.161441616359</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000002123e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.820084251692327</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-54.83999999999992</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.37649e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.149</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.596706586826347</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8336492890996244</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.291514143094856</v>
+      </c>
+      <c r="I10" t="n">
+        <v>653.398653846112</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.721246669950677</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.62069416838311</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.460x + -9955.161</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.243334346150276e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2155.090664404788</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8203513308286863</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-44.71000000000004</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.3946e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-62.553</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3200221238937945</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.61591263650556</v>
+      </c>
+      <c r="H11" t="n">
+        <v>276.2913917940495</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.842035928143885</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.255435101084105</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75.1224995448122</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 3.764x + -6556.328</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.59161761483623e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2127.584134469996</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000035e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8206519868547215</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-194.3999999999996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.14633e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-55.334</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>18.11669994310894</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.25101179123476</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.037x + -26266.441</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.81803029116612e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2450.505382732978</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8180927730493248</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-129.9099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.251e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-58.469</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.006786703601104252</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3150268336314803</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8527007299270027</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.204079601990086</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.20089894166334</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.98704961183948</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.400x + -23409.503</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.085923516628149e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2347.688636653309</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8183457305185744</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-97.59999999999991</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.27513e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-59.584</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1459541984732713</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.926535087719225</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.797562626946508</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.576778733385329</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.82604301641445</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.044x + -22255.775</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.265186523582785e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2309.481426074799</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8184161549734839</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-82.95000000000005</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.29049e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.277</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4692889561270771</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9116977225673216</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.815850144092205</v>
+      </c>
+      <c r="I5" t="n">
+        <v>173.9439537329087</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.021182506718702</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.20005825457285</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.845x + -19500.892</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.073219316667966e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2279.789276511653</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8185314720472997</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-70.30000000000018</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.30636e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-60.752</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9440814176407966</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.72363765750833</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.092x + -17734.641</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.298161265587734e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2251.031850161536</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003917e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8187058255063128</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-74.16000000000008</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.32519e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.21</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2500770416024655</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4604651162790542</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.71813361611883</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.559489456159805</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>82.91530875048139</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.046x + -15418.210</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.042972965399277e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2222.276373719201</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8189326649600858</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-62.17999999999984</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.34312e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-61.653</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3191794871794817</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.640834575260764</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.172555746140719</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.879716981132042</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.82888160635306</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 6.964x + -13086.260</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.933617990239786e-13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2194.046159524713</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8191920538596626</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-60.82000000000016</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.3612e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.013</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.567500000000028</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.075768535262141</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.51779964221831</v>
+      </c>
+      <c r="I9" t="n">
+        <v>292.7091143594105</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.667149493518808</v>
+      </c>
+      <c r="K9" t="n">
+        <v>81.29782815404234</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.533x + -12093.728</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.263239373616513e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2166.462163373291</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000004362e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8194635650255985</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-54.39999999999986</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.37954e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.373</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6559210526315982</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8984952120382679</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.350042408821053</v>
+      </c>
+      <c r="I10" t="n">
+        <v>564.6109271523191</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.713717801351708</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.23500153666801</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.811x + -10551.161</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.740060517801523e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2139.724830477282</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8197604937916433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-50.50999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.39762e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-62.731</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2037453183520762</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.238876404494462</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.346649029982357</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11390.30999998893</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.821237857540497</v>
+      </c>
+      <c r="K11" t="n">
+        <v>78.01720259259039</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 4.712x + -8339.407</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.888759237023528e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2114.494610485073</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8200546022365006</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-44.42999999999984</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.41496e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-63.049</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3843800322061</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.530796460177017</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.891521739130549</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.005970416552191</v>
+      </c>
+      <c r="K12" t="n">
+        <v>75.25192574559955</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 3.799x + -6528.485</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.693809161777374e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2090.244748072032</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000001333e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8203531302882033</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-38.93999999999983</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.43213e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-63.364</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2459412780656477</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7463380281690878</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.704994903159933</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.121494783008797</v>
+      </c>
+      <c r="K13" t="n">
+        <v>71.39174275552924</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 2.970x + -4907.951</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.391034973962976e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2066.446967194479</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000208e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8206453582175531</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-37.82000000000016</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.44883e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-63.687</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2079326923076946</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.882362204724447</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.318309270614921</v>
+      </c>
+      <c r="K14" t="n">
+        <v>68.20342119189704</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 2.501x + -4011.885</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.300316489939316e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2044.275253061377</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8209498127938462</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-33.23000000000002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.46501e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-63.988</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1392197125256601</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.52917431192662</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.422280471821686</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.515123601871113</v>
+      </c>
+      <c r="K15" t="n">
+        <v>54.84148549150882</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 1.420x + -2001.452</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.191286456926767e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2022.474701616153</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8212629292047802</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-23.8900000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.48013e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-64.258</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3359173126615216</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6720588235294519</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.220303756994377</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.379581017918847</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-23.63536197186177</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = -0.438x + 1401.696</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.182612958551111e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2000.97871736425</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8215734390118673</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-22.00999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.49666e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-64.566</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.02359999999999986</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7093489148580715</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2605.043283580649</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.583666061705995</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.773100922539091</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-36.01505624880785</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = -0.727x + 1872.911</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>4.711685474233437e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1979.544298344718</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8218871171799974</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-14.58999999999992</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.51121e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-64.82299999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1123209169054632</v>
+      </c>
+      <c r="G18" t="n">
+        <v>883.7073232323244</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.425930232558231</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.482765335929903</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.73105770764128</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-68.81653130893991</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = -2.580x + 5169.995</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.799914322032931e-11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1958.74119708094</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8222087567964652</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-10.91000000000008</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.5255e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-65.11499999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7019999999999325</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.293315858453439</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.100254452926099</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.136919366292168</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-74.81551650009332</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = -3.685x + 7053.335</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.688386246057792e-12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1937.588282522877</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8225421938164377</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-5.690000000000055</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.54098e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-65.384</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6063231850118003</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.248702101359796</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.549525616698344</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.286854447512148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-78.03794608922435</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = -4.720x + 8779.037</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.76441651384682e-12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1916.581456870169</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8228727225789749</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-5.620000000000118</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.55608e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-65.66800000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3681362725451663</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9428822495605768</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.236293436293487</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.196409828974637</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-76.73231190597836</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = -4.241x + 7825.692</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>461.2513999276247</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1696.838879881661</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.754721301734316e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8259443670313199</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.029999999999973</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.57192e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-65.953</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3356725146198866</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7418524871354636</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.667121212121131</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.803703703703512</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.333713407990969</v>
+      </c>
+      <c r="K22" t="n">
+        <v>74.49474938169908</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 3.605x + -5830.555</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.467865674446815e-11</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1875.43471340691</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.823550779313926</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-289.4000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.94187e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-51.14</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>13.69580238676602</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.96946972824345</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.466x + -22388.803</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.040828909659335e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2591.399615200155</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000005124e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8225864766707481</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-143.6699999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.27898e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-57.557</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>20.15736461012811</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.53954779932567</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.819x + -26396.609</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.883353722665607e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2321.20835883814</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8234048628961428</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-94.08999999999992</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.33221e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-59.642</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>12.35927601205413</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.04865534310625</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.543x + -22842.830</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.410196628143468e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2253.115139858811</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8235695509221728</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-69.83999999999992</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.35217e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.738</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>0.810913572756554</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.52834704789227</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.816x + -16938.416</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.355990394307768e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2213.466860077176</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000068331e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8236929932369786</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-63.00999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.36806e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.461</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.111538461538285</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.099029126213587</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.138233054074499</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2221.532214764973</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.131373530147696</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.98602521586047</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 7.103x + -13298.135</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.743619582382439e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2179.268045470058</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8238621482507884</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-55.33999999999992</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.38812e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-62.068</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5806366047744882</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8970430107527364</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.47830637488106</v>
+      </c>
+      <c r="I7" t="n">
+        <v>403.0279236276496</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.309353274992665</v>
+      </c>
+      <c r="K7" t="n">
+        <v>79.93270674439823</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.633x + -10260.825</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.470805315339147e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2146.054531081825</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000087e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8240555537218642</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-50.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.40612e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.597</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4242494226327956</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5970027247956328</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.787431693988916</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5223.416923074484</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.598506859201136</v>
+      </c>
+      <c r="K8" t="n">
+        <v>76.96888144100916</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 4.321x + -7605.695</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.780358642101849e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2114.055675517818</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8243048022491064</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-43.14999999999986</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.42607e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.053</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3615646258503517</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8495522388060159</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.284954280964136</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.689521479569689</v>
+      </c>
+      <c r="K9" t="n">
+        <v>72.80696309005485</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 3.232x + -5445.027</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.73992650562642e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2082.746494416246</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000002658e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8245733819663018</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-35.37999999999988</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.44569e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.487</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2295197740112858</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6112984822934435</v>
+      </c>
+      <c r="H10" t="n">
+        <v>399.3817551962897</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.335656108597199</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.838067248680737</v>
+      </c>
+      <c r="K10" t="n">
+        <v>60.86448546867136</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 1.794x + -2702.963</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.498870308889907e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2053.725834070181</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8248636158348125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-23.38999999999987</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.46292e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.859</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.383333333334092</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.154151624548844</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.703608847497197</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.530267965895247</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-18.15268803265198</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = -0.328x + 1256.842</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.863599503820712e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2026.031721643197</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000005478e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8251534583632906</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-173.5799999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.14726e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-56.353</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>19.38498010593134</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.38198389171703</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.380x + -26828.378</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.945528969817851e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2424.07613736572</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8199851919565687</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-106.6700000000003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.25872e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-59.507</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.308009422850403</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8328431372548774</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.122504091653089</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.338336347197144</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.91485694832897</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.238x + -22740.029</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.667653178952902e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2308.935672098836</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000033749e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8202379931327785</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-85.11999999999989</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.28245e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-60.381</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9141361256544275</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8769628099173143</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.833357717629965</v>
+      </c>
+      <c r="I4" t="n">
+        <v>142.7481943250273</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.937863145258136</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.33357356445418</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.078x + -19956.310</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.462409081477049e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2271.735300960781</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8202760045559823</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-81.08000000000015</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.29792e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.832</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2020768431983517</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.036260330578504</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.91253918495291</v>
+      </c>
+      <c r="I5" t="n">
+        <v>224.9227088948739</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.08892164087448</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.91562640302743</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.381x + -18308.841</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.617557587630218e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2245.239778973065</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8203445327519937</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-79.54000000000019</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.31247e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.244</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03830548926013796</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.093220338982955</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.15626984126985</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.722546103509673</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.42670931435386</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.678x + -16694.666</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.437707714253742e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2219.411129374885</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8204929258916049</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-67.3900000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.33109e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.596</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.306286549707623</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.562730627306267</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.971620612397284</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1234.577573529507</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.778893109061333</v>
+      </c>
+      <c r="K7" t="n">
+        <v>82.57540916369737</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 7.674x + -14521.805</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.787847203415164e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2194.750305082619</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8206972511395739</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.34663e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-61.908</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2817002881844403</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.155047821466561</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.237425404944574</v>
+      </c>
+      <c r="I8" t="n">
+        <v>112119.4333325042</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.626852099491773</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.99637270391783</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 7.112x + -13269.737</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.502112230666082e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2171.177977453772</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8209178833731177</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-56.36000000000013</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.36424e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.217</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3871093749999261</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9506643046944263</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.766031987814212</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.738913043478221</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80.72897074396093</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.126x + -11214.572</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.176966877862571e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2148.020677728776</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000972e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8211662549472581</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-51.93000000000006</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.38049e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.497</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4017374517374492</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.26008583690985</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.224400684931585</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.99437095412321</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79.52783502169258</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 5.410x + -9725.398</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.287214376077713e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2126.353981522449</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.00000000000074e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8214255365798371</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-52.80000000000018</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.39585e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-62.784</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1506641366223918</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6927304964538441</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.541446208112873</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1709.757999999496</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.868388573956533</v>
+      </c>
+      <c r="K11" t="n">
+        <v>78.76880552389031</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.036x + -8935.459</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.291454818469938e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2105.199455352495</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8217033429359762</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-39.61999999999989</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.41123e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-63.066</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4281138790035462</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.312233285917384</v>
+      </c>
+      <c r="H12" t="n">
+        <v>330.6118887823631</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.687955993051528</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.493623451193612</v>
+      </c>
+      <c r="K12" t="n">
+        <v>73.43323657420989</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 3.362x + -5674.162</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.966514247220899e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2084.414270177135</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8219854570824879</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-40.91000000000008</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.42596e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-63.348</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1232914923291428</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.36311569301263</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.32188019966725</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.030746267733815</v>
+      </c>
+      <c r="K13" t="n">
+        <v>72.71956515545914</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 3.214x + -5368.021</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.083413885404588e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2064.244919235202</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000098e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8222747325284969</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-47.32999999999993</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.44129e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-63.608</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3254041570438689</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3886494252873395</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8826548672566261</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.520977011494161</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>74.58429760798448</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 3.627x + -6107.819</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.927002076461528e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2044.298649405384</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8225724399148835</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-37.62000000000012</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.4564e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-63.88</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0791935483870929</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2133555926544215</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.383493810178837</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.333103540397866</v>
+      </c>
+      <c r="K15" t="n">
+        <v>65.83595470154087</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 2.229x + -3482.672</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.076747928480313e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2024.673744779838</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000794e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8228728451387118</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-28.78999999999996</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.47052e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-64.137</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1811463046757076</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8685601056803796</v>
+      </c>
+      <c r="H16" t="n">
+        <v>909.962827225143</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.242078364565547</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.378344915662903</v>
+      </c>
+      <c r="K16" t="n">
+        <v>27.52461027105345</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 0.521x + -328.387</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.279216371395521e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2005.24249818509</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8231814522867867</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-24.8900000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.48488e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-64.378</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1554809843400395</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.020277777777849</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8482.382926825059</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.414725069897545</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.430423228090625</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-17.26249288163301</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = -0.311x + 1172.470</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.944392334971067e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1985.935182710915</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8234970103522875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-30.57999999999993</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.49741e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-64.628</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6134433962264116</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1633245382585726</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.052777777777718</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.007588279310649</v>
+      </c>
+      <c r="K18" t="n">
+        <v>45.25799158971661</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 1.009x + -1235.475</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.268326875040545e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1966.762201431688</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8238135155774827</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-17.43999999999983</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.51216e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-64.874</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0715821812595967</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.831372549019604</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.336851520572438</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.518871021079078</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-64.57295199316155</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = -2.103x + 4320.004</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.512479130005232e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1947.623851993005</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8241244208803208</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-19.13999999999987</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.52769e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-65.133</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.115000000000002</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3848120300751967</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.489920424403127</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.90649180316512</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-59.11177625396401</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = -1.672x + 3490.251</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.177546872564243e-12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1928.492748216604</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8244536716799277</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-8.779999999999973</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.541e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-65.38500000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4890322580645503</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.490776699029215</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.044499178981979</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.954561668839922</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-75.71666965056761</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = -3.928x + 7403.073</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.291644411025263e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1909.218863983835</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8247730757494215</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.55412e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-65.63500000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3913953488371869</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3852.91098901098</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.114653784219079</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.333633093525165</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.83198675839066</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-73.08906196034226</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = -3.289x + 6199.558</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.590795143356186e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1890.459693166599</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8251086426222195</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-275.71</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.32062e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-56.251</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1442961165048552</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8743421052631835</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.258320000000041</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.044751908397064</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.95192980577479</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.02635672175349</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.557x + -18661.780</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.131801177028946e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2112.413326485524</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.818023149798667</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-128.76</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.56222e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-62.968</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02130365659776961</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1078549848942542</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9628620102213769</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.452154398563648</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.19664631545549</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.37214446279282</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.354x + -20851.079</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.400859152752665e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1895.102039855793</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8186695257787544</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-85.8599999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.5748e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-64.93000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1555066079295477</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1941068139962854</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8233979135617905</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.791917591125088</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9.064672098686874</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.37694364448107</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.157x + -16414.504</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.260402274030566e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1839.135513088014</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001192e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8188227417856027</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-67.93000000000006</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.57369e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-65.857</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02426850258175494</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.405607476635465</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9432282003710352</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.630025445292553</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.13626690366171</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.308x + -13082.172</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.602179346621871e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1806.943526198307</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000005129e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8189578561440372</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-48.96000000000004</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.57601e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-66.48099999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7377094972066865</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.084462151394417</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.873888091822141</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.207916986933048</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.33681676392436</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 6.563x + -10050.725</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.346683637406767</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1907.220431516589</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.51883301213593e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7890356792397567</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-50.62999999999988</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.58108e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-66.998</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03327932475838208</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5479498530074235</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.668420172831819</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12.90349678608272</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7.41854747130174</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80.50229486478456</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.977x + -8986.067</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.732442839492702e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1751.145691773412</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8192865498640411</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-42.43000000000006</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.59288e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-67.44</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2589958158995792</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2702702702702569</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9154981549814504</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.917049180327905</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>78.18563593405783</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 4.781x + -6965.624</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.958784315320988e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1723.454014588223</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8195503098821437</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-35.94000000000005</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.60394e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-67.877</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3961240310077724</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.393096234309656</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.317835671342571</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.687535816618758</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>74.6982300161572</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 3.655x + -5118.323</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.300005257000134e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1696.018140351011</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8198595087628128</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-34.09000000000015</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.61266e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-68.25700000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3763157894736899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8636363636364613</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8702460850112506</v>
+      </c>
+      <c r="I10" t="n">
+        <v>543.2853695324141</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.653156911152102</v>
+      </c>
+      <c r="K10" t="n">
+        <v>71.57503328686998</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 3.002x + -4046.337</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.736013423185014e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1670.48590028759</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8201887806134781</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-28.01999999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.62456e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-68.602</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.102197802197874</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4770562770562493</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.239691714836004</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1316.630291970661</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.73206022516489</v>
+      </c>
+      <c r="K11" t="n">
+        <v>62.55343621990598</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 1.925x + -2373.948</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.893808886928976e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1646.944710328125</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000007e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8205033760807476</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-104.5999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.17859e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-58.554</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07266602502405951</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8454022988505475</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.555994256999213</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.290491923641691</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.781353702259</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 10.949x + -23178.240</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-23178.24023521944</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.276838273332596e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>140.1799999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000742e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8223847912655973</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-81.90000000000009</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.21029e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-59.437</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>7.154960209335949</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.57848864456533</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.537x + -21796.422</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-21796.42237363628</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.729833070191376e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>126.8299999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000122e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8226058930129354</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-77.73000000000025</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.23599e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-60.13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03899159663866206</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5478220574605841</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.897486252945944</v>
+      </c>
+      <c r="I4" t="n">
+        <v>231.6316516931672</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.297663788725042</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.83042443673912</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 9.251x + -18694.047</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-18694.04726858732</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.901129054328679e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>129.8900000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8228147166386627</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-71.15999999999985</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.25831e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.728</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08493353028065175</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.68775862068974</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.041478599221797</v>
+      </c>
+      <c r="I5" t="n">
+        <v>675.7308617234859</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.480870917573931</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.07162700835414</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 8.229x + -16278.731</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16278.73085870794</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.284194519695916e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>128.7199999999998</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8230321595261403</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-70.27999999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.28003e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.248</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05288640595902749</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4151675485008757</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.240799256505666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.635645933014421</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>82.36197485878387</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 7.457x + -14454.604</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14454.60429870954</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.629721820495902e-13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8231931885969932</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-58.00999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.29857e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.701</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1745253164556875</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.270411392404985</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.130775254502606</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.889757709251244</v>
+      </c>
+      <c r="K7" t="n">
+        <v>81.43053702847548</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 6.636x + -12602.995</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12602.99540603366</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.214984352901275e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>123.3899999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.823443621170365</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-46.70999999999981</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.31574e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.13</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>79.281078070878</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 5.283x + -9728.877</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9728.877440864233</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.150855921476016e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>114.1599999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001085e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8237228001495134</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-51.35000000000014</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.33588e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.571</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.277572559366735</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2684343434343661</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.613992537313464</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1575.687727272639</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.072037184651951</v>
+      </c>
+      <c r="K9" t="n">
+        <v>78.59841228995109</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 4.959x + -9004.028</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9004.028070926124</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.572198403157648e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>124.97</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8239724135541396</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-48.05999999999995</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.34989e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.929</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4283082077051611</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.758064516128983</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.36522593320236</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.146366262172829</v>
+      </c>
+      <c r="K10" t="n">
+        <v>77.15390158802263</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 4.385x + -7790.142</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7790.141647886042</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.50505628096771e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000012837e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8242502393606477</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-37.72000000000003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.36729e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.275</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6925000000000469</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.053614457831325</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1022.759475218544</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.751132884262002</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.681403828623322</v>
+      </c>
+      <c r="K11" t="n">
+        <v>66.38860652072991</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 2.288x + -3682.099</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-3682.098932190307</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.018956099445599e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>117.9300000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8245305029910103</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>83.63707276303212</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.968x + -19007.552</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-19007.55173147595</v>
       </c>
       <c r="Y2" t="n">
         <v>2.305487546816426e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2417.965521357722</v>
+        <v>153.9400000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000068e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>82.92801880106893</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 8.061x + -15991.101</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15991.10059884027</v>
       </c>
       <c r="Y3" t="n">
         <v>2.015821897910493e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2301.573766587481</v>
+        <v>140.1000000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>81.66510725083067</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 6.826x + -13168.147</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13168.14695762455</v>
       </c>
       <c r="Y4" t="n">
         <v>5.862163991411075e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2261.126882389999</v>
+        <v>131.8100000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>81.30848418582072</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 6.542x + -12429.988</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12429.98792904282</v>
       </c>
       <c r="Y5" t="n">
         <v>1.451102402535445e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2232.736037910744</v>
+        <v>130.5900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>80.85566924505827</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.212x + -11647.801</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11647.80140229969</v>
       </c>
       <c r="Y6" t="n">
         <v>1.297928399771804e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2205.440712058308</v>
+        <v>137.3799999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000003472e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>79.02287130917607</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.156x + -9436.253</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9436.252704124152</v>
       </c>
       <c r="Y7" t="n">
         <v>125.3025939566045</v>
       </c>
       <c r="Z7" t="n">
-        <v>2209.799804394665</v>
+        <v>130.0599999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.231638106498333e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>76.28232249545654</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 4.097x + -7251.209</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7251.208791127721</v>
       </c>
       <c r="Y8" t="n">
         <v>5.774349664341948e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2152.559998539048</v>
+        <v>121.1600000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>76.11669083330794</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 4.046x + -7088.804</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7088.803743242986</v>
       </c>
       <c r="Y9" t="n">
         <v>5.944182475079335e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>2127.274118260848</v>
+        <v>125.3099999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>73.98840073679317</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 3.485x + -5966.943</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-5966.943088565754</v>
       </c>
       <c r="Y10" t="n">
         <v>3.396965877691165e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2102.88909854987</v>
+        <v>129.1700000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>69.93700535867382</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 2.738x + -4505.987</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-4505.986568045884</v>
       </c>
       <c r="Y11" t="n">
         <v>4.433486849496139e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>2079.65642336472</v>
+        <v>127.95</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>50.63635627834223</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 1.219x + -1616.933</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-1616.932975848739</v>
       </c>
       <c r="Y12" t="n">
         <v>1.784480943215926e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>2057.527191636916</v>
+        <v>120.77</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>50.34960190914557</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 1.207x + -1602.722</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-1602.722166044065</v>
       </c>
       <c r="Y13" t="n">
         <v>3.011136158609636e-11</v>
       </c>
       <c r="Z13" t="n">
-        <v>2035.811585040424</v>
+        <v>124.23</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>28.04471875508875</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 0.533x + -390.128</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-390.1280970922538</v>
       </c>
       <c r="Y14" t="n">
         <v>5.305616843956753e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>2014.774469124145</v>
+        <v>126.1100000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>-68.79314964519257</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = -2.577x + 5268.739</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>5268.739025487145</v>
       </c>
       <c r="Y15" t="n">
         <v>1.163205638417968e-11</v>
       </c>
       <c r="Z15" t="n">
-        <v>1994.147219145599</v>
+        <v>116.3699999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>-62.86804767742596</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = -1.951x + 4066.303</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>4066.303261733255</v>
       </c>
       <c r="Y16" t="n">
         <v>3.176327724613628e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>1973.157681957575</v>
+        <v>119.0800000000002</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>-78.39695937242601</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = -4.870x + 9217.453</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>9217.453206608392</v>
       </c>
       <c r="Y17" t="n">
         <v>5.157181690796733e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1952.948415790365</v>
+        <v>111.79</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>-76.25317310947334</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = -4.088x + 7715.603</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>7715.60251121063</v>
       </c>
       <c r="Y18" t="n">
         <v>1.66133114213418e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1932.629378412675</v>
+        <v>115.9400000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000102e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>-78.77424625186011</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = -5.038x + 9281.968</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>9281.968402027896</v>
       </c>
       <c r="Y19" t="n">
         <v>1.445087443522884e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1912.442615431743</v>
+        <v>113.76</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000669e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>74.98267765672875</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 3.728x + -6081.930</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-6081.93013548339</v>
       </c>
       <c r="Y20" t="n">
         <v>8.633609001397241e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1891.887281090243</v>
+        <v>111.52</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>74.44158083602571</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 3.592x + -5784.175</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-5784.175344101349</v>
       </c>
       <c r="Y21" t="n">
         <v>8.706330029905297e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>1871.62320880451</v>
+        <v>114.9300000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000204e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>75.30292114361427</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 3.813x + -6100.369</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-6100.36882643658</v>
       </c>
       <c r="Y22" t="n">
         <v>2.837006812737307e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>1851.003755098749</v>
+        <v>107.3500000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000003e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-124.3899999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.04926e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-58.214</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04644696189495512</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6047662694775062</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.619613075383694</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.890705734089445</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.74538630669684</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 10.873x + -24017.426</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-24017.42558936794</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.018961759963461e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>154.5299999999997</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8218558078482964</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-87.51000000000022</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.15374e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-60.08</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03797054009819028</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8841448189762631</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.26974137931004</v>
+      </c>
+      <c r="I3" t="n">
+        <v>173.0477318548305</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.018503658248576</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.13147163907111</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 9.729x + -20180.041</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-20180.0408729663</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.132674585236267e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>137.4100000000003</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8220182930970963</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-67.74000000000024</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.18004e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-60.705</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.57752631034326</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 8.884x + -18040.471</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-18040.47114921402</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.170553018344547e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>124.1600000000003</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.821973648606483</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-69.43999999999983</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.1971e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-61.094</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1359477124183026</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7293293293293914</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.715991763898412</v>
+      </c>
+      <c r="I5" t="n">
+        <v>713.6562886598233</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.65386804657168</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82.93088605358636</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 8.064x + -16118.501</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16118.50102573419</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.148000360147535e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>129.6000000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.821995432473609</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-57.8900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.21371e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.448</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81.46822795171664</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 6.666x + -13041.410</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13041.40975842422</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.95081126143784e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>122.6499999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8221397714155021</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-63.80000000000018</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.23037e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.788</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4662745098038931</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6736093143595919</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.191355932203389</v>
+      </c>
+      <c r="I7" t="n">
+        <v>292.66503322259</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.947805810316715</v>
+      </c>
+      <c r="K7" t="n">
+        <v>81.38561440072588</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 6.601x + -12784.787</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12784.78656282724</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>119.0294440445591</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>131.2200000000003</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.196614208838177e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8166596150155181</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-56.19999999999982</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.24435e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.117</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3178205128205296</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.039636363636344</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.194574898785436</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.220375034984794</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.13937701828618</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 5.753x + -10921.496</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10921.49564717989</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.460346492402929e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>125.8799999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000557e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8225843157073186</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-48.02999999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.26033e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.442</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1526717557252051</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.239229422066519</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.784963887065014</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.144047619047588</v>
+      </c>
+      <c r="K9" t="n">
+        <v>78.09361849994475</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 4.743x + -8784.805</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8784.80523251102</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.457567406465911e-13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>122.0399999999997</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8228596173478033</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-44.34999999999991</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2751e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.735</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6097014925373273</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.003682719546728</v>
+      </c>
+      <c r="H10" t="n">
+        <v>299.8491596638792</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.132101167315206</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.423043603811694</v>
+      </c>
+      <c r="K10" t="n">
+        <v>75.83637764747112</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 3.963x + -7147.063</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7147.062839848233</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.549132589095633e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>120.8399999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.823170328854244</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-42.77999999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.28981e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.019</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4302290076335862</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.24875816993474</v>
+      </c>
+      <c r="H11" t="n">
+        <v>367.562860082289</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.873760580411096</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.549518248175215</v>
+      </c>
+      <c r="K11" t="n">
+        <v>72.73986747606965</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 3.219x + -5613.012</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-5613.012241345244</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.156015966963722e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>121.53</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8234597107321138</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-41.07999999999993</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.30459e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-63.313</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.06406533575317329</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.171212121212403</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.007351077313182</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.106843921660651</v>
+      </c>
+      <c r="K12" t="n">
+        <v>71.59047861190733</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 3.004x + -5166.965</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-5166.964550673434</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.770800010249129e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8237716845670795</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-38.22000000000003</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.31745e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-63.592</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1065573770491746</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.034165366614693</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.590749306198065</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.280710140450405</v>
+      </c>
+      <c r="K13" t="n">
+        <v>66.23152262048305</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 2.271x + -3707.166</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-3707.166244170628</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.582474068052654e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>123.1400000000001</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000368e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8240962852574766</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-36.63000000000011</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.33128e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-63.878</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2197994987468596</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1180043383948174</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.328846153846242</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.700469604320364</v>
+      </c>
+      <c r="K14" t="n">
+        <v>64.25475203196149</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 2.074x + -3319.740</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-3319.740469582753</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.699911127128245e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>125.1800000000001</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000115e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8244241756078227</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-30.22000000000003</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.34492e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-64.126</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.475775656324579</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8960817717205903</v>
+      </c>
+      <c r="H15" t="n">
+        <v>961.1973333335477</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.537706422018219</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.71337122689763</v>
+      </c>
+      <c r="K15" t="n">
+        <v>22.92762099042951</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 0.423x + -155.216</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-155.2162001030414</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.891140401836062e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>120.8500000000001</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8247571507709734</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-27.95000000000005</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.35929e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-64.416</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.281329113924048</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5151773049646078</v>
+      </c>
+      <c r="H16" t="n">
+        <v>723.7262000000411</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.490900195694669</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.768283675387803</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.249891039188775</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 0.057x + 499.214</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>499.2140144648812</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.985272942773469e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>123.5400000000002</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8250851309788773</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-22.51999999999998</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.37169e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-64.68600000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1200374531835111</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.786549062844572</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.694616680889813</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-40.10971874740019</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = -0.842x + 2155.805</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>2155.805052559103</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.452523814215023e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000008798e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8254201358440191</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-21.57999999999993</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.38357e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-64.90600000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2024671052631591</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2546811397557736</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.190197568389069</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.859668034322323</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-48.93478791313917</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = -1.148x + 2697.432</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>2697.432087641368</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>107.908199366633</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.645355878914446e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.7977635727290978</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-11.63999999999987</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.39616e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-65.164</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1636641221374012</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3460.560952381193</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.830323679727472</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.984615384615495</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.25589051771197</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-74.31068098453683</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = -3.560x + 7086.760</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>7086.759727820572</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.107918707631474e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>112.6799999999998</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8260997385674429</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-9.910000000000082</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.40596e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-65.38</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5144366197183463</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7280.824000007189</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.324057217165128</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.303342128408208</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.155306601443777</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-74.92991744729504</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = -3.714x + 7303.129</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>7303.129144768417</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.847758214541238e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>110.6900000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8264401375421431</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-7.730000000000018</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.42004e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-65.67</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1907563025209764</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.089017341040608</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.105840286054973</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.149077612360673</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-74.68593886394015</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = -3.652x + 7082.456</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>7082.456086213839</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.178067897774014e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>114.77</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8267866329088928</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-3.029999999999973</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.43202e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-65.934</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.9834645669283</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.70421686746988</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.71260964912276</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.234339058086627</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-77.55052566930308</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = -4.530x + 8562.697</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>8562.696830682264</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.129758966349955e-12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>112.3499999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8271434006221668</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.16452626865906</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.785x + -25281.559</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-25281.55929627744</v>
       </c>
       <c r="Y2" t="n">
         <v>7.868591856394237e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2873.051711335656</v>
+        <v>263.0700000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000338e-08</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.8553839247722</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.800x + -31411.764</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-31411.76374128252</v>
       </c>
       <c r="Y3" t="n">
         <v>7.386941090141653e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2576.664866082346</v>
+        <v>143.1900000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000031913e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>85.02398593840023</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.485x + -25036.399</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-25036.39938591619</v>
       </c>
       <c r="Y4" t="n">
         <v>6.67126040680553e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>2500.221549416978</v>
+        <v>143.3899999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>84.92742135131648</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.266x + -24126.267</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-24126.26652424969</v>
       </c>
       <c r="Y5" t="n">
         <v>4.589610258755812e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2459.790101126679</v>
+        <v>132.3599999999997</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000036e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>84.07790794279029</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.640x + -20255.639</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20255.63900181402</v>
       </c>
       <c r="Y6" t="n">
         <v>2.359960949912924e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>2426.847221845132</v>
+        <v>127.7199999999998</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>83.02287756366351</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 8.171x + -16838.398</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16838.39833609839</v>
       </c>
       <c r="Y7" t="n">
         <v>3.760370553760807e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>2396.315984342618</v>
+        <v>133.1899999999996</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>81.63012528882994</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.797x + -13700.943</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13700.94313990342</v>
       </c>
       <c r="Y8" t="n">
         <v>4.846590310715652e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2366.057565798163</v>
+        <v>124.3500000000004</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000005845e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>80.90383505785877</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.246x + -12385.145</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12385.14499795848</v>
       </c>
       <c r="Y9" t="n">
         <v>3.821215079699915e-13</v>
       </c>
       <c r="Z9" t="n">
-        <v>2336.223801284917</v>
+        <v>129.1900000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>73.92006560510514</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 3.469x + -6457.358</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-6457.358030293683</v>
       </c>
       <c r="Y10" t="n">
         <v>1.885640927781418e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2308.217256683847</v>
+        <v>120.5199999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000305e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>78.28458178914315</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 4.822x + -9193.046</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9193.045938178606</v>
       </c>
       <c r="Y11" t="n">
         <v>1.555662023802641e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2280.936781745298</v>
+        <v>129.4500000000003</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.0078829532745</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.448x + -25270.975</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-25270.9745077079</v>
       </c>
       <c r="Y2" t="n">
         <v>8.309946678020667e-13</v>
       </c>
       <c r="Z2" t="n">
-        <v>2485.610650043614</v>
+        <v>204.7799999999997</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.44063142246873</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.540x + -26112.598</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-26112.59757183991</v>
       </c>
       <c r="Y3" t="n">
         <v>5.073045540896301e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2372.172733323586</v>
+        <v>142.29</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>85.26229246737196</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.066x + -24600.018</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-24600.01779766982</v>
       </c>
       <c r="Y4" t="n">
         <v>3.824996657782406e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>2331.549221204692</v>
+        <v>134.6900000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>84.63861690599957</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.656x + -21330.647</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21330.64729598035</v>
       </c>
       <c r="Y5" t="n">
         <v>1.555386667669817e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2299.858461579325</v>
+        <v>137.0199999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001449e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>84.47579681114158</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.340x + -20424.201</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20424.20110545467</v>
       </c>
       <c r="Y6" t="n">
         <v>3.109190749550578e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2270.18104004765</v>
+        <v>126.8599999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001782e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>84.12649034663309</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.721x + -18922.248</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-18922.24803844098</v>
       </c>
       <c r="Y7" t="n">
         <v>3.549341362568593e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2241.100628829656</v>
+        <v>120.3499999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000012e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>83.35567793304396</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 8.585x + -16423.551</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-16423.55133321817</v>
       </c>
       <c r="Y8" t="n">
         <v>1.402424305082267e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2212.917017104517</v>
+        <v>125.47</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000056e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>82.87607870025458</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 8.001x + -15080.722</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15080.72249101161</v>
       </c>
       <c r="Y9" t="n">
         <v>2.053972134084737e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>2186.593551621414</v>
+        <v>127.28</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>81.62960740627466</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 6.796x + -12558.127</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12558.12680005444</v>
       </c>
       <c r="Y10" t="n">
         <v>1.260525917041039e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2162.173723793554</v>
+        <v>120.25</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000203e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>80.64484665020996</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 6.070x + -11034.925</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11034.92547586477</v>
       </c>
       <c r="Y11" t="n">
         <v>4.567745128575015e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2138.299674143591</v>
+        <v>123.72</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000022e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>80.25023565861777</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 5.820x + -10454.226</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10454.22567970742</v>
       </c>
       <c r="Y12" t="n">
         <v>2.389039415977951e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2115.391337621069</v>
+        <v>126.5799999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000225e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>69.02407399548717</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 2.608x + -4258.023</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-4258.023366482982</v>
       </c>
       <c r="Y13" t="n">
         <v>5.155813984957102e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2092.927651858601</v>
+        <v>114.27</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000008e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>75.9714115717095</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 4.002x + -6855.007</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-6855.007206655303</v>
       </c>
       <c r="Y14" t="n">
         <v>5.822896123862566e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>2071.226138550229</v>
+        <v>121.25</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>43.8615558925129</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 0.961x + -1115.675</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-1115.674699726089</v>
       </c>
       <c r="Y15" t="n">
         <v>5.04175754828238e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2050.369855721834</v>
+        <v>111.6500000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>63.04135340473545</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 1.966x + -3000.044</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-3000.043639337012</v>
       </c>
       <c r="Y16" t="n">
         <v>5.892824235530616e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>2029.181306073275</v>
+        <v>119.8300000000002</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>45.43448501065251</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 1.015x + -1248.499</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-1248.498711361743</v>
       </c>
       <c r="Y17" t="n">
         <v>1.240231171114659e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>2008.1894650394</v>
+        <v>117.21</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>-72.92742366345705</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = -3.256x + 6505.741</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>6505.740889531367</v>
       </c>
       <c r="Y18" t="n">
         <v>465.5936907559623</v>
       </c>
       <c r="Z18" t="n">
-        <v>1743.016283833224</v>
+        <v>104.8700000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.988629627763726e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>-30.26983426558344</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = -0.584x + 1616.698</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1616.698489650714</v>
       </c>
       <c r="Y19" t="n">
         <v>5.787366203060401e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1967.176560805307</v>
+        <v>113.1200000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>-74.38969936980901</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = -3.579x + 6905.370</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>6905.369524495869</v>
       </c>
       <c r="Y20" t="n">
         <v>1.102194484601837e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1947.229307023899</v>
+        <v>106.8999999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>-76.43617560078853</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = -4.145x + 7829.007</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>7829.0071820168</v>
       </c>
       <c r="Y21" t="n">
         <v>6.799349272414639e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1927.511229689941</v>
+        <v>106.3899999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>-76.73571255951464</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = -4.242x + 7876.848</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>7876.847570079973</v>
       </c>
       <c r="Y22" t="n">
         <v>3.579989602858862e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>1907.721475918999</v>
+        <v>108.8399999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.68508640050176</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.036x + -21927.340</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21927.33982403725</v>
       </c>
       <c r="Y2" t="n">
         <v>1.531754418550794e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2682.331075286985</v>
+        <v>292.1700000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000009e-08</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.49846534058848</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.702x + -27183.681</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-27183.68093179626</v>
       </c>
       <c r="Y3" t="n">
         <v>9.567543483768303e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2418.552936682619</v>
+        <v>166.9500000000003</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000131e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.00571262187555</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.443x + -23542.616</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-23542.6158993587</v>
       </c>
       <c r="Y4" t="n">
         <v>1.414655296836617e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2351.00434950218</v>
+        <v>145.3099999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001422e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>84.95371298669677</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.325x + -22889.888</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-22889.88801247129</v>
       </c>
       <c r="Y5" t="n">
         <v>2.074252383869141e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2311.64343558264</v>
+        <v>134.6100000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000516e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>84.39779243039936</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.195x + -20227.348</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20227.34755178795</v>
       </c>
       <c r="Y6" t="n">
         <v>1.219845479983952e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2277.875356554868</v>
+        <v>131.2200000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001422e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>83.36981504542359</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 8.603x + -16713.459</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16713.45949904044</v>
       </c>
       <c r="Y7" t="n">
         <v>1.954266480573372e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2245.355227051818</v>
+        <v>134.5200000000002</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000009e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>82.67269415750867</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 7.777x + -14842.733</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14842.73348834367</v>
       </c>
       <c r="Y8" t="n">
         <v>3.495896350373366e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2214.379935668665</v>
+        <v>130.25</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000007262e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>81.59169219635113</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.765x + -12651.224</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12651.22439576775</v>
       </c>
       <c r="Y9" t="n">
         <v>4.516199958612458e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2184.161441616359</v>
+        <v>130.0600000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002123e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>79.62069416838311</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.460x + -9955.161</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9955.161489567143</v>
       </c>
       <c r="Y10" t="n">
         <v>3.243334346150276e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>2155.090664404788</v>
+        <v>127.1099999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>75.1224995448122</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 3.764x + -6556.328</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-6556.328123392039</v>
       </c>
       <c r="Y11" t="n">
         <v>2.59161761483623e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2127.584134469996</v>
+        <v>120.49</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000035e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.25101179123476</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.037x + -26266.441</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26266.44067188984</v>
       </c>
       <c r="Y2" t="n">
         <v>7.81803029116612e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2450.505382732978</v>
+        <v>194.3999999999996</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>84.98704961183948</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.400x + -23409.503</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-23409.50289409664</v>
       </c>
       <c r="Y3" t="n">
         <v>3.085923516628149e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2347.688636653309</v>
+        <v>146.3099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000184e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>84.82604301641445</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.044x + -22255.775</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-22255.7748838759</v>
       </c>
       <c r="Y4" t="n">
         <v>3.265186523582785e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2309.481426074799</v>
+        <v>134.1599999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>84.20005825457285</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.845x + -19500.892</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-19500.89224602438</v>
       </c>
       <c r="Y5" t="n">
         <v>4.073219316667966e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2279.789276511653</v>
+        <v>131.1099999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>83.72363765750833</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.092x + -17734.641</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-17734.64062313891</v>
       </c>
       <c r="Y6" t="n">
         <v>2.298161265587734e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2251.031850161536</v>
+        <v>123.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003917e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>82.91530875048139</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 8.046x + -15418.210</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-15418.20997681798</v>
       </c>
       <c r="Y7" t="n">
         <v>3.042972965399277e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2222.276373719201</v>
+        <v>133.1500000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000002e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>81.82888160635306</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 6.964x + -13086.260</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13086.25996492417</v>
       </c>
       <c r="Y8" t="n">
         <v>7.933617990239786e-13</v>
       </c>
       <c r="Z8" t="n">
-        <v>2194.046159524713</v>
+        <v>125.3800000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>81.29782815404234</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.533x + -12093.728</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12093.72838407259</v>
       </c>
       <c r="Y9" t="n">
         <v>4.263239373616513e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2166.462163373291</v>
+        <v>128.3900000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000004362e-08</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>80.23500153666801</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.811x + -10551.161</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10551.16107144091</v>
       </c>
       <c r="Y10" t="n">
         <v>3.740060517801523e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2139.724830477282</v>
+        <v>125.3399999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>78.01720259259039</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 4.712x + -8339.407</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8339.406866685262</v>
       </c>
       <c r="Y11" t="n">
         <v>2.888759237023528e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>2114.494610485073</v>
+        <v>125.4199999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>75.25192574559955</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 3.799x + -6528.485</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-6528.484747240417</v>
       </c>
       <c r="Y12" t="n">
         <v>1.693809161777374e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2090.244748072032</v>
+        <v>121.98</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000001333e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>71.39174275552924</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 2.970x + -4907.951</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-4907.951170024037</v>
       </c>
       <c r="Y13" t="n">
         <v>3.391034973962976e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2066.446967194479</v>
+        <v>120.1899999999998</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000208e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>68.20342119189704</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 2.501x + -4011.885</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-4011.884611853175</v>
       </c>
       <c r="Y14" t="n">
         <v>7.300316489939316e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2044.275253061377</v>
+        <v>123.7</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000009e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>54.84148549150882</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 1.420x + -2001.452</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-2001.451557276632</v>
       </c>
       <c r="Y15" t="n">
         <v>1.191286456926767e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>2022.474701616153</v>
+        <v>122.9000000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>-23.63536197186177</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = -0.438x + 1401.696</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1401.696019463868</v>
       </c>
       <c r="Y16" t="n">
         <v>5.182612958551111e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>2000.97871736425</v>
+        <v>115.8800000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>-36.01505624880785</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = -0.727x + 1872.911</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1872.9110975536</v>
       </c>
       <c r="Y17" t="n">
         <v>4.711685474233437e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1979.544298344718</v>
+        <v>118.29</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>-68.81653130893991</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = -2.580x + 5169.995</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>5169.994898817462</v>
       </c>
       <c r="Y18" t="n">
         <v>2.799914322032931e-11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1958.74119708094</v>
+        <v>112.3800000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>-74.81551650009332</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = -3.685x + 7053.335</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>7053.334562523114</v>
       </c>
       <c r="Y19" t="n">
         <v>5.688386246057792e-12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1937.588282522877</v>
+        <v>110.7800000000002</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>-78.03794608922435</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = -4.720x + 8779.037</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>8779.037450271646</v>
       </c>
       <c r="Y20" t="n">
         <v>6.76441651384682e-12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1916.581456870169</v>
+        <v>107.99</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>-76.73231190597836</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = -4.241x + 7825.692</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>7825.69187997649</v>
       </c>
       <c r="Y21" t="n">
         <v>461.2513999276247</v>
       </c>
       <c r="Z21" t="n">
-        <v>1696.838879881661</v>
+        <v>112.01</v>
       </c>
       <c r="AA21" t="n">
         <v>1.754721301734316e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>74.49474938169908</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 3.605x + -5830.555</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-5830.555360614539</v>
       </c>
       <c r="Y22" t="n">
         <v>8.467865674446815e-11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1875.43471340691</v>
+        <v>108.73</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.96946972824345</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.466x + -22388.803</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-22388.80319877982</v>
       </c>
       <c r="Y2" t="n">
         <v>1.040828909659335e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2591.399615200155</v>
+        <v>289.4000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000005124e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.53954779932567</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.819x + -26396.609</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-26396.60937732317</v>
       </c>
       <c r="Y3" t="n">
         <v>3.883353722665607e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2321.20835883814</v>
+        <v>143.6699999999996</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000022e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>85.04865534310625</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.543x + -22842.830</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-22842.82970925371</v>
       </c>
       <c r="Y4" t="n">
         <v>1.410196628143468e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2253.115139858811</v>
+        <v>129.95</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>83.52834704789227</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 8.816x + -16938.416</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16938.41615410658</v>
       </c>
       <c r="Y5" t="n">
         <v>1.355990394307768e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2213.466860077176</v>
+        <v>124.6900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000068331e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>81.98602521586047</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 7.103x + -13298.135</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13298.13547812229</v>
       </c>
       <c r="Y6" t="n">
         <v>1.743619582382439e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2179.268045470058</v>
+        <v>127.71</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000063e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>79.93270674439823</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.633x + -10260.825</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10260.82528673172</v>
       </c>
       <c r="Y7" t="n">
         <v>2.470805315339147e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2146.054531081825</v>
+        <v>129.21</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000087e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>76.96888144100916</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 4.321x + -7605.695</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7605.695436689388</v>
       </c>
       <c r="Y8" t="n">
         <v>9.780358642101849e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2114.055675517818</v>
+        <v>129.9200000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000025e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>72.80696309005485</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 3.232x + -5445.027</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-5445.0274526308</v>
       </c>
       <c r="Y9" t="n">
         <v>3.73992650562642e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2082.746494416246</v>
+        <v>126.51</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002658e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>60.86448546867136</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 1.794x + -2702.963</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-2702.963308183399</v>
       </c>
       <c r="Y10" t="n">
         <v>5.498870308889907e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2053.725834070181</v>
+        <v>123.48</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>-18.15268803265198</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = -0.328x + 1256.842</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1256.841685910484</v>
       </c>
       <c r="Y11" t="n">
         <v>2.863599503820712e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>2026.031721643197</v>
+        <v>113.9299999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005478e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.38198389171703</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.380x + -26828.378</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26828.37751742029</v>
       </c>
       <c r="Y2" t="n">
         <v>2.945528969817851e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2424.07613736572</v>
+        <v>173.5799999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000125e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>84.91485694832897</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.238x + -22740.029</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-22740.02872814703</v>
       </c>
       <c r="Y3" t="n">
         <v>1.667653178952902e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2308.935672098836</v>
+        <v>138.9600000000003</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000033749e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>84.33357356445418</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.078x + -19956.310</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-19956.30977812716</v>
       </c>
       <c r="Y4" t="n">
         <v>1.462409081477049e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2271.735300960781</v>
+        <v>131.79</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>83.91562640302743</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.381x + -18308.841</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-18308.84051384599</v>
       </c>
       <c r="Y5" t="n">
         <v>5.617557587630218e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2245.239778973065</v>
+        <v>132.6400000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000057e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>83.42670931435386</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 8.678x + -16694.666</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-16694.66620275111</v>
       </c>
       <c r="Y6" t="n">
         <v>1.437707714253742e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2219.411129374885</v>
+        <v>134.76</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>82.57540916369737</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 7.674x + -14521.805</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14521.8051493096</v>
       </c>
       <c r="Y7" t="n">
         <v>1.787847203415164e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>2194.750305082619</v>
+        <v>127.6500000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>81.99637270391783</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 7.112x + -13269.737</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13269.73746493533</v>
       </c>
       <c r="Y8" t="n">
         <v>4.502112230666082e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2171.177977453772</v>
+        <v>125.3400000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>80.72897074396093</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.126x + -11214.572</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11214.57245444018</v>
       </c>
       <c r="Y9" t="n">
         <v>1.176966877862571e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2148.020677728776</v>
+        <v>124.25</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000972e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>79.52783502169258</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 5.410x + -9725.398</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9725.398204445482</v>
       </c>
       <c r="Y10" t="n">
         <v>2.287214376077713e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2126.353981522449</v>
+        <v>122.25</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000074e-08</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>78.76880552389031</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.036x + -8935.459</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8935.4587760678</v>
       </c>
       <c r="Y11" t="n">
         <v>4.291454818469938e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2105.199455352495</v>
+        <v>126.9000000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000004e-08</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>73.43323657420989</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 3.362x + -5674.162</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-5674.162228133481</v>
       </c>
       <c r="Y12" t="n">
         <v>2.966514247220899e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2084.414270177135</v>
+        <v>116.55</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000003e-08</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>72.71956515545914</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 3.214x + -5368.021</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-5368.021292083731</v>
       </c>
       <c r="Y13" t="n">
         <v>1.083413885404588e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2064.244919235202</v>
+        <v>121.25</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000098e-08</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>74.58429760798448</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 3.627x + -6107.819</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-6107.818877749405</v>
       </c>
       <c r="Y14" t="n">
         <v>7.927002076461528e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2044.298649405384</v>
+        <v>130.97</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>65.83595470154087</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 2.229x + -3482.672</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-3482.671990874283</v>
       </c>
       <c r="Y15" t="n">
         <v>1.076747928480313e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2024.673744779838</v>
+        <v>125.5900000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000794e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>27.52461027105345</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 0.521x + -328.387</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-328.387019495245</v>
       </c>
       <c r="Y16" t="n">
         <v>3.279216371395521e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2005.24249818509</v>
+        <v>118.8500000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000003e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>-17.26249288163301</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = -0.311x + 1172.470</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1172.469699247953</v>
       </c>
       <c r="Y17" t="n">
         <v>1.944392334971067e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1985.935182710915</v>
+        <v>116.8700000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>45.25799158971661</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 1.009x + -1235.475</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-1235.474705142059</v>
       </c>
       <c r="Y18" t="n">
         <v>4.268326875040545e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1966.762201431688</v>
+        <v>124.8700000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>-64.57295199316155</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = -2.103x + 4320.004</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>4320.004066215066</v>
       </c>
       <c r="Y19" t="n">
         <v>8.512479130005232e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1947.623851993005</v>
+        <v>113.6299999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>-59.11177625396401</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = -1.672x + 3490.251</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>3490.250535860603</v>
       </c>
       <c r="Y20" t="n">
         <v>2.177546872564243e-12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1928.492748216604</v>
+        <v>118.5</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>-75.71666965056761</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = -3.928x + 7403.073</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>7403.073278594797</v>
       </c>
       <c r="Y21" t="n">
         <v>2.291644411025263e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1909.218863983835</v>
+        <v>111.27</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>-73.08906196034226</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = -3.289x + 6199.558</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>6199.55822260074</v>
       </c>
       <c r="Y22" t="n">
         <v>4.590795143356186e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>1890.459693166599</v>
+        <v>114.78</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.02635672175349</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.557x + -18661.780</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-18661.78018724119</v>
       </c>
       <c r="Y2" t="n">
         <v>3.131801177028946e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2112.413326485524</v>
+        <v>275.71</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>85.37214446279282</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.354x + -20851.079</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-20851.07949251159</v>
       </c>
       <c r="Y3" t="n">
         <v>2.400859152752665e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>1895.102039855793</v>
+        <v>135.3199999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>84.37694364448107</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.157x + -16414.504</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-16414.50398004065</v>
       </c>
       <c r="Y4" t="n">
         <v>7.260402274030566e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>1839.135513088014</v>
+        <v>127.1199999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001192e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>83.13626690366171</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 8.308x + -13082.172</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13082.17204302591</v>
       </c>
       <c r="Y5" t="n">
         <v>3.602179346621871e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1806.943526198307</v>
+        <v>122.79</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000005129e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>81.33681676392436</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 6.563x + -10050.725</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10050.72522303196</v>
       </c>
       <c r="Y6" t="n">
         <v>2.346683637406767</v>
       </c>
       <c r="Z6" t="n">
-        <v>1907.220431516589</v>
+        <v>111.28</v>
       </c>
       <c r="AA6" t="n">
         <v>1.51883301213593e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>80.50229486478456</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.977x + -8986.067</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8986.067495305362</v>
       </c>
       <c r="Y7" t="n">
         <v>2.732442839492702e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1751.145691773412</v>
+        <v>118.3499999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000063e-08</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>78.18563593405783</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 4.781x + -6965.624</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-6965.624355708699</v>
       </c>
       <c r="Y8" t="n">
         <v>1.958784315320988e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1723.454014588223</v>
+        <v>113.73</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000039e-08</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>74.6982300161572</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 3.655x + -5118.323</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-5118.32328526468</v>
       </c>
       <c r="Y9" t="n">
         <v>6.300005257000134e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>1696.018140351011</v>
+        <v>110.6699999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>71.57503328686998</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 3.002x + -4046.337</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-4046.337269879557</v>
       </c>
       <c r="Y10" t="n">
         <v>3.736013423185014e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>1670.48590028759</v>
+        <v>109.6600000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>62.55343621990598</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 1.925x + -2373.948</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-2373.947858626498</v>
       </c>
       <c r="Y11" t="n">
         <v>4.893808886928976e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1646.944710328125</v>
+        <v>106.6600000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000007e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>84.781353702259</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.949x + -23178.240</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.94867250983305</v>
       </c>
       <c r="X2" t="n">
         <v>-23178.24023521944</v>
@@ -600,7 +598,7 @@
         <v>1.276838273332596e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>140.1799999999998</v>
+        <v>2422.705116619908</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000742e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>84.57848864456533</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.537x + -21796.422</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.53667018594114</v>
       </c>
       <c r="X3" t="n">
         <v>-21796.42237363628</v>
@@ -652,7 +648,7 @@
         <v>1.729833070191376e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>126.8299999999999</v>
+        <v>2370.400911638438</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000122e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>83.83042443673912</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.251x + -18694.047</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.250905860654612</v>
       </c>
       <c r="X4" t="n">
         <v>-18694.04726858732</v>
@@ -704,7 +698,7 @@
         <v>5.901129054328679e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>129.8900000000001</v>
+        <v>2327.83135363464</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>83.07162700835414</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 8.229x + -16278.731</t>
-        </is>
+      <c r="W5" t="n">
+        <v>8.229383810777586</v>
       </c>
       <c r="X5" t="n">
         <v>-16278.73085870794</v>
@@ -756,7 +748,7 @@
         <v>1.284194519695916e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>128.7199999999998</v>
+        <v>2288.712561472484</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>82.36197485878387</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 7.457x + -14454.604</t>
-        </is>
+      <c r="W6" t="n">
+        <v>7.456897644967356</v>
       </c>
       <c r="X6" t="n">
         <v>-14454.60429870954</v>
@@ -808,7 +798,7 @@
         <v>6.629721820495902e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>133.05</v>
+        <v>2256.205389589224</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>81.43053702847548</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.636x + -12602.995</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.636111229355053</v>
       </c>
       <c r="X7" t="n">
         <v>-12602.99540603366</v>
@@ -860,7 +848,7 @@
         <v>5.214984352901275e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>123.3899999999999</v>
+        <v>2222.869071045858</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000019e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>79.281078070878</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.283x + -9728.877</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.282786958013472</v>
       </c>
       <c r="X8" t="n">
         <v>-9728.877440864233</v>
@@ -912,7 +898,7 @@
         <v>1.150855921476016e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>114.1599999999999</v>
+        <v>2191.775370489228</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001085e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>78.59841228995109</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 4.959x + -9004.028</t>
-        </is>
+      <c r="W9" t="n">
+        <v>4.958738167826652</v>
       </c>
       <c r="X9" t="n">
         <v>-9004.028070926124</v>
@@ -964,7 +948,7 @@
         <v>2.572198403157648e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>124.97</v>
+        <v>2162.685098791999</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>77.15390158802263</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 4.385x + -7790.142</t>
-        </is>
+      <c r="W10" t="n">
+        <v>4.385182514387092</v>
       </c>
       <c r="X10" t="n">
         <v>-7790.141647886042</v>
@@ -1016,7 +998,7 @@
         <v>2.50505628096771e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>123.78</v>
+        <v>2135.956504251289</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000012837e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>66.38860652072991</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 2.288x + -3682.099</t>
-        </is>
+      <c r="W11" t="n">
+        <v>2.287669458763684</v>
       </c>
       <c r="X11" t="n">
         <v>-3682.098932190307</v>
@@ -1068,7 +1048,7 @@
         <v>8.018956099445599e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>117.9300000000001</v>
+        <v>2110.764773032064</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>83.63707276303212</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.968x + -19007.552</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.967577436002831</v>
       </c>
       <c r="X2" t="n">
         <v>-19007.55173147595</v>
@@ -1266,7 +1244,7 @@
         <v>2.305487546816426e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>153.9400000000001</v>
+        <v>2417.965521357722</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000068e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>82.92801880106893</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 8.061x + -15991.101</t>
-        </is>
+      <c r="W3" t="n">
+        <v>8.060615349379423</v>
       </c>
       <c r="X3" t="n">
         <v>-15991.10059884027</v>
@@ -1318,7 +1294,7 @@
         <v>2.015821897910493e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>140.1000000000001</v>
+        <v>2301.573766587481</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>81.66510725083067</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 6.826x + -13168.147</t>
-        </is>
+      <c r="W4" t="n">
+        <v>6.825648183267987</v>
       </c>
       <c r="X4" t="n">
         <v>-13168.14695762455</v>
@@ -1370,7 +1344,7 @@
         <v>5.862163991411075e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>131.8100000000002</v>
+        <v>2261.126882389999</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>81.30848418582072</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 6.542x + -12429.988</t>
-        </is>
+      <c r="W5" t="n">
+        <v>6.541507475214534</v>
       </c>
       <c r="X5" t="n">
         <v>-12429.98792904282</v>
@@ -1422,7 +1394,7 @@
         <v>1.451102402535445e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>130.5900000000001</v>
+        <v>2232.736037910744</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>80.85566924505827</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.212x + -11647.801</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.212425880600651</v>
       </c>
       <c r="X6" t="n">
         <v>-11647.80140229969</v>
@@ -1474,7 +1444,7 @@
         <v>1.297928399771804e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>137.3799999999999</v>
+        <v>2205.440712058308</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000003472e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>79.02287130917607</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.156x + -9436.253</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.155540620960839</v>
       </c>
       <c r="X7" t="n">
         <v>-9436.252704124152</v>
@@ -1526,7 +1494,7 @@
         <v>125.3025939566045</v>
       </c>
       <c r="Z7" t="n">
-        <v>130.0599999999999</v>
+        <v>2209.799804394665</v>
       </c>
       <c r="AA7" t="n">
         <v>1.231638106498333e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>76.28232249545654</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 4.097x + -7251.209</t>
-        </is>
+      <c r="W8" t="n">
+        <v>4.096671401867356</v>
       </c>
       <c r="X8" t="n">
         <v>-7251.208791127721</v>
@@ -1578,7 +1544,7 @@
         <v>5.774349664341948e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>121.1600000000001</v>
+        <v>2152.559998539048</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>76.11669083330794</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 4.046x + -7088.804</t>
-        </is>
+      <c r="W9" t="n">
+        <v>4.045866336559725</v>
       </c>
       <c r="X9" t="n">
         <v>-7088.803743242986</v>
@@ -1630,7 +1594,7 @@
         <v>5.944182475079335e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>125.3099999999999</v>
+        <v>2127.274118260848</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>73.98840073679317</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 3.485x + -5966.943</t>
-        </is>
+      <c r="W10" t="n">
+        <v>3.484751726182765</v>
       </c>
       <c r="X10" t="n">
         <v>-5966.943088565754</v>
@@ -1682,7 +1644,7 @@
         <v>3.396965877691165e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>129.1700000000001</v>
+        <v>2102.88909854987</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>69.93700535867382</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 2.738x + -4505.987</t>
-        </is>
+      <c r="W11" t="n">
+        <v>2.738106809484905</v>
       </c>
       <c r="X11" t="n">
         <v>-4505.986568045884</v>
@@ -1734,7 +1694,7 @@
         <v>4.433486849496139e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>127.95</v>
+        <v>2079.65642336472</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>50.63635627834223</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 1.219x + -1616.933</t>
-        </is>
+      <c r="W12" t="n">
+        <v>1.218996133234133</v>
       </c>
       <c r="X12" t="n">
         <v>-1616.932975848739</v>
@@ -1786,7 +1744,7 @@
         <v>1.784480943215926e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>120.77</v>
+        <v>2057.527191636916</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>50.34960190914557</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 1.207x + -1602.722</t>
-        </is>
+      <c r="W13" t="n">
+        <v>1.206629765195123</v>
       </c>
       <c r="X13" t="n">
         <v>-1602.722166044065</v>
@@ -1838,7 +1794,7 @@
         <v>3.011136158609636e-11</v>
       </c>
       <c r="Z13" t="n">
-        <v>124.23</v>
+        <v>2035.811585040424</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>28.04471875508875</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 0.533x + -390.128</t>
-        </is>
+      <c r="W14" t="n">
+        <v>0.5327109930503482</v>
       </c>
       <c r="X14" t="n">
         <v>-390.1280970922538</v>
@@ -1890,7 +1844,7 @@
         <v>5.305616843956753e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>126.1100000000001</v>
+        <v>2014.774469124145</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>-68.79314964519257</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = -2.577x + 5268.739</t>
-        </is>
+      <c r="W15" t="n">
+        <v>-2.577239926784001</v>
       </c>
       <c r="X15" t="n">
         <v>5268.739025487145</v>
@@ -1942,7 +1894,7 @@
         <v>1.163205638417968e-11</v>
       </c>
       <c r="Z15" t="n">
-        <v>116.3699999999999</v>
+        <v>1994.147219145599</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>-62.86804767742596</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = -1.951x + 4066.303</t>
-        </is>
+      <c r="W16" t="n">
+        <v>-1.95148696353566</v>
       </c>
       <c r="X16" t="n">
         <v>4066.303261733255</v>
@@ -1994,7 +1944,7 @@
         <v>3.176327724613628e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>119.0800000000002</v>
+        <v>1973.157681957575</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>-78.39695937242601</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = -4.870x + 9217.453</t>
-        </is>
+      <c r="W17" t="n">
+        <v>-4.870307937627723</v>
       </c>
       <c r="X17" t="n">
         <v>9217.453206608392</v>
@@ -2046,7 +1994,7 @@
         <v>5.157181690796733e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>111.79</v>
+        <v>1952.948415790365</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>-76.25317310947334</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = -4.088x + 7715.603</t>
-        </is>
+      <c r="W18" t="n">
+        <v>-4.087643211434847</v>
       </c>
       <c r="X18" t="n">
         <v>7715.60251121063</v>
@@ -2098,7 +2044,7 @@
         <v>1.66133114213418e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>115.9400000000001</v>
+        <v>1932.629378412675</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000102e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>-78.77424625186011</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = -5.038x + 9281.968</t>
-        </is>
+      <c r="W19" t="n">
+        <v>-5.038481808364024</v>
       </c>
       <c r="X19" t="n">
         <v>9281.968402027896</v>
@@ -2150,7 +2094,7 @@
         <v>1.445087443522884e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>113.76</v>
+        <v>1912.442615431743</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000669e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>74.98267765672875</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 3.728x + -6081.930</t>
-        </is>
+      <c r="W20" t="n">
+        <v>3.727542621691137</v>
       </c>
       <c r="X20" t="n">
         <v>-6081.93013548339</v>
@@ -2202,7 +2144,7 @@
         <v>8.633609001397241e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>111.52</v>
+        <v>1891.887281090243</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>74.44158083602571</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 3.592x + -5784.175</t>
-        </is>
+      <c r="W21" t="n">
+        <v>3.591658864458969</v>
       </c>
       <c r="X21" t="n">
         <v>-5784.175344101349</v>
@@ -2254,7 +2194,7 @@
         <v>8.706330029905297e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>114.9300000000001</v>
+        <v>1871.62320880451</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000204e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>75.30292114361427</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 3.813x + -6100.369</t>
-        </is>
+      <c r="W22" t="n">
+        <v>3.812565189279494</v>
       </c>
       <c r="X22" t="n">
         <v>-6100.36882643658</v>
@@ -2306,7 +2244,7 @@
         <v>2.837006812737307e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>107.3500000000001</v>
+        <v>1851.003755098749</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000003e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>84.74538630669684</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.873x + -24017.426</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.87331222080123</v>
       </c>
       <c r="X2" t="n">
         <v>-24017.42558936794</v>
@@ -2504,7 +2440,7 @@
         <v>4.018961759963461e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>154.5299999999997</v>
+        <v>2505.224868458088</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000001e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>84.13147163907111</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.729x + -20180.041</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.729062230346807</v>
       </c>
       <c r="X3" t="n">
         <v>-20180.0408729663</v>
@@ -2556,7 +2490,7 @@
         <v>6.132674585236267e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>137.4100000000003</v>
+        <v>2390.069361808413</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>83.57752631034326</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 8.884x + -18040.471</t>
-        </is>
+      <c r="W4" t="n">
+        <v>8.883743071332535</v>
       </c>
       <c r="X4" t="n">
         <v>-18040.47114921402</v>
@@ -2608,7 +2540,7 @@
         <v>1.170553018344547e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>124.1600000000003</v>
+        <v>2352.29782171012</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>82.93088605358636</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 8.064x + -16118.501</t>
-        </is>
+      <c r="W5" t="n">
+        <v>8.063918194323405</v>
       </c>
       <c r="X5" t="n">
         <v>-16118.50102573419</v>
@@ -2660,7 +2590,7 @@
         <v>1.148000360147535e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>129.6000000000001</v>
+        <v>2324.863946572199</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000002e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>81.46822795171664</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.666x + -13041.410</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.66586849835438</v>
       </c>
       <c r="X6" t="n">
         <v>-13041.40975842422</v>
@@ -2712,7 +2640,7 @@
         <v>3.95081126143784e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>122.6499999999999</v>
+        <v>2298.503304776806</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>81.38561440072588</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 6.601x + -12784.787</t>
-        </is>
+      <c r="W7" t="n">
+        <v>6.600982078730866</v>
       </c>
       <c r="X7" t="n">
         <v>-12784.78656282724</v>
@@ -2764,7 +2690,7 @@
         <v>119.0294440445591</v>
       </c>
       <c r="Z7" t="n">
-        <v>131.2200000000003</v>
+        <v>2227.125863504964</v>
       </c>
       <c r="AA7" t="n">
         <v>1.196614208838177e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>80.13937701828618</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 5.753x + -10921.496</t>
-        </is>
+      <c r="W8" t="n">
+        <v>5.7530834835997</v>
       </c>
       <c r="X8" t="n">
         <v>-10921.49564717989</v>
@@ -2816,7 +2740,7 @@
         <v>1.460346492402929e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>125.8799999999999</v>
+        <v>2247.267598737305</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000557e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>78.09361849994475</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 4.743x + -8784.805</t>
-        </is>
+      <c r="W9" t="n">
+        <v>4.742722040825522</v>
       </c>
       <c r="X9" t="n">
         <v>-8784.80523251102</v>
@@ -2868,7 +2790,7 @@
         <v>2.457567406465911e-13</v>
       </c>
       <c r="Z9" t="n">
-        <v>122.0399999999997</v>
+        <v>2222.816833725593</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>75.83637764747112</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 3.963x + -7147.063</t>
-        </is>
+      <c r="W10" t="n">
+        <v>3.962538992795366</v>
       </c>
       <c r="X10" t="n">
         <v>-7147.062839848233</v>
@@ -2920,7 +2840,7 @@
         <v>2.549132589095633e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>120.8399999999999</v>
+        <v>2199.248690266319</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000036e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>72.73986747606965</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 3.219x + -5613.012</t>
-        </is>
+      <c r="W11" t="n">
+        <v>3.218516401070234</v>
       </c>
       <c r="X11" t="n">
         <v>-5613.012241345244</v>
@@ -2972,7 +2890,7 @@
         <v>1.156015966963722e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>121.53</v>
+        <v>2176.297211736432</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000009e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>71.59047861190733</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 3.004x + -5166.965</t>
-        </is>
+      <c r="W12" t="n">
+        <v>3.004443841302589</v>
       </c>
       <c r="X12" t="n">
         <v>-5166.964550673434</v>
@@ -3024,7 +2940,7 @@
         <v>3.770800010249129e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>124.7</v>
+        <v>2154.008670540396</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000002e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>66.23152262048305</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 2.271x + -3707.166</t>
-        </is>
+      <c r="W13" t="n">
+        <v>2.270686163714053</v>
       </c>
       <c r="X13" t="n">
         <v>-3707.166244170628</v>
@@ -3076,7 +2990,7 @@
         <v>2.582474068052654e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>123.1400000000001</v>
+        <v>2132.535168681811</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000368e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>64.25475203196149</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 2.074x + -3319.740</t>
-        </is>
+      <c r="W14" t="n">
+        <v>2.073654076586092</v>
       </c>
       <c r="X14" t="n">
         <v>-3319.740469582753</v>
@@ -3128,7 +3040,7 @@
         <v>3.699911127128245e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>125.1800000000001</v>
+        <v>2111.570456908615</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000115e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>22.92762099042951</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 0.423x + -155.216</t>
-        </is>
+      <c r="W15" t="n">
+        <v>0.4229847510692788</v>
       </c>
       <c r="X15" t="n">
         <v>-155.2162001030414</v>
@@ -3180,7 +3090,7 @@
         <v>1.891140401836062e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>120.8500000000001</v>
+        <v>2091.07144806103</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>3.249891039188775</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 0.057x + 499.214</t>
-        </is>
+      <c r="W16" t="n">
+        <v>0.05678220727091689</v>
       </c>
       <c r="X16" t="n">
         <v>499.2140144648812</v>
@@ -3232,7 +3140,7 @@
         <v>5.985272942773469e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>123.5400000000002</v>
+        <v>2070.557646823435</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>-40.10971874740019</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = -0.842x + 2155.805</t>
-        </is>
+      <c r="W17" t="n">
+        <v>-0.8423681365908554</v>
       </c>
       <c r="X17" t="n">
         <v>2155.805052559103</v>
@@ -3284,7 +3190,7 @@
         <v>1.452523814215023e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>120.55</v>
+        <v>2050.48155539346</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000008798e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>-48.93478791313917</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = -1.148x + 2697.432</t>
-        </is>
+      <c r="W18" t="n">
+        <v>-1.14772750959925</v>
       </c>
       <c r="X18" t="n">
         <v>2697.432087641368</v>
@@ -3336,7 +3240,7 @@
         <v>107.908199366633</v>
       </c>
       <c r="Z18" t="n">
-        <v>120.04</v>
+        <v>2143.401149902774</v>
       </c>
       <c r="AA18" t="n">
         <v>1.645355878914446e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>-74.31068098453683</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = -3.560x + 7086.760</t>
-        </is>
+      <c r="W19" t="n">
+        <v>-3.56016083577585</v>
       </c>
       <c r="X19" t="n">
         <v>7086.759727820572</v>
@@ -3388,7 +3290,7 @@
         <v>7.107918707631474e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>112.6799999999998</v>
+        <v>2011.351659247111</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>-74.92991744729504</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = -3.714x + 7303.129</t>
-        </is>
+      <c r="W20" t="n">
+        <v>-3.713874024733899</v>
       </c>
       <c r="X20" t="n">
         <v>7303.129144768417</v>
@@ -3440,7 +3340,7 @@
         <v>1.847758214541238e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>110.6900000000001</v>
+        <v>1991.949668606389</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>-74.68593886394015</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = -3.652x + 7082.456</t>
-        </is>
+      <c r="W21" t="n">
+        <v>-3.651862930883819</v>
       </c>
       <c r="X21" t="n">
         <v>7082.456086213839</v>
@@ -3492,7 +3390,7 @@
         <v>3.178067897774014e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>114.77</v>
+        <v>1972.547613987283</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>-77.55052566930308</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = -4.530x + 8562.697</t>
-        </is>
+      <c r="W22" t="n">
+        <v>-4.529607859471222</v>
       </c>
       <c r="X22" t="n">
         <v>8562.696830682264</v>
@@ -3544,7 +3440,7 @@
         <v>8.129758966349955e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>112.3499999999999</v>
+        <v>1952.730681313109</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.16452626865906</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.785x + -25281.559</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.784558052165991</v>
       </c>
       <c r="X2" t="n">
         <v>-25281.55929627744</v>
@@ -3742,7 +3636,7 @@
         <v>7.868591856394237e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>263.0700000000002</v>
+        <v>2873.051711335656</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000338e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.8553839247722</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.800x + -31411.764</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.80002561372089</v>
       </c>
       <c r="X3" t="n">
         <v>-31411.76374128252</v>
@@ -3794,7 +3686,7 @@
         <v>7.386941090141653e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>143.1900000000001</v>
+        <v>2576.664866082346</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000031913e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.02398593840023</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.485x + -25036.399</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.48542876141742</v>
       </c>
       <c r="X4" t="n">
         <v>-25036.39938591619</v>
@@ -3846,7 +3736,7 @@
         <v>6.67126040680553e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>143.3899999999999</v>
+        <v>2500.221549416978</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>84.92742135131648</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.266x + -24126.267</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.26567136449748</v>
       </c>
       <c r="X5" t="n">
         <v>-24126.26652424969</v>
@@ -3898,7 +3786,7 @@
         <v>4.589610258755812e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>132.3599999999997</v>
+        <v>2459.790101126679</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000036e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>84.07790794279029</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.640x + -20255.639</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.640444233848433</v>
       </c>
       <c r="X6" t="n">
         <v>-20255.63900181402</v>
@@ -3950,7 +3836,7 @@
         <v>2.359960949912924e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>127.7199999999998</v>
+        <v>2426.847221845132</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>83.02287756366351</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 8.171x + -16838.398</t>
-        </is>
+      <c r="W7" t="n">
+        <v>8.171318407695193</v>
       </c>
       <c r="X7" t="n">
         <v>-16838.39833609839</v>
@@ -4002,7 +3886,7 @@
         <v>3.760370553760807e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>133.1899999999996</v>
+        <v>2396.315984342618</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>81.63012528882994</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.797x + -13700.943</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.796712991659272</v>
       </c>
       <c r="X8" t="n">
         <v>-13700.94313990342</v>
@@ -4054,7 +3936,7 @@
         <v>4.846590310715652e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>124.3500000000004</v>
+        <v>2366.057565798163</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000005845e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>80.90383505785877</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.246x + -12385.145</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.245885605420618</v>
       </c>
       <c r="X9" t="n">
         <v>-12385.14499795848</v>
@@ -4106,7 +3986,7 @@
         <v>3.821215079699915e-13</v>
       </c>
       <c r="Z9" t="n">
-        <v>129.1900000000001</v>
+        <v>2336.223801284917</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>73.92006560510514</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 3.469x + -6457.358</t>
-        </is>
+      <c r="W10" t="n">
+        <v>3.469140709124173</v>
       </c>
       <c r="X10" t="n">
         <v>-6457.358030293683</v>
@@ -4158,7 +4036,7 @@
         <v>1.885640927781418e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>120.5199999999998</v>
+        <v>2308.217256683847</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000305e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>78.28458178914315</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 4.822x + -9193.046</t>
-        </is>
+      <c r="W11" t="n">
+        <v>4.822282046526968</v>
       </c>
       <c r="X11" t="n">
         <v>-9193.045938178606</v>
@@ -4210,7 +4086,7 @@
         <v>1.555662023802641e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>129.4500000000003</v>
+        <v>2280.936781745298</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.0078829532745</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.448x + -25270.975</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.4481931601502</v>
       </c>
       <c r="X2" t="n">
         <v>-25270.9745077079</v>
@@ -4408,7 +4282,7 @@
         <v>8.309946678020667e-13</v>
       </c>
       <c r="Z2" t="n">
-        <v>204.7799999999997</v>
+        <v>2485.610650043614</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.44063142246873</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.540x + -26112.598</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.54006748820524</v>
       </c>
       <c r="X3" t="n">
         <v>-26112.59757183991</v>
@@ -4460,7 +4332,7 @@
         <v>5.073045540896301e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>142.29</v>
+        <v>2372.172733323586</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>85.26229246737196</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.066x + -24600.018</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.06599072710019</v>
       </c>
       <c r="X4" t="n">
         <v>-24600.01779766982</v>
@@ -4512,7 +4382,7 @@
         <v>3.824996657782406e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>134.6900000000003</v>
+        <v>2331.549221204692</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>84.63861690599957</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.656x + -21330.647</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.65554400894035</v>
       </c>
       <c r="X5" t="n">
         <v>-21330.64729598035</v>
@@ -4564,7 +4432,7 @@
         <v>1.555386667669817e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>137.0199999999998</v>
+        <v>2299.858461579325</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001449e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>84.47579681114158</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.340x + -20424.201</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.33961419755706</v>
       </c>
       <c r="X6" t="n">
         <v>-20424.20110545467</v>
@@ -4616,7 +4482,7 @@
         <v>3.109190749550578e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>126.8599999999999</v>
+        <v>2270.18104004765</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001782e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>84.12649034663309</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.721x + -18922.248</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.720753047561018</v>
       </c>
       <c r="X7" t="n">
         <v>-18922.24803844098</v>
@@ -4668,7 +4532,7 @@
         <v>3.549341362568593e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>120.3499999999999</v>
+        <v>2241.100628829656</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000012e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>83.35567793304396</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 8.585x + -16423.551</t>
-        </is>
+      <c r="W8" t="n">
+        <v>8.584579653801629</v>
       </c>
       <c r="X8" t="n">
         <v>-16423.55133321817</v>
@@ -4720,7 +4582,7 @@
         <v>1.402424305082267e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>125.47</v>
+        <v>2212.917017104517</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000056e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>82.87607870025458</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 8.001x + -15080.722</t>
-        </is>
+      <c r="W9" t="n">
+        <v>8.00124248383432</v>
       </c>
       <c r="X9" t="n">
         <v>-15080.72249101161</v>
@@ -4772,7 +4632,7 @@
         <v>2.053972134084737e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>127.28</v>
+        <v>2186.593551621414</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>81.62960740627466</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 6.796x + -12558.127</t>
-        </is>
+      <c r="W10" t="n">
+        <v>6.796286431008581</v>
       </c>
       <c r="X10" t="n">
         <v>-12558.12680005444</v>
@@ -4824,7 +4682,7 @@
         <v>1.260525917041039e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>120.25</v>
+        <v>2162.173723793554</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000203e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>80.64484665020996</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 6.070x + -11034.925</t>
-        </is>
+      <c r="W11" t="n">
+        <v>6.069992211960154</v>
       </c>
       <c r="X11" t="n">
         <v>-11034.92547586477</v>
@@ -4876,7 +4732,7 @@
         <v>4.567745128575015e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>123.72</v>
+        <v>2138.299674143591</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000022e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>80.25023565861777</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 5.820x + -10454.226</t>
-        </is>
+      <c r="W12" t="n">
+        <v>5.819800615889765</v>
       </c>
       <c r="X12" t="n">
         <v>-10454.22567970742</v>
@@ -4928,7 +4782,7 @@
         <v>2.389039415977951e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>126.5799999999999</v>
+        <v>2115.391337621069</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000225e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>69.02407399548717</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 2.608x + -4258.023</t>
-        </is>
+      <c r="W13" t="n">
+        <v>2.608364302778769</v>
       </c>
       <c r="X13" t="n">
         <v>-4258.023366482982</v>
@@ -4980,7 +4832,7 @@
         <v>5.155813984957102e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>114.27</v>
+        <v>2092.927651858601</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000008e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>75.9714115717095</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 4.002x + -6855.007</t>
-        </is>
+      <c r="W14" t="n">
+        <v>4.002272510476752</v>
       </c>
       <c r="X14" t="n">
         <v>-6855.007206655303</v>
@@ -5032,7 +4882,7 @@
         <v>5.822896123862566e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>121.25</v>
+        <v>2071.226138550229</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>43.8615558925129</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 0.961x + -1115.675</t>
-        </is>
+      <c r="W15" t="n">
+        <v>0.9610299937090596</v>
       </c>
       <c r="X15" t="n">
         <v>-1115.674699726089</v>
@@ -5084,7 +4932,7 @@
         <v>5.04175754828238e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>111.6500000000001</v>
+        <v>2050.369855721834</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>63.04135340473545</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 1.966x + -3000.044</t>
-        </is>
+      <c r="W16" t="n">
+        <v>1.966117303975074</v>
       </c>
       <c r="X16" t="n">
         <v>-3000.043639337012</v>
@@ -5136,7 +4982,7 @@
         <v>5.892824235530616e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>119.8300000000002</v>
+        <v>2029.181306073275</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>45.43448501065251</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 1.015x + -1248.499</t>
-        </is>
+      <c r="W17" t="n">
+        <v>1.015282571619792</v>
       </c>
       <c r="X17" t="n">
         <v>-1248.498711361743</v>
@@ -5188,7 +5032,7 @@
         <v>1.240231171114659e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>117.21</v>
+        <v>2008.1894650394</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>-72.92742366345705</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = -3.256x + 6505.741</t>
-        </is>
+      <c r="W18" t="n">
+        <v>-3.256095338395242</v>
       </c>
       <c r="X18" t="n">
         <v>6505.740889531367</v>
@@ -5240,7 +5082,7 @@
         <v>465.5936907559623</v>
       </c>
       <c r="Z18" t="n">
-        <v>104.8700000000001</v>
+        <v>1743.016283833224</v>
       </c>
       <c r="AA18" t="n">
         <v>1.988629627763726e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>-30.26983426558344</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = -0.584x + 1616.698</t>
-        </is>
+      <c r="W19" t="n">
+        <v>-0.5836467645861675</v>
       </c>
       <c r="X19" t="n">
         <v>1616.698489650714</v>
@@ -5292,7 +5132,7 @@
         <v>5.787366203060401e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>113.1200000000001</v>
+        <v>1967.176560805307</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>-74.38969936980901</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = -3.579x + 6905.370</t>
-        </is>
+      <c r="W20" t="n">
+        <v>-3.579113167266549</v>
       </c>
       <c r="X20" t="n">
         <v>6905.369524495869</v>
@@ -5344,7 +5182,7 @@
         <v>1.102194484601837e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>106.8999999999999</v>
+        <v>1947.229307023899</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>-76.43617560078853</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = -4.145x + 7829.007</t>
-        </is>
+      <c r="W21" t="n">
+        <v>-4.144953568440815</v>
       </c>
       <c r="X21" t="n">
         <v>7829.0071820168</v>
@@ -5396,7 +5232,7 @@
         <v>6.799349272414639e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>106.3899999999999</v>
+        <v>1927.511229689941</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>-76.73571255951464</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = -4.242x + 7876.848</t>
-        </is>
+      <c r="W22" t="n">
+        <v>-4.242106379727296</v>
       </c>
       <c r="X22" t="n">
         <v>7876.847570079973</v>
@@ -5448,7 +5282,7 @@
         <v>3.579989602858862e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>108.8399999999999</v>
+        <v>1907.721475918999</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.68508640050176</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.036x + -21927.340</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.036321548134451</v>
       </c>
       <c r="X2" t="n">
         <v>-21927.33982403725</v>
@@ -5646,7 +5478,7 @@
         <v>1.531754418550794e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>292.1700000000001</v>
+        <v>2682.331075286985</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000009e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.49846534058848</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.702x + -27183.681</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.70185507930735</v>
       </c>
       <c r="X3" t="n">
         <v>-27183.68093179626</v>
@@ -5698,7 +5528,7 @@
         <v>9.567543483768303e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>166.9500000000003</v>
+        <v>2418.552936682619</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000131e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.00571262187555</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.443x + -23542.616</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.44319292846364</v>
       </c>
       <c r="X4" t="n">
         <v>-23542.6158993587</v>
@@ -5750,7 +5578,7 @@
         <v>1.414655296836617e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>145.3099999999999</v>
+        <v>2351.00434950218</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001422e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>84.95371298669677</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.325x + -22889.888</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.32467361721992</v>
       </c>
       <c r="X5" t="n">
         <v>-22889.88801247129</v>
@@ -5802,7 +5628,7 @@
         <v>2.074252383869141e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>134.6100000000001</v>
+        <v>2311.64343558264</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000516e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>84.39779243039936</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.195x + -20227.348</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.19474436953413</v>
       </c>
       <c r="X6" t="n">
         <v>-20227.34755178795</v>
@@ -5854,7 +5678,7 @@
         <v>1.219845479983952e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>131.2200000000003</v>
+        <v>2277.875356554868</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001422e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>83.36981504542359</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 8.603x + -16713.459</t>
-        </is>
+      <c r="W7" t="n">
+        <v>8.603048958290429</v>
       </c>
       <c r="X7" t="n">
         <v>-16713.45949904044</v>
@@ -5906,7 +5728,7 @@
         <v>1.954266480573372e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>134.5200000000002</v>
+        <v>2245.355227051818</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000009e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>82.67269415750867</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 7.777x + -14842.733</t>
-        </is>
+      <c r="W8" t="n">
+        <v>7.776812830372212</v>
       </c>
       <c r="X8" t="n">
         <v>-14842.73348834367</v>
@@ -5958,7 +5778,7 @@
         <v>3.495896350373366e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>130.25</v>
+        <v>2214.379935668665</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000007262e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>81.59169219635113</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.765x + -12651.224</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.765198806685627</v>
       </c>
       <c r="X9" t="n">
         <v>-12651.22439576775</v>
@@ -6010,7 +5828,7 @@
         <v>4.516199958612458e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>130.0600000000002</v>
+        <v>2184.161441616359</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002123e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>79.62069416838311</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.460x + -9955.161</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.459676907538616</v>
       </c>
       <c r="X10" t="n">
         <v>-9955.161489567143</v>
@@ -6062,7 +5878,7 @@
         <v>3.243334346150276e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>127.1099999999999</v>
+        <v>2155.090664404788</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>75.1224995448122</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 3.764x + -6556.328</t>
-        </is>
+      <c r="W11" t="n">
+        <v>3.76422437885523</v>
       </c>
       <c r="X11" t="n">
         <v>-6556.328123392039</v>
@@ -6114,7 +5928,7 @@
         <v>2.59161761483623e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>120.49</v>
+        <v>2127.584134469996</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000035e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.25101179123476</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.037x + -26266.441</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.03719813107754</v>
       </c>
       <c r="X2" t="n">
         <v>-26266.44067188984</v>
@@ -6312,7 +6124,7 @@
         <v>7.81803029116612e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>194.3999999999996</v>
+        <v>2450.505382732978</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>84.98704961183948</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.400x + -23409.503</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.40037341705818</v>
       </c>
       <c r="X3" t="n">
         <v>-23409.50289409664</v>
@@ -6364,7 +6174,7 @@
         <v>3.085923516628149e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>146.3099999999999</v>
+        <v>2347.688636653309</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000184e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>84.82604301641445</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.044x + -22255.775</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.04376290704604</v>
       </c>
       <c r="X4" t="n">
         <v>-22255.7748838759</v>
@@ -6416,7 +6224,7 @@
         <v>3.265186523582785e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>134.1599999999999</v>
+        <v>2309.481426074799</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>84.20005825457285</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.845x + -19500.892</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.844916128231484</v>
       </c>
       <c r="X5" t="n">
         <v>-19500.89224602438</v>
@@ -6468,7 +6274,7 @@
         <v>4.073219316667966e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>131.1099999999999</v>
+        <v>2279.789276511653</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>83.72363765750833</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.092x + -17734.641</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.092275950907407</v>
       </c>
       <c r="X6" t="n">
         <v>-17734.64062313891</v>
@@ -6520,7 +6324,7 @@
         <v>2.298161265587734e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>123.5</v>
+        <v>2251.031850161536</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003917e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>82.91530875048139</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 8.046x + -15418.210</t>
-        </is>
+      <c r="W7" t="n">
+        <v>8.046006418355486</v>
       </c>
       <c r="X7" t="n">
         <v>-15418.20997681798</v>
@@ -6572,7 +6374,7 @@
         <v>3.042972965399277e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>133.1500000000001</v>
+        <v>2222.276373719201</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000002e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>81.82888160635306</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 6.964x + -13086.260</t>
-        </is>
+      <c r="W8" t="n">
+        <v>6.964385214785362</v>
       </c>
       <c r="X8" t="n">
         <v>-13086.25996492417</v>
@@ -6624,7 +6424,7 @@
         <v>7.933617990239786e-13</v>
       </c>
       <c r="Z8" t="n">
-        <v>125.3800000000001</v>
+        <v>2194.046159524713</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>81.29782815404234</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.533x + -12093.728</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.533372937607274</v>
       </c>
       <c r="X9" t="n">
         <v>-12093.72838407259</v>
@@ -6676,7 +6474,7 @@
         <v>4.263239373616513e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>128.3900000000001</v>
+        <v>2166.462163373291</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000004362e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>80.23500153666801</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.811x + -10551.161</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.810543488692669</v>
       </c>
       <c r="X10" t="n">
         <v>-10551.16107144091</v>
@@ -6728,7 +6524,7 @@
         <v>3.740060517801523e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.3399999999999</v>
+        <v>2139.724830477282</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>78.01720259259039</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 4.712x + -8339.407</t>
-        </is>
+      <c r="W11" t="n">
+        <v>4.711585593391511</v>
       </c>
       <c r="X11" t="n">
         <v>-8339.406866685262</v>
@@ -6780,7 +6574,7 @@
         <v>2.888759237023528e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>125.4199999999998</v>
+        <v>2114.494610485073</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>75.25192574559955</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 3.799x + -6528.485</t>
-        </is>
+      <c r="W12" t="n">
+        <v>3.798784631991308</v>
       </c>
       <c r="X12" t="n">
         <v>-6528.484747240417</v>
@@ -6832,7 +6624,7 @@
         <v>1.693809161777374e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>121.98</v>
+        <v>2090.244748072032</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000001333e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>71.39174275552924</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 2.970x + -4907.951</t>
-        </is>
+      <c r="W13" t="n">
+        <v>2.970023898174118</v>
       </c>
       <c r="X13" t="n">
         <v>-4907.951170024037</v>
@@ -6884,7 +6674,7 @@
         <v>3.391034973962976e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>120.1899999999998</v>
+        <v>2066.446967194479</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000208e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>68.20342119189704</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 2.501x + -4011.885</t>
-        </is>
+      <c r="W14" t="n">
+        <v>2.500611385362059</v>
       </c>
       <c r="X14" t="n">
         <v>-4011.884611853175</v>
@@ -6936,7 +6724,7 @@
         <v>7.300316489939316e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>123.7</v>
+        <v>2044.275253061377</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000009e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>54.84148549150882</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 1.420x + -2001.452</t>
-        </is>
+      <c r="W15" t="n">
+        <v>1.419771704861776</v>
       </c>
       <c r="X15" t="n">
         <v>-2001.451557276632</v>
@@ -6988,7 +6774,7 @@
         <v>1.191286456926767e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>122.9000000000001</v>
+        <v>2022.474701616153</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>-23.63536197186177</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = -0.438x + 1401.696</t>
-        </is>
+      <c r="W16" t="n">
+        <v>-0.4376244417697306</v>
       </c>
       <c r="X16" t="n">
         <v>1401.696019463868</v>
@@ -7040,7 +6824,7 @@
         <v>5.182612958551111e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>115.8800000000001</v>
+        <v>2000.97871736425</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>-36.01505624880785</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = -0.727x + 1872.911</t>
-        </is>
+      <c r="W17" t="n">
+        <v>-0.7269440984999576</v>
       </c>
       <c r="X17" t="n">
         <v>1872.9110975536</v>
@@ -7092,7 +6874,7 @@
         <v>4.711685474233437e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>118.29</v>
+        <v>1979.544298344718</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>-68.81653130893991</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = -2.580x + 5169.995</t>
-        </is>
+      <c r="W18" t="n">
+        <v>-2.580361879013001</v>
       </c>
       <c r="X18" t="n">
         <v>5169.994898817462</v>
@@ -7144,7 +6924,7 @@
         <v>2.799914322032931e-11</v>
       </c>
       <c r="Z18" t="n">
-        <v>112.3800000000001</v>
+        <v>1958.74119708094</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>-74.81551650009332</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = -3.685x + 7053.335</t>
-        </is>
+      <c r="W19" t="n">
+        <v>-3.684554891064483</v>
       </c>
       <c r="X19" t="n">
         <v>7053.334562523114</v>
@@ -7196,7 +6974,7 @@
         <v>5.688386246057792e-12</v>
       </c>
       <c r="Z19" t="n">
-        <v>110.7800000000002</v>
+        <v>1937.588282522877</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>-78.03794608922435</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = -4.720x + 8779.037</t>
-        </is>
+      <c r="W20" t="n">
+        <v>-4.719998978962239</v>
       </c>
       <c r="X20" t="n">
         <v>8779.037450271646</v>
@@ -7248,7 +7024,7 @@
         <v>6.76441651384682e-12</v>
       </c>
       <c r="Z20" t="n">
-        <v>107.99</v>
+        <v>1916.581456870169</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>-76.73231190597836</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = -4.241x + 7825.692</t>
-        </is>
+      <c r="W21" t="n">
+        <v>-4.240979233174182</v>
       </c>
       <c r="X21" t="n">
         <v>7825.69187997649</v>
@@ -7300,7 +7074,7 @@
         <v>461.2513999276247</v>
       </c>
       <c r="Z21" t="n">
-        <v>112.01</v>
+        <v>1696.838879881661</v>
       </c>
       <c r="AA21" t="n">
         <v>1.754721301734316e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>74.49474938169908</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 3.605x + -5830.555</t>
-        </is>
+      <c r="W22" t="n">
+        <v>3.604600745001127</v>
       </c>
       <c r="X22" t="n">
         <v>-5830.555360614539</v>
@@ -7352,7 +7124,7 @@
         <v>8.467865674446815e-11</v>
       </c>
       <c r="Z22" t="n">
-        <v>108.73</v>
+        <v>1875.43471340691</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.96946972824345</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.466x + -22388.803</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.465842002254481</v>
       </c>
       <c r="X2" t="n">
         <v>-22388.80319877982</v>
@@ -7550,7 +7320,7 @@
         <v>1.040828909659335e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>289.4000000000001</v>
+        <v>2591.399615200155</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000005124e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.53954779932567</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.819x + -26396.609</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.81932459788951</v>
       </c>
       <c r="X3" t="n">
         <v>-26396.60937732317</v>
@@ -7602,7 +7370,7 @@
         <v>3.883353722665607e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>143.6699999999996</v>
+        <v>2321.20835883814</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000022e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.04865534310625</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.543x + -22842.830</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.54294140083858</v>
       </c>
       <c r="X4" t="n">
         <v>-22842.82970925371</v>
@@ -7654,7 +7420,7 @@
         <v>1.410196628143468e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>129.95</v>
+        <v>2253.115139858811</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>83.52834704789227</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 8.816x + -16938.416</t>
-        </is>
+      <c r="W5" t="n">
+        <v>8.815662882784993</v>
       </c>
       <c r="X5" t="n">
         <v>-16938.41615410658</v>
@@ -7706,7 +7470,7 @@
         <v>1.355990394307768e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>124.6900000000001</v>
+        <v>2213.466860077176</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000068331e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>81.98602521586047</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 7.103x + -13298.135</t>
-        </is>
+      <c r="W6" t="n">
+        <v>7.102799040974584</v>
       </c>
       <c r="X6" t="n">
         <v>-13298.13547812229</v>
@@ -7758,7 +7520,7 @@
         <v>1.743619582382439e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>127.71</v>
+        <v>2179.268045470058</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000063e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>79.93270674439823</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.633x + -10260.825</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.632589437901719</v>
       </c>
       <c r="X7" t="n">
         <v>-10260.82528673172</v>
@@ -7810,7 +7570,7 @@
         <v>2.470805315339147e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>129.21</v>
+        <v>2146.054531081825</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000087e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>76.96888144100916</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 4.321x + -7605.695</t>
-        </is>
+      <c r="W8" t="n">
+        <v>4.320768072165426</v>
       </c>
       <c r="X8" t="n">
         <v>-7605.695436689388</v>
@@ -7862,7 +7620,7 @@
         <v>9.780358642101849e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>129.9200000000001</v>
+        <v>2114.055675517818</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000025e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>72.80696309005485</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 3.232x + -5445.027</t>
-        </is>
+      <c r="W9" t="n">
+        <v>3.231868389029313</v>
       </c>
       <c r="X9" t="n">
         <v>-5445.0274526308</v>
@@ -7914,7 +7670,7 @@
         <v>3.73992650562642e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>126.51</v>
+        <v>2082.746494416246</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002658e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>60.86448546867136</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 1.794x + -2702.963</t>
-        </is>
+      <c r="W10" t="n">
+        <v>1.794027646419339</v>
       </c>
       <c r="X10" t="n">
         <v>-2702.963308183399</v>
@@ -7966,7 +7720,7 @@
         <v>5.498870308889907e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>123.48</v>
+        <v>2053.725834070181</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>-18.15268803265198</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = -0.328x + 1256.842</t>
-        </is>
+      <c r="W11" t="n">
+        <v>-0.3278685073504194</v>
       </c>
       <c r="X11" t="n">
         <v>1256.841685910484</v>
@@ -8018,7 +7770,7 @@
         <v>2.863599503820712e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>113.9299999999998</v>
+        <v>2026.031721643197</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005478e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.38198389171703</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.380x + -26828.378</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.38013344779855</v>
       </c>
       <c r="X2" t="n">
         <v>-26828.37751742029</v>
@@ -8216,7 +7966,7 @@
         <v>2.945528969817851e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.5799999999999</v>
+        <v>2424.07613736572</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000125e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>84.91485694832897</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.238x + -22740.029</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.23768990782095</v>
       </c>
       <c r="X3" t="n">
         <v>-22740.02872814703</v>
@@ -8268,7 +8016,7 @@
         <v>1.667653178952902e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>138.9600000000003</v>
+        <v>2308.935672098836</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000033749e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>84.33357356445418</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.078x + -19956.310</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.07846112782562</v>
       </c>
       <c r="X4" t="n">
         <v>-19956.30977812716</v>
@@ -8320,7 +8066,7 @@
         <v>1.462409081477049e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>131.79</v>
+        <v>2271.735300960781</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>83.91562640302743</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.381x + -18308.841</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.381449906243233</v>
       </c>
       <c r="X5" t="n">
         <v>-18308.84051384599</v>
@@ -8372,7 +8116,7 @@
         <v>5.617557587630218e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>132.6400000000001</v>
+        <v>2245.239778973065</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000057e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>83.42670931435386</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 8.678x + -16694.666</t>
-        </is>
+      <c r="W6" t="n">
+        <v>8.678177576855584</v>
       </c>
       <c r="X6" t="n">
         <v>-16694.66620275111</v>
@@ -8424,7 +8166,7 @@
         <v>1.437707714253742e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>134.76</v>
+        <v>2219.411129374885</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>82.57540916369737</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 7.674x + -14521.805</t>
-        </is>
+      <c r="W7" t="n">
+        <v>7.673785607154372</v>
       </c>
       <c r="X7" t="n">
         <v>-14521.8051493096</v>
@@ -8476,7 +8216,7 @@
         <v>1.787847203415164e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>127.6500000000001</v>
+        <v>2194.750305082619</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>81.99637270391783</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 7.112x + -13269.737</t>
-        </is>
+      <c r="W8" t="n">
+        <v>7.112102684443761</v>
       </c>
       <c r="X8" t="n">
         <v>-13269.73746493533</v>
@@ -8528,7 +8266,7 @@
         <v>4.502112230666082e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>125.3400000000001</v>
+        <v>2171.177977453772</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>80.72897074396093</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.126x + -11214.572</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.126057264935233</v>
       </c>
       <c r="X9" t="n">
         <v>-11214.57245444018</v>
@@ -8580,7 +8316,7 @@
         <v>1.176966877862571e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>124.25</v>
+        <v>2148.020677728776</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000972e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>79.52783502169258</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 5.410x + -9725.398</t>
-        </is>
+      <c r="W10" t="n">
+        <v>5.410184223599325</v>
       </c>
       <c r="X10" t="n">
         <v>-9725.398204445482</v>
@@ -8632,7 +8366,7 @@
         <v>2.287214376077713e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>122.25</v>
+        <v>2126.353981522449</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000074e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>78.76880552389031</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.036x + -8935.459</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.035977400135164</v>
       </c>
       <c r="X11" t="n">
         <v>-8935.4587760678</v>
@@ -8684,7 +8416,7 @@
         <v>4.291454818469938e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>126.9000000000001</v>
+        <v>2105.199455352495</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000004e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>73.43323657420989</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 3.362x + -5674.162</t>
-        </is>
+      <c r="W12" t="n">
+        <v>3.36155452585845</v>
       </c>
       <c r="X12" t="n">
         <v>-5674.162228133481</v>
@@ -8736,7 +8466,7 @@
         <v>2.966514247220899e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>116.55</v>
+        <v>2084.414270177135</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000003e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>72.71956515545914</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 3.214x + -5368.021</t>
-        </is>
+      <c r="W13" t="n">
+        <v>3.214496065197946</v>
       </c>
       <c r="X13" t="n">
         <v>-5368.021292083731</v>
@@ -8788,7 +8516,7 @@
         <v>1.083413885404588e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>121.25</v>
+        <v>2064.244919235202</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000098e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>74.58429760798448</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 3.627x + -6107.819</t>
-        </is>
+      <c r="W14" t="n">
+        <v>3.626594717795229</v>
       </c>
       <c r="X14" t="n">
         <v>-6107.818877749405</v>
@@ -8840,7 +8566,7 @@
         <v>7.927002076461528e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>130.97</v>
+        <v>2044.298649405384</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>65.83595470154087</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 2.229x + -3482.672</t>
-        </is>
+      <c r="W15" t="n">
+        <v>2.228840598736393</v>
       </c>
       <c r="X15" t="n">
         <v>-3482.671990874283</v>
@@ -8892,7 +8616,7 @@
         <v>1.076747928480313e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>125.5900000000001</v>
+        <v>2024.673744779838</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000794e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>27.52461027105345</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 0.521x + -328.387</t>
-        </is>
+      <c r="W16" t="n">
+        <v>0.5211131013699194</v>
       </c>
       <c r="X16" t="n">
         <v>-328.387019495245</v>
@@ -8944,7 +8666,7 @@
         <v>3.279216371395521e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>118.8500000000001</v>
+        <v>2005.24249818509</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000003e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>-17.26249288163301</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = -0.311x + 1172.470</t>
-        </is>
+      <c r="W17" t="n">
+        <v>-0.3107473341642026</v>
       </c>
       <c r="X17" t="n">
         <v>1172.469699247953</v>
@@ -8996,7 +8716,7 @@
         <v>1.944392334971067e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>116.8700000000001</v>
+        <v>1985.935182710915</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>45.25799158971661</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 1.009x + -1235.475</t>
-        </is>
+      <c r="W18" t="n">
+        <v>1.009046400662567</v>
       </c>
       <c r="X18" t="n">
         <v>-1235.474705142059</v>
@@ -9048,7 +8766,7 @@
         <v>4.268326875040545e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>124.8700000000001</v>
+        <v>1966.762201431688</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>-64.57295199316155</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = -2.103x + 4320.004</t>
-        </is>
+      <c r="W19" t="n">
+        <v>-2.103431817874846</v>
       </c>
       <c r="X19" t="n">
         <v>4320.004066215066</v>
@@ -9100,7 +8816,7 @@
         <v>8.512479130005232e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>113.6299999999999</v>
+        <v>1947.623851993005</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>-59.11177625396401</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = -1.672x + 3490.251</t>
-        </is>
+      <c r="W20" t="n">
+        <v>-1.6716578646309</v>
       </c>
       <c r="X20" t="n">
         <v>3490.250535860603</v>
@@ -9152,7 +8866,7 @@
         <v>2.177546872564243e-12</v>
       </c>
       <c r="Z20" t="n">
-        <v>118.5</v>
+        <v>1928.492748216604</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>-75.71666965056761</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = -3.928x + 7403.073</t>
-        </is>
+      <c r="W21" t="n">
+        <v>-3.927930591105219</v>
       </c>
       <c r="X21" t="n">
         <v>7403.073278594797</v>
@@ -9204,7 +8916,7 @@
         <v>2.291644411025263e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>111.27</v>
+        <v>1909.218863983835</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>-73.08906196034226</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = -3.289x + 6199.558</t>
-        </is>
+      <c r="W22" t="n">
+        <v>-3.289129958966575</v>
       </c>
       <c r="X22" t="n">
         <v>6199.55822260074</v>
@@ -9256,7 +8966,7 @@
         <v>4.590795143356186e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>114.78</v>
+        <v>1890.459693166599</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.02635672175349</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.557x + -18661.780</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.556651234098043</v>
       </c>
       <c r="X2" t="n">
         <v>-18661.78018724119</v>
@@ -9454,7 +9162,7 @@
         <v>3.131801177028946e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>275.71</v>
+        <v>2112.413326485524</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>85.37214446279282</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.354x + -20851.079</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.35369719285699</v>
       </c>
       <c r="X3" t="n">
         <v>-20851.07949251159</v>
@@ -9506,7 +9212,7 @@
         <v>2.400859152752665e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>135.3199999999999</v>
+        <v>1895.102039855793</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>84.37694364448107</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.157x + -16414.504</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.15670254258108</v>
       </c>
       <c r="X4" t="n">
         <v>-16414.50398004065</v>
@@ -9558,7 +9262,7 @@
         <v>7.260402274030566e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>127.1199999999999</v>
+        <v>1839.135513088014</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001192e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>83.13626690366171</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 8.308x + -13082.172</t>
-        </is>
+      <c r="W5" t="n">
+        <v>8.307641982282108</v>
       </c>
       <c r="X5" t="n">
         <v>-13082.17204302591</v>
@@ -9610,7 +9312,7 @@
         <v>3.602179346621871e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>122.79</v>
+        <v>1806.943526198307</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000005129e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>81.33681676392436</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 6.563x + -10050.725</t>
-        </is>
+      <c r="W6" t="n">
+        <v>6.563232418309902</v>
       </c>
       <c r="X6" t="n">
         <v>-10050.72522303196</v>
@@ -9662,7 +9362,7 @@
         <v>2.346683637406767</v>
       </c>
       <c r="Z6" t="n">
-        <v>111.28</v>
+        <v>1907.220431516589</v>
       </c>
       <c r="AA6" t="n">
         <v>1.51883301213593e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>80.50229486478456</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.977x + -8986.067</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.977235050476501</v>
       </c>
       <c r="X7" t="n">
         <v>-8986.067495305362</v>
@@ -9714,7 +9412,7 @@
         <v>2.732442839492702e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>118.3499999999999</v>
+        <v>1751.145691773412</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000063e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>78.18563593405783</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 4.781x + -6965.624</t>
-        </is>
+      <c r="W8" t="n">
+        <v>4.780742256901767</v>
       </c>
       <c r="X8" t="n">
         <v>-6965.624355708699</v>
@@ -9766,7 +9462,7 @@
         <v>1.958784315320988e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.73</v>
+        <v>1723.454014588223</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000039e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>74.6982300161572</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 3.655x + -5118.323</t>
-        </is>
+      <c r="W9" t="n">
+        <v>3.654940738289015</v>
       </c>
       <c r="X9" t="n">
         <v>-5118.32328526468</v>
@@ -9818,7 +9512,7 @@
         <v>6.300005257000134e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>110.6699999999998</v>
+        <v>1696.018140351011</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>71.57503328686998</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 3.002x + -4046.337</t>
-        </is>
+      <c r="W10" t="n">
+        <v>3.001743117900863</v>
       </c>
       <c r="X10" t="n">
         <v>-4046.337269879557</v>
@@ -9870,7 +9562,7 @@
         <v>3.736013423185014e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>109.6600000000001</v>
+        <v>1670.48590028759</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>62.55343621990598</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 1.925x + -2373.948</t>
-        </is>
+      <c r="W11" t="n">
+        <v>1.925364211937832</v>
       </c>
       <c r="X11" t="n">
         <v>-2373.947858626498</v>
@@ -9922,7 +9612,7 @@
         <v>4.893808886928976e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>106.6600000000001</v>
+        <v>1646.944710328125</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000007e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-104.5999999999999</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-81.90000000000009</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-77.73000000000025</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-71.15999999999985</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-70.27999999999997</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-58.00999999999999</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-46.70999999999981</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-51.35000000000014</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-48.05999999999995</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-37.72000000000003</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-263.0700000000002</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-143.1900000000001</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-118.27</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-93.33999999999969</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-76.90999999999985</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-74.12999999999965</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-60.10000000000036</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-61.01999999999998</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-44.8599999999999</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-53.12000000000012</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-292.1700000000001</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-166.9500000000003</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-132.9700000000003</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-102.9400000000001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-86.97000000000025</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-80.40000000000009</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-69.32000000000016</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-64.16000000000008</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-54.83999999999992</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-44.71000000000004</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-289.4000000000001</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-143.6699999999996</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-94.08999999999992</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-69.83999999999992</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-63.00999999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-55.33999999999992</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-50.75</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-43.14999999999986</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-35.37999999999988</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-23.38999999999987</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-275.71</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-128.76</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-85.8599999999999</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-67.93000000000006</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-48.96000000000004</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-50.62999999999988</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-42.43000000000006</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-35.94000000000005</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-34.09000000000015</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-28.01999999999998</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-104.5999999999999</v>
+        <v>1740.956</v>
       </c>
       <c r="D2" t="n">
         <v>3.17859e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-81.90000000000009</v>
+        <v>1704.67</v>
       </c>
       <c r="D3" t="n">
         <v>3.21029e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-77.73000000000025</v>
+        <v>1660.337</v>
       </c>
       <c r="D4" t="n">
         <v>3.23599e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-71.15999999999985</v>
+        <v>1625.349</v>
       </c>
       <c r="D5" t="n">
         <v>3.25831e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-70.27999999999997</v>
+        <v>1587.723</v>
       </c>
       <c r="D6" t="n">
         <v>3.28003e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-58.00999999999999</v>
+        <v>1567.936</v>
       </c>
       <c r="D7" t="n">
         <v>3.29857e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-46.70999999999981</v>
+        <v>1549.315</v>
       </c>
       <c r="D8" t="n">
         <v>3.31574e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-51.35000000000014</v>
+        <v>1513.606</v>
       </c>
       <c r="D9" t="n">
         <v>3.33588e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-48.05999999999995</v>
+        <v>1492.513</v>
       </c>
       <c r="D10" t="n">
         <v>3.34989e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-37.72000000000003</v>
+        <v>1474.663</v>
       </c>
       <c r="D11" t="n">
         <v>3.36729e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-99.82999999999993</v>
+        <v>1706.695</v>
       </c>
       <c r="D2" t="n">
         <v>3.09071e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-76.97999999999979</v>
+        <v>1580.673</v>
       </c>
       <c r="D3" t="n">
         <v>3.18587e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-62.08000000000015</v>
+        <v>1548.632</v>
       </c>
       <c r="D4" t="n">
         <v>3.21315e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-61.15000000000009</v>
+        <v>1521.659</v>
       </c>
       <c r="D5" t="n">
         <v>3.22833e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-63.92000000000007</v>
+        <v>1489.293</v>
       </c>
       <c r="D6" t="n">
         <v>3.24531e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-52.77999999999997</v>
+        <v>1473.133</v>
       </c>
       <c r="D7" t="n">
         <v>3.26186e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-43.41000000000008</v>
+        <v>1458.818</v>
       </c>
       <c r="D8" t="n">
         <v>3.27694e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-43.94000000000005</v>
+        <v>1432.441</v>
       </c>
       <c r="D9" t="n">
         <v>3.29332e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-43.53999999999996</v>
+        <v>1406.501</v>
       </c>
       <c r="D10" t="n">
         <v>3.30992e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-39.28999999999996</v>
+        <v>1388.331</v>
       </c>
       <c r="D11" t="n">
         <v>3.32542e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-30.91999999999985</v>
+        <v>1376.488</v>
       </c>
       <c r="D12" t="n">
         <v>3.33962e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-31.24000000000001</v>
+        <v>1352.049</v>
       </c>
       <c r="D13" t="n">
         <v>3.35429e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-27.74000000000001</v>
+        <v>1332.727</v>
       </c>
       <c r="D14" t="n">
         <v>3.36847e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-14.77999999999997</v>
+        <v>1325.684</v>
       </c>
       <c r="D15" t="n">
         <v>3.38341e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-16.70000000000005</v>
+        <v>1303.442</v>
       </c>
       <c r="D16" t="n">
         <v>3.39545e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-5.819999999999936</v>
+        <v>1293.281</v>
       </c>
       <c r="D17" t="n">
         <v>3.40946e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-6.590000000000146</v>
+        <v>1272.355</v>
       </c>
       <c r="D18" t="n">
         <v>3.42359e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-2.079999999999927</v>
+        <v>1256.646</v>
       </c>
       <c r="D19" t="n">
         <v>3.43612e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>4.970000000000027</v>
+        <v>1245.451</v>
       </c>
       <c r="D20" t="n">
         <v>3.45046e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>3.6400000000001</v>
+        <v>1224.886</v>
       </c>
       <c r="D21" t="n">
         <v>3.46242e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>13.3599999999999</v>
+        <v>1216.132</v>
       </c>
       <c r="D22" t="n">
         <v>3.47565e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-124.3899999999999</v>
+        <v>1829.528</v>
       </c>
       <c r="D2" t="n">
         <v>3.04926e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-87.51000000000022</v>
+        <v>1707.352</v>
       </c>
       <c r="D3" t="n">
         <v>3.15374e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-67.74000000000024</v>
+        <v>1678.505</v>
       </c>
       <c r="D4" t="n">
         <v>3.18004e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-69.43999999999983</v>
+        <v>1645.988</v>
       </c>
       <c r="D5" t="n">
         <v>3.1971e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-57.8900000000001</v>
+        <v>1629.336</v>
       </c>
       <c r="D6" t="n">
         <v>3.21371e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-63.80000000000018</v>
+        <v>1596.888</v>
       </c>
       <c r="D7" t="n">
         <v>3.23037e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-56.19999999999982</v>
+        <v>1579.441</v>
       </c>
       <c r="D8" t="n">
         <v>3.24435e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-48.02999999999997</v>
+        <v>1562.146</v>
       </c>
       <c r="D9" t="n">
         <v>3.26033e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-44.34999999999991</v>
+        <v>1542.601</v>
       </c>
       <c r="D10" t="n">
         <v>3.2751e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-42.77999999999997</v>
+        <v>1525.781</v>
       </c>
       <c r="D11" t="n">
         <v>3.28981e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-41.07999999999993</v>
+        <v>1504.315</v>
       </c>
       <c r="D12" t="n">
         <v>3.30459e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-38.22000000000003</v>
+        <v>1486.375</v>
       </c>
       <c r="D13" t="n">
         <v>3.31745e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-36.63000000000011</v>
+        <v>1466.53</v>
       </c>
       <c r="D14" t="n">
         <v>3.33128e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-30.22000000000003</v>
+        <v>1453.219</v>
       </c>
       <c r="D15" t="n">
         <v>3.34492e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-27.95000000000005</v>
+        <v>1433.583</v>
       </c>
       <c r="D16" t="n">
         <v>3.35929e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-22.51999999999998</v>
+        <v>1417.403</v>
       </c>
       <c r="D17" t="n">
         <v>3.37169e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-21.57999999999993</v>
+        <v>1403.068</v>
       </c>
       <c r="D18" t="n">
         <v>3.38357e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-11.63999999999987</v>
+        <v>1392.533</v>
       </c>
       <c r="D19" t="n">
         <v>3.39616e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-9.910000000000082</v>
+        <v>1377.431</v>
       </c>
       <c r="D20" t="n">
         <v>3.40596e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-7.730000000000018</v>
+        <v>1358.738</v>
       </c>
       <c r="D21" t="n">
         <v>3.42004e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-3.029999999999973</v>
+        <v>1345.235</v>
       </c>
       <c r="D22" t="n">
         <v>3.43202e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-263.0700000000002</v>
+        <v>2170.048</v>
       </c>
       <c r="D2" t="n">
         <v>2.74941e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-143.1900000000001</v>
+        <v>1863.008</v>
       </c>
       <c r="D3" t="n">
         <v>3.06186e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-118.27</v>
+        <v>1771.989</v>
       </c>
       <c r="D4" t="n">
         <v>3.12655e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-93.33999999999969</v>
+        <v>1740.698</v>
       </c>
       <c r="D5" t="n">
         <v>3.14783e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-76.90999999999985</v>
+        <v>1713.602</v>
       </c>
       <c r="D6" t="n">
         <v>3.16504e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-74.12999999999965</v>
+        <v>1679.236</v>
       </c>
       <c r="D7" t="n">
         <v>3.17977e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-60.10000000000036</v>
+        <v>1659.663</v>
       </c>
       <c r="D8" t="n">
         <v>3.195e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-61.01999999999998</v>
+        <v>1626.902</v>
       </c>
       <c r="D9" t="n">
         <v>3.2094e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-44.8599999999999</v>
+        <v>1609.305</v>
       </c>
       <c r="D10" t="n">
         <v>3.22689e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-53.12000000000012</v>
+        <v>1576.191</v>
       </c>
       <c r="D11" t="n">
         <v>3.23942e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-204.7799999999997</v>
+        <v>1770.221</v>
       </c>
       <c r="D2" t="n">
         <v>3.10092e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-133.04</v>
+        <v>1647.525</v>
       </c>
       <c r="D3" t="n">
         <v>3.21803e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-108.3900000000001</v>
+        <v>1609.344</v>
       </c>
       <c r="D4" t="n">
         <v>3.24336e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-99.22999999999979</v>
+        <v>1577.062</v>
       </c>
       <c r="D5" t="n">
         <v>3.26052e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-81.45000000000005</v>
+        <v>1558.979</v>
       </c>
       <c r="D6" t="n">
         <v>3.27741e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-71.59000000000015</v>
+        <v>1538.572</v>
       </c>
       <c r="D7" t="n">
         <v>3.29345e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-69.77000000000021</v>
+        <v>1510.204</v>
       </c>
       <c r="D8" t="n">
         <v>3.30995e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-68.56999999999994</v>
+        <v>1482.629</v>
       </c>
       <c r="D9" t="n">
         <v>3.32603e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-56.64999999999986</v>
+        <v>1467.942</v>
       </c>
       <c r="D10" t="n">
         <v>3.34092e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-55.8900000000001</v>
+        <v>1443.448</v>
       </c>
       <c r="D11" t="n">
         <v>3.35646e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-56.93000000000006</v>
+        <v>1420.421</v>
       </c>
       <c r="D12" t="n">
         <v>3.36976e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-37.25999999999999</v>
+        <v>1413.051</v>
       </c>
       <c r="D13" t="n">
         <v>3.3863e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-44.46000000000004</v>
+        <v>1386.372</v>
       </c>
       <c r="D14" t="n">
         <v>3.40057e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-30.53999999999996</v>
+        <v>1377.975</v>
       </c>
       <c r="D15" t="n">
         <v>3.41422e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-35.28999999999996</v>
+        <v>1351.625</v>
       </c>
       <c r="D16" t="n">
         <v>3.42764e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-29.54000000000019</v>
+        <v>1336.306</v>
       </c>
       <c r="D17" t="n">
         <v>3.4415e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-13.74000000000001</v>
+        <v>1330.848</v>
       </c>
       <c r="D18" t="n">
         <v>3.45598e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-21.32000000000016</v>
+        <v>1305.144</v>
       </c>
       <c r="D19" t="n">
         <v>3.46799e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-11.02999999999997</v>
+        <v>1293.338</v>
       </c>
       <c r="D20" t="n">
         <v>3.48343e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-9.689999999999827</v>
+        <v>1281.105</v>
       </c>
       <c r="D21" t="n">
         <v>3.49556e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-6.049999999999955</v>
+        <v>1261.615</v>
       </c>
       <c r="D22" t="n">
         <v>3.50962e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-292.1700000000001</v>
+        <v>2010.608</v>
       </c>
       <c r="D2" t="n">
         <v>2.88254e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-166.9500000000003</v>
+        <v>1720.705</v>
       </c>
       <c r="D3" t="n">
         <v>3.20864e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-132.9700000000003</v>
+        <v>1642.312</v>
       </c>
       <c r="D4" t="n">
         <v>3.26903e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-102.9400000000001</v>
+        <v>1612.218</v>
       </c>
       <c r="D5" t="n">
         <v>3.29217e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-86.97000000000025</v>
+        <v>1581.77</v>
       </c>
       <c r="D6" t="n">
         <v>3.30891e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-80.40000000000009</v>
+        <v>1548.466</v>
       </c>
       <c r="D7" t="n">
         <v>3.32649e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-69.32000000000016</v>
+        <v>1524.622</v>
       </c>
       <c r="D8" t="n">
         <v>3.34175e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-64.16000000000008</v>
+        <v>1496.33</v>
       </c>
       <c r="D9" t="n">
         <v>3.35994e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-54.83999999999992</v>
+        <v>1472.461</v>
       </c>
       <c r="D10" t="n">
         <v>3.37649e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-44.71000000000004</v>
+        <v>1454.528</v>
       </c>
       <c r="D11" t="n">
         <v>3.3946e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-194.3999999999996</v>
+        <v>1754.182</v>
       </c>
       <c r="D2" t="n">
         <v>3.14633e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-129.9099999999999</v>
+        <v>1632.782</v>
       </c>
       <c r="D3" t="n">
         <v>3.251e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-97.59999999999991</v>
+        <v>1602.448</v>
       </c>
       <c r="D4" t="n">
         <v>3.27513e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-82.95000000000005</v>
+        <v>1576.056</v>
       </c>
       <c r="D5" t="n">
         <v>3.29049e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-70.30000000000018</v>
+        <v>1557.45</v>
       </c>
       <c r="D6" t="n">
         <v>3.30636e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-74.16000000000008</v>
+        <v>1521.223</v>
       </c>
       <c r="D7" t="n">
         <v>3.32519e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-62.17999999999984</v>
+        <v>1501.749</v>
       </c>
       <c r="D8" t="n">
         <v>3.34312e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-60.82000000000016</v>
+        <v>1476.246</v>
       </c>
       <c r="D9" t="n">
         <v>3.3612e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-54.39999999999986</v>
+        <v>1455.254</v>
       </c>
       <c r="D10" t="n">
         <v>3.37954e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-50.50999999999999</v>
+        <v>1431.631</v>
       </c>
       <c r="D11" t="n">
         <v>3.39762e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-44.42999999999984</v>
+        <v>1414.23</v>
       </c>
       <c r="D12" t="n">
         <v>3.41496e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-38.93999999999983</v>
+        <v>1395.136</v>
       </c>
       <c r="D13" t="n">
         <v>3.43213e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-37.82000000000016</v>
+        <v>1371.555</v>
       </c>
       <c r="D14" t="n">
         <v>3.44883e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-33.23000000000002</v>
+        <v>1353.532</v>
       </c>
       <c r="D15" t="n">
         <v>3.46501e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-23.8900000000001</v>
+        <v>1343.273</v>
       </c>
       <c r="D16" t="n">
         <v>3.48013e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-22.00999999999999</v>
+        <v>1321.571</v>
       </c>
       <c r="D17" t="n">
         <v>3.49666e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-14.58999999999992</v>
+        <v>1311.858</v>
       </c>
       <c r="D18" t="n">
         <v>3.51121e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-10.91000000000008</v>
+        <v>1295.136</v>
       </c>
       <c r="D19" t="n">
         <v>3.5255e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-5.690000000000055</v>
+        <v>1280.185</v>
       </c>
       <c r="D20" t="n">
         <v>3.54098e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-5.620000000000118</v>
+        <v>1258.87</v>
       </c>
       <c r="D21" t="n">
         <v>3.55608e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>1.029999999999973</v>
+        <v>1243.613</v>
       </c>
       <c r="D22" t="n">
         <v>3.57192e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-289.4000000000001</v>
+        <v>1974.047</v>
       </c>
       <c r="D2" t="n">
         <v>2.94187e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-143.6699999999996</v>
+        <v>1669.798</v>
       </c>
       <c r="D3" t="n">
         <v>3.27898e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-94.08999999999992</v>
+        <v>1601.145</v>
       </c>
       <c r="D4" t="n">
         <v>3.33221e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-69.83999999999992</v>
+        <v>1569.926</v>
       </c>
       <c r="D5" t="n">
         <v>3.35217e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-63.00999999999999</v>
+        <v>1533.049</v>
       </c>
       <c r="D6" t="n">
         <v>3.36806e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-55.33999999999992</v>
+        <v>1502.28</v>
       </c>
       <c r="D7" t="n">
         <v>3.38812e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-50.75</v>
+        <v>1469.375</v>
       </c>
       <c r="D8" t="n">
         <v>3.40612e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-43.14999999999986</v>
+        <v>1444.824</v>
       </c>
       <c r="D9" t="n">
         <v>3.42607e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-35.37999999999988</v>
+        <v>1421.813</v>
       </c>
       <c r="D10" t="n">
         <v>3.44569e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-23.38999999999987</v>
+        <v>1403.842</v>
       </c>
       <c r="D11" t="n">
         <v>3.46292e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-173.5799999999999</v>
+        <v>1753.193</v>
       </c>
       <c r="D2" t="n">
         <v>3.14726e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-106.6700000000003</v>
+        <v>1620.097</v>
       </c>
       <c r="D3" t="n">
         <v>3.25872e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-85.11999999999989</v>
+        <v>1586.794</v>
       </c>
       <c r="D4" t="n">
         <v>3.28245e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-81.08000000000015</v>
+        <v>1559.819</v>
       </c>
       <c r="D5" t="n">
         <v>3.29792e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-79.54000000000019</v>
+        <v>1534.044</v>
       </c>
       <c r="D6" t="n">
         <v>3.31247e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-67.3900000000001</v>
+        <v>1518.468</v>
       </c>
       <c r="D7" t="n">
         <v>3.33109e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-61.5</v>
+        <v>1500.94</v>
       </c>
       <c r="D8" t="n">
         <v>3.34663e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-56.36000000000013</v>
+        <v>1481.147</v>
       </c>
       <c r="D9" t="n">
         <v>3.36424e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-51.93000000000006</v>
+        <v>1463.616</v>
       </c>
       <c r="D10" t="n">
         <v>3.38049e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-52.80000000000018</v>
+        <v>1440.428</v>
       </c>
       <c r="D11" t="n">
         <v>3.39585e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-39.61999999999989</v>
+        <v>1432.094</v>
       </c>
       <c r="D12" t="n">
         <v>3.41123e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-40.91000000000008</v>
+        <v>1409.932</v>
       </c>
       <c r="D13" t="n">
         <v>3.42596e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-47.32999999999993</v>
+        <v>1382.546</v>
       </c>
       <c r="D14" t="n">
         <v>3.44129e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-37.62000000000012</v>
+        <v>1377.792</v>
       </c>
       <c r="D15" t="n">
         <v>3.4564e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-28.78999999999996</v>
+        <v>1367.065</v>
       </c>
       <c r="D16" t="n">
         <v>3.47052e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-24.8900000000001</v>
+        <v>1350.783</v>
       </c>
       <c r="D17" t="n">
         <v>3.48488e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-30.57999999999993</v>
+        <v>1328.941</v>
       </c>
       <c r="D18" t="n">
         <v>3.49741e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-17.43999999999983</v>
+        <v>1322.094</v>
       </c>
       <c r="D19" t="n">
         <v>3.51216e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-19.13999999999987</v>
+        <v>1298.512</v>
       </c>
       <c r="D20" t="n">
         <v>3.52769e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-8.779999999999973</v>
+        <v>1291.598</v>
       </c>
       <c r="D21" t="n">
         <v>3.541e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-10.5</v>
+        <v>1271.381</v>
       </c>
       <c r="D22" t="n">
         <v>3.55412e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-275.71</v>
+        <v>1483.47</v>
       </c>
       <c r="D2" t="n">
         <v>3.32062e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-128.76</v>
+        <v>1220.564</v>
       </c>
       <c r="D3" t="n">
         <v>3.56222e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-85.8599999999999</v>
+        <v>1161.111</v>
       </c>
       <c r="D4" t="n">
         <v>3.5748e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-67.93000000000006</v>
+        <v>1131.448</v>
       </c>
       <c r="D5" t="n">
         <v>3.57369e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-48.96000000000004</v>
+        <v>1115.07</v>
       </c>
       <c r="D6" t="n">
         <v>3.57601e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-50.62999999999988</v>
+        <v>1082.491</v>
       </c>
       <c r="D7" t="n">
         <v>3.58108e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-42.43000000000006</v>
+        <v>1065.059</v>
       </c>
       <c r="D8" t="n">
         <v>3.59288e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-35.94000000000005</v>
+        <v>1043.966</v>
       </c>
       <c r="D9" t="n">
         <v>3.60394e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-34.09000000000015</v>
+        <v>1020.695</v>
       </c>
       <c r="D10" t="n">
         <v>3.61266e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-28.01999999999998</v>
+        <v>1003.49</v>
       </c>
       <c r="D11" t="n">
         <v>3.62456e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1740.956</v>
       </c>
+      <c r="C2" t="n">
+        <v>2115.153889952818</v>
+      </c>
       <c r="D2" t="n">
         <v>3.17859e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1704.67</v>
       </c>
+      <c r="C3" t="n">
+        <v>2071.393393079094</v>
+      </c>
       <c r="D3" t="n">
         <v>3.21029e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1660.337</v>
       </c>
+      <c r="C4" t="n">
+        <v>2033.493600698011</v>
+      </c>
       <c r="D4" t="n">
         <v>3.23599e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1625.349</v>
       </c>
+      <c r="C5" t="n">
+        <v>1999.908874851046</v>
+      </c>
       <c r="D5" t="n">
         <v>3.25831e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1587.723</v>
       </c>
+      <c r="C6" t="n">
+        <v>1963.162848822801</v>
+      </c>
       <c r="D6" t="n">
         <v>3.28003e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1567.936</v>
       </c>
+      <c r="C7" t="n">
+        <v>1940.421843420092</v>
+      </c>
       <c r="D7" t="n">
         <v>3.29857e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1549.315</v>
       </c>
+      <c r="C8" t="n">
+        <v>1918.313577980136</v>
+      </c>
       <c r="D8" t="n">
         <v>3.31574e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1513.606</v>
       </c>
+      <c r="C9" t="n">
+        <v>1888.490272372503</v>
+      </c>
       <c r="D9" t="n">
         <v>3.33588e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1492.513</v>
       </c>
+      <c r="C10" t="n">
+        <v>1868.009192225542</v>
+      </c>
       <c r="D10" t="n">
         <v>3.34989e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1474.663</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1849.270879488455</v>
       </c>
       <c r="D11" t="n">
         <v>3.36729e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1706.695</v>
       </c>
+      <c r="C2" t="n">
+        <v>2165.46282109952</v>
+      </c>
       <c r="D2" t="n">
         <v>3.09071e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1580.673</v>
       </c>
+      <c r="C3" t="n">
+        <v>2007.961490090597</v>
+      </c>
       <c r="D3" t="n">
         <v>3.18587e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1548.632</v>
       </c>
+      <c r="C4" t="n">
+        <v>1971.872988501418</v>
+      </c>
       <c r="D4" t="n">
         <v>3.21315e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1521.659</v>
       </c>
+      <c r="C5" t="n">
+        <v>1946.210979886356</v>
+      </c>
       <c r="D5" t="n">
         <v>3.22833e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1489.293</v>
       </c>
+      <c r="C6" t="n">
+        <v>1919.416053393009</v>
+      </c>
       <c r="D6" t="n">
         <v>3.24531e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1473.133</v>
       </c>
+      <c r="C7" t="n">
+        <v>1901.711640029624</v>
+      </c>
       <c r="D7" t="n">
         <v>3.26186e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1458.818</v>
       </c>
+      <c r="C8" t="n">
+        <v>1881.963773609128</v>
+      </c>
       <c r="D8" t="n">
         <v>3.27694e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1432.441</v>
       </c>
+      <c r="C9" t="n">
+        <v>1859.011374040162</v>
+      </c>
       <c r="D9" t="n">
         <v>3.29332e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1406.501</v>
       </c>
+      <c r="C10" t="n">
+        <v>1836.65844757893</v>
+      </c>
       <c r="D10" t="n">
         <v>3.30992e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1388.331</v>
       </c>
+      <c r="C11" t="n">
+        <v>1818.508999383328</v>
+      </c>
       <c r="D11" t="n">
         <v>3.32542e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1376.488</v>
       </c>
+      <c r="C12" t="n">
+        <v>1802.095041525357</v>
+      </c>
       <c r="D12" t="n">
         <v>3.33962e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1352.049</v>
       </c>
+      <c r="C13" t="n">
+        <v>1781.868507687502</v>
+      </c>
       <c r="D13" t="n">
         <v>3.35429e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1332.727</v>
       </c>
+      <c r="C14" t="n">
+        <v>1762.406799978909</v>
+      </c>
       <c r="D14" t="n">
         <v>3.36847e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1325.684</v>
       </c>
+      <c r="C15" t="n">
+        <v>1750.101055997032</v>
+      </c>
       <c r="D15" t="n">
         <v>3.38341e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1303.442</v>
       </c>
+      <c r="C16" t="n">
+        <v>1731.114104068098</v>
+      </c>
       <c r="D16" t="n">
         <v>3.39545e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1293.281</v>
       </c>
+      <c r="C17" t="n">
+        <v>1717.148538504679</v>
+      </c>
       <c r="D17" t="n">
         <v>3.40946e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1272.355</v>
       </c>
+      <c r="C18" t="n">
+        <v>1697.990309042169</v>
+      </c>
       <c r="D18" t="n">
         <v>3.42359e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1256.646</v>
       </c>
+      <c r="C19" t="n">
+        <v>1682.224331323963</v>
+      </c>
       <c r="D19" t="n">
         <v>3.43612e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1245.451</v>
       </c>
+      <c r="C20" t="n">
+        <v>1668.136698600441</v>
+      </c>
       <c r="D20" t="n">
         <v>3.45046e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1224.886</v>
       </c>
+      <c r="C21" t="n">
+        <v>1648.966038630779</v>
+      </c>
       <c r="D21" t="n">
         <v>3.46242e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1216.132</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1637.444020368364</v>
       </c>
       <c r="D22" t="n">
         <v>3.47565e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>1829.528</v>
       </c>
+      <c r="C2" t="n">
+        <v>2232.854733550869</v>
+      </c>
       <c r="D2" t="n">
         <v>3.04926e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1707.352</v>
       </c>
+      <c r="C3" t="n">
+        <v>2081.699584522211</v>
+      </c>
       <c r="D3" t="n">
         <v>3.15374e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1678.505</v>
       </c>
+      <c r="C4" t="n">
+        <v>2047.176054452896</v>
+      </c>
       <c r="D4" t="n">
         <v>3.18004e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1645.988</v>
       </c>
+      <c r="C5" t="n">
+        <v>2020.295075895481</v>
+      </c>
       <c r="D5" t="n">
         <v>3.1971e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1629.336</v>
       </c>
+      <c r="C6" t="n">
+        <v>2002.385141513267</v>
+      </c>
       <c r="D6" t="n">
         <v>3.21371e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1596.888</v>
       </c>
+      <c r="C7" t="n">
+        <v>1975.172005524785</v>
+      </c>
       <c r="D7" t="n">
         <v>3.23037e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1579.441</v>
       </c>
+      <c r="C8" t="n">
+        <v>1958.69036968718</v>
+      </c>
       <c r="D8" t="n">
         <v>3.24435e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1562.146</v>
       </c>
+      <c r="C9" t="n">
+        <v>1939.357780702128</v>
+      </c>
       <c r="D9" t="n">
         <v>3.26033e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1542.601</v>
       </c>
+      <c r="C10" t="n">
+        <v>1919.144399165686</v>
+      </c>
       <c r="D10" t="n">
         <v>3.2751e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1525.781</v>
       </c>
+      <c r="C11" t="n">
+        <v>1900.682596455563</v>
+      </c>
       <c r="D11" t="n">
         <v>3.28981e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1504.315</v>
       </c>
+      <c r="C12" t="n">
+        <v>1880.305804373608</v>
+      </c>
       <c r="D12" t="n">
         <v>3.30459e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1486.375</v>
       </c>
+      <c r="C13" t="n">
+        <v>1862.778728723531</v>
+      </c>
       <c r="D13" t="n">
         <v>3.31745e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1466.53</v>
       </c>
+      <c r="C14" t="n">
+        <v>1843.816574812802</v>
+      </c>
       <c r="D14" t="n">
         <v>3.33128e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1453.219</v>
       </c>
+      <c r="C15" t="n">
+        <v>1831.451831078917</v>
+      </c>
       <c r="D15" t="n">
         <v>3.34492e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1433.583</v>
       </c>
+      <c r="C16" t="n">
+        <v>1812.413390085947</v>
+      </c>
       <c r="D16" t="n">
         <v>3.35929e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1417.403</v>
       </c>
+      <c r="C17" t="n">
+        <v>1796.747461141449</v>
+      </c>
       <c r="D17" t="n">
         <v>3.37169e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1403.068</v>
       </c>
+      <c r="C18" t="n">
+        <v>1782.260272155784</v>
+      </c>
       <c r="D18" t="n">
         <v>3.38357e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1392.533</v>
       </c>
+      <c r="C19" t="n">
+        <v>1769.760248003048</v>
+      </c>
       <c r="D19" t="n">
         <v>3.39616e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1377.431</v>
       </c>
+      <c r="C20" t="n">
+        <v>1753.173570453875</v>
+      </c>
       <c r="D20" t="n">
         <v>3.40596e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1358.738</v>
       </c>
+      <c r="C21" t="n">
+        <v>1736.692461542023</v>
+      </c>
       <c r="D21" t="n">
         <v>3.42004e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1345.235</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1721.743842360765</v>
       </c>
       <c r="D22" t="n">
         <v>3.43202e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2170.048</v>
       </c>
+      <c r="C2" t="n">
+        <v>2638.566975843747</v>
+      </c>
       <c r="D2" t="n">
         <v>2.74941e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1863.008</v>
       </c>
+      <c r="C3" t="n">
+        <v>2259.377683196543</v>
+      </c>
       <c r="D3" t="n">
         <v>3.06186e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1771.989</v>
       </c>
+      <c r="C4" t="n">
+        <v>2165.72826407297</v>
+      </c>
       <c r="D4" t="n">
         <v>3.12655e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1740.698</v>
       </c>
+      <c r="C5" t="n">
+        <v>2134.537846059957</v>
+      </c>
       <c r="D5" t="n">
         <v>3.14783e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1713.602</v>
       </c>
+      <c r="C6" t="n">
+        <v>2108.027874267371</v>
+      </c>
       <c r="D6" t="n">
         <v>3.16504e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1679.236</v>
       </c>
+      <c r="C7" t="n">
+        <v>2077.577671332773</v>
+      </c>
       <c r="D7" t="n">
         <v>3.17977e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1659.663</v>
       </c>
+      <c r="C8" t="n">
+        <v>2058.516417802642</v>
+      </c>
       <c r="D8" t="n">
         <v>3.195e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1626.902</v>
       </c>
+      <c r="C9" t="n">
+        <v>2030.858335645932</v>
+      </c>
       <c r="D9" t="n">
         <v>3.2094e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1609.305</v>
       </c>
+      <c r="C10" t="n">
+        <v>2011.305554211372</v>
+      </c>
       <c r="D10" t="n">
         <v>3.22689e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1576.191</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1983.181267054139</v>
       </c>
       <c r="D11" t="n">
         <v>3.23942e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1770.221</v>
       </c>
+      <c r="C2" t="n">
+        <v>2217.008184803722</v>
+      </c>
       <c r="D2" t="n">
         <v>3.10092e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1647.525</v>
       </c>
+      <c r="C3" t="n">
+        <v>2068.531982575427</v>
+      </c>
       <c r="D3" t="n">
         <v>3.21803e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1609.344</v>
       </c>
+      <c r="C4" t="n">
+        <v>2028.468404671067</v>
+      </c>
       <c r="D4" t="n">
         <v>3.24336e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1577.062</v>
       </c>
+      <c r="C5" t="n">
+        <v>1998.43950285299</v>
+      </c>
       <c r="D5" t="n">
         <v>3.26052e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1558.979</v>
       </c>
+      <c r="C6" t="n">
+        <v>1978.690397929426</v>
+      </c>
       <c r="D6" t="n">
         <v>3.27741e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1538.572</v>
       </c>
+      <c r="C7" t="n">
+        <v>1957.891608196941</v>
+      </c>
       <c r="D7" t="n">
         <v>3.29345e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1510.204</v>
       </c>
+      <c r="C8" t="n">
+        <v>1932.999833010673</v>
+      </c>
       <c r="D8" t="n">
         <v>3.30995e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1482.629</v>
       </c>
+      <c r="C9" t="n">
+        <v>1906.888542324745</v>
+      </c>
       <c r="D9" t="n">
         <v>3.32603e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1467.942</v>
       </c>
+      <c r="C10" t="n">
+        <v>1891.350105230444</v>
+      </c>
       <c r="D10" t="n">
         <v>3.34092e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1443.448</v>
       </c>
+      <c r="C11" t="n">
+        <v>1867.741964053769</v>
+      </c>
       <c r="D11" t="n">
         <v>3.35646e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1420.421</v>
       </c>
+      <c r="C12" t="n">
+        <v>1846.25238494473</v>
+      </c>
       <c r="D12" t="n">
         <v>3.36976e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1413.051</v>
       </c>
+      <c r="C13" t="n">
+        <v>1833.671179969087</v>
+      </c>
       <c r="D13" t="n">
         <v>3.3863e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1386.372</v>
       </c>
+      <c r="C14" t="n">
+        <v>1811.403429574767</v>
+      </c>
       <c r="D14" t="n">
         <v>3.40057e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1377.975</v>
       </c>
+      <c r="C15" t="n">
+        <v>1798.854039583229</v>
+      </c>
       <c r="D15" t="n">
         <v>3.41422e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1351.625</v>
       </c>
+      <c r="C16" t="n">
+        <v>1776.547617350616</v>
+      </c>
       <c r="D16" t="n">
         <v>3.42764e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1336.306</v>
       </c>
+      <c r="C17" t="n">
+        <v>1760.461068443667</v>
+      </c>
       <c r="D17" t="n">
         <v>3.4415e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1330.848</v>
       </c>
+      <c r="C18" t="n">
+        <v>1749.426332727932</v>
+      </c>
       <c r="D18" t="n">
         <v>3.45598e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1305.144</v>
       </c>
+      <c r="C19" t="n">
+        <v>1726.563335698608</v>
+      </c>
       <c r="D19" t="n">
         <v>3.46799e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1293.338</v>
       </c>
+      <c r="C20" t="n">
+        <v>1713.861849146121</v>
+      </c>
       <c r="D20" t="n">
         <v>3.48343e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1281.105</v>
       </c>
+      <c r="C21" t="n">
+        <v>1697.734957059718</v>
+      </c>
       <c r="D21" t="n">
         <v>3.49556e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1261.615</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1680.352044435787</v>
       </c>
       <c r="D22" t="n">
         <v>3.50962e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2010.608</v>
       </c>
+      <c r="C2" t="n">
+        <v>2488.187217156694</v>
+      </c>
       <c r="D2" t="n">
         <v>2.88254e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1720.705</v>
       </c>
+      <c r="C3" t="n">
+        <v>2120.719521190824</v>
+      </c>
       <c r="D3" t="n">
         <v>3.20864e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1642.312</v>
       </c>
+      <c r="C4" t="n">
+        <v>2041.481979996777</v>
+      </c>
       <c r="D4" t="n">
         <v>3.26903e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1612.218</v>
       </c>
+      <c r="C5" t="n">
+        <v>2009.385546974985</v>
+      </c>
       <c r="D5" t="n">
         <v>3.29217e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1581.77</v>
       </c>
+      <c r="C6" t="n">
+        <v>1981.768243524108</v>
+      </c>
       <c r="D6" t="n">
         <v>3.30891e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1548.466</v>
       </c>
+      <c r="C7" t="n">
+        <v>1954.075724428917</v>
+      </c>
       <c r="D7" t="n">
         <v>3.32649e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1524.622</v>
       </c>
+      <c r="C8" t="n">
+        <v>1928.244455604551</v>
+      </c>
       <c r="D8" t="n">
         <v>3.34175e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1496.33</v>
       </c>
+      <c r="C9" t="n">
+        <v>1904.093996290159</v>
+      </c>
       <c r="D9" t="n">
         <v>3.35994e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1472.461</v>
       </c>
+      <c r="C10" t="n">
+        <v>1880.159041288339</v>
+      </c>
       <c r="D10" t="n">
         <v>3.37649e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1454.528</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1861.744587009153</v>
       </c>
       <c r="D11" t="n">
         <v>3.3946e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1754.182</v>
       </c>
+      <c r="C2" t="n">
+        <v>2181.823583035389</v>
+      </c>
       <c r="D2" t="n">
         <v>3.14633e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1632.782</v>
       </c>
+      <c r="C3" t="n">
+        <v>2040.649786075043</v>
+      </c>
       <c r="D3" t="n">
         <v>3.251e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1602.448</v>
       </c>
+      <c r="C4" t="n">
+        <v>2006.74377425686</v>
+      </c>
       <c r="D4" t="n">
         <v>3.27513e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1576.056</v>
       </c>
+      <c r="C5" t="n">
+        <v>1983.081242921831</v>
+      </c>
       <c r="D5" t="n">
         <v>3.29049e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1557.45</v>
       </c>
+      <c r="C6" t="n">
+        <v>1962.851284996393</v>
+      </c>
       <c r="D6" t="n">
         <v>3.30636e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1521.223</v>
       </c>
+      <c r="C7" t="n">
+        <v>1934.390900264862</v>
+      </c>
       <c r="D7" t="n">
         <v>3.32519e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1501.749</v>
       </c>
+      <c r="C8" t="n">
+        <v>1913.585525197995</v>
+      </c>
       <c r="D8" t="n">
         <v>3.34312e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1476.246</v>
       </c>
+      <c r="C9" t="n">
+        <v>1888.708046471417</v>
+      </c>
       <c r="D9" t="n">
         <v>3.3612e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1455.254</v>
       </c>
+      <c r="C10" t="n">
+        <v>1866.698473035864</v>
+      </c>
       <c r="D10" t="n">
         <v>3.37954e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1431.631</v>
       </c>
+      <c r="C11" t="n">
+        <v>1847.583463993273</v>
+      </c>
       <c r="D11" t="n">
         <v>3.39762e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1414.23</v>
       </c>
+      <c r="C12" t="n">
+        <v>1828.027322595682</v>
+      </c>
       <c r="D12" t="n">
         <v>3.41496e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1395.136</v>
       </c>
+      <c r="C13" t="n">
+        <v>1806.991798334985</v>
+      </c>
       <c r="D13" t="n">
         <v>3.43213e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1371.555</v>
       </c>
+      <c r="C14" t="n">
+        <v>1787.206329023053</v>
+      </c>
       <c r="D14" t="n">
         <v>3.44883e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1353.532</v>
       </c>
+      <c r="C15" t="n">
+        <v>1768.142256051785</v>
+      </c>
       <c r="D15" t="n">
         <v>3.46501e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1343.273</v>
       </c>
+      <c r="C16" t="n">
+        <v>1753.974413991728</v>
+      </c>
       <c r="D16" t="n">
         <v>3.48013e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1321.571</v>
       </c>
+      <c r="C17" t="n">
+        <v>1733.439058392677</v>
+      </c>
       <c r="D17" t="n">
         <v>3.49666e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1311.858</v>
       </c>
+      <c r="C18" t="n">
+        <v>1720.773387495169</v>
+      </c>
       <c r="D18" t="n">
         <v>3.51121e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1295.136</v>
       </c>
+      <c r="C19" t="n">
+        <v>1705.620746222601</v>
+      </c>
       <c r="D19" t="n">
         <v>3.5255e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1280.185</v>
       </c>
+      <c r="C20" t="n">
+        <v>1689.417897437787</v>
+      </c>
       <c r="D20" t="n">
         <v>3.54098e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1258.87</v>
       </c>
+      <c r="C21" t="n">
+        <v>1671.737387785594</v>
+      </c>
       <c r="D21" t="n">
         <v>3.55608e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1243.613</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1655.201138344873</v>
       </c>
       <c r="D22" t="n">
         <v>3.57192e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>1974.047</v>
       </c>
+      <c r="C2" t="n">
+        <v>2415.099627131626</v>
+      </c>
       <c r="D2" t="n">
         <v>2.94187e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1669.798</v>
       </c>
+      <c r="C3" t="n">
+        <v>2039.931030640798</v>
+      </c>
       <c r="D3" t="n">
         <v>3.27898e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1601.145</v>
       </c>
+      <c r="C4" t="n">
+        <v>1967.588397631326</v>
+      </c>
       <c r="D4" t="n">
         <v>3.33221e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1569.926</v>
       </c>
+      <c r="C5" t="n">
+        <v>1932.88505797966</v>
+      </c>
       <c r="D5" t="n">
         <v>3.35217e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1533.049</v>
       </c>
+      <c r="C6" t="n">
+        <v>1900.743158813034</v>
+      </c>
       <c r="D6" t="n">
         <v>3.36806e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1502.28</v>
       </c>
+      <c r="C7" t="n">
+        <v>1872.726034253964</v>
+      </c>
       <c r="D7" t="n">
         <v>3.38812e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1469.375</v>
       </c>
+      <c r="C8" t="n">
+        <v>1846.28784329965</v>
+      </c>
       <c r="D8" t="n">
         <v>3.40612e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1444.824</v>
       </c>
+      <c r="C9" t="n">
+        <v>1822.796514274516</v>
+      </c>
       <c r="D9" t="n">
         <v>3.42607e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1421.813</v>
       </c>
+      <c r="C10" t="n">
+        <v>1800.000473124783</v>
+      </c>
       <c r="D10" t="n">
         <v>3.44569e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1403.842</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1781.291563797772</v>
       </c>
       <c r="D11" t="n">
         <v>3.46292e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1753.193</v>
       </c>
+      <c r="C2" t="n">
+        <v>2177.629856735957</v>
+      </c>
       <c r="D2" t="n">
         <v>3.14726e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1620.097</v>
       </c>
+      <c r="C3" t="n">
+        <v>2022.021685136089</v>
+      </c>
       <c r="D3" t="n">
         <v>3.25872e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1586.794</v>
       </c>
+      <c r="C4" t="n">
+        <v>1983.840222782687</v>
+      </c>
       <c r="D4" t="n">
         <v>3.28245e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1559.819</v>
       </c>
+      <c r="C5" t="n">
+        <v>1961.528565715493</v>
+      </c>
       <c r="D5" t="n">
         <v>3.29792e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1534.044</v>
       </c>
+      <c r="C6" t="n">
+        <v>1936.530048235078</v>
+      </c>
       <c r="D6" t="n">
         <v>3.31247e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1518.468</v>
       </c>
+      <c r="C7" t="n">
+        <v>1920.664010257213</v>
+      </c>
       <c r="D7" t="n">
         <v>3.33109e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1500.94</v>
       </c>
+      <c r="C8" t="n">
+        <v>1902.041843157619</v>
+      </c>
       <c r="D8" t="n">
         <v>3.34663e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1481.147</v>
       </c>
+      <c r="C9" t="n">
+        <v>1882.131795377778</v>
+      </c>
       <c r="D9" t="n">
         <v>3.36424e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1463.616</v>
       </c>
+      <c r="C10" t="n">
+        <v>1865.681548701116</v>
+      </c>
       <c r="D10" t="n">
         <v>3.38049e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1440.428</v>
       </c>
+      <c r="C11" t="n">
+        <v>1843.582081332437</v>
+      </c>
       <c r="D11" t="n">
         <v>3.39585e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1432.094</v>
       </c>
+      <c r="C12" t="n">
+        <v>1830.271970797333</v>
+      </c>
       <c r="D12" t="n">
         <v>3.41123e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1409.932</v>
       </c>
+      <c r="C13" t="n">
+        <v>1811.046269992676</v>
+      </c>
       <c r="D13" t="n">
         <v>3.42596e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1382.546</v>
       </c>
+      <c r="C14" t="n">
+        <v>1789.446639315326</v>
+      </c>
       <c r="D14" t="n">
         <v>3.44129e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1377.792</v>
       </c>
+      <c r="C15" t="n">
+        <v>1776.422981836055</v>
+      </c>
       <c r="D15" t="n">
         <v>3.4564e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1367.065</v>
       </c>
+      <c r="C16" t="n">
+        <v>1764.997622112465</v>
+      </c>
       <c r="D16" t="n">
         <v>3.47052e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1350.783</v>
       </c>
+      <c r="C17" t="n">
+        <v>1750.516151263335</v>
+      </c>
       <c r="D17" t="n">
         <v>3.48488e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1328.941</v>
       </c>
+      <c r="C18" t="n">
+        <v>1730.883096934075</v>
+      </c>
       <c r="D18" t="n">
         <v>3.49741e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1322.094</v>
       </c>
+      <c r="C19" t="n">
+        <v>1721.648686934279</v>
+      </c>
       <c r="D19" t="n">
         <v>3.51216e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1298.512</v>
       </c>
+      <c r="C20" t="n">
+        <v>1704.33091592751</v>
+      </c>
       <c r="D20" t="n">
         <v>3.52769e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1291.598</v>
       </c>
+      <c r="C21" t="n">
+        <v>1692.652379878525</v>
+      </c>
       <c r="D21" t="n">
         <v>3.541e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1271.381</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1674.16157758049</v>
       </c>
       <c r="D22" t="n">
         <v>3.55412e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1483.47</v>
       </c>
+      <c r="C2" t="n">
+        <v>2066.063085128366</v>
+      </c>
       <c r="D2" t="n">
         <v>3.32062e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1220.564</v>
       </c>
+      <c r="C3" t="n">
+        <v>1698.472395683319</v>
+      </c>
       <c r="D3" t="n">
         <v>3.56222e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1161.111</v>
       </c>
+      <c r="C4" t="n">
+        <v>1629.669829606613</v>
+      </c>
       <c r="D4" t="n">
         <v>3.5748e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1131.448</v>
       </c>
+      <c r="C5" t="n">
+        <v>1600.056500087459</v>
+      </c>
       <c r="D5" t="n">
         <v>3.57369e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1115.07</v>
       </c>
+      <c r="C6" t="n">
+        <v>1583.061275403915</v>
+      </c>
       <c r="D6" t="n">
         <v>3.57601e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1082.491</v>
       </c>
+      <c r="C7" t="n">
+        <v>1553.812980561614</v>
+      </c>
       <c r="D7" t="n">
         <v>3.58108e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1065.059</v>
       </c>
+      <c r="C8" t="n">
+        <v>1533.619470434819</v>
+      </c>
       <c r="D8" t="n">
         <v>3.59288e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1043.966</v>
       </c>
+      <c r="C9" t="n">
+        <v>1514.17109381599</v>
+      </c>
       <c r="D9" t="n">
         <v>3.60394e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1020.695</v>
       </c>
+      <c r="C10" t="n">
+        <v>1493.98594376344</v>
+      </c>
       <c r="D10" t="n">
         <v>3.61266e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1003.49</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1479.095000796789</v>
       </c>
       <c r="D11" t="n">
         <v>3.62456e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -565,7 +565,7 @@
         <v>1740.956</v>
       </c>
       <c r="C2" t="n">
-        <v>2115.153889952818</v>
+        <v>15373.23556834625</v>
       </c>
       <c r="D2" t="n">
         <v>3.17859e-07</v>
@@ -598,10 +598,7 @@
         <v>-23178.24023521944</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.276838273332596e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2422.705116619908</v>
+        <v>-12982.08739033649</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000742e-08</v>
@@ -618,7 +615,7 @@
         <v>1704.67</v>
       </c>
       <c r="C3" t="n">
-        <v>2071.393393079094</v>
+        <v>17715.41365568978</v>
       </c>
       <c r="D3" t="n">
         <v>3.21029e-07</v>
@@ -651,10 +648,7 @@
         <v>-21796.42237363628</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.729833070191376e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2370.400911638438</v>
+        <v>-15394.26522568965</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000122e-08</v>
@@ -671,7 +665,7 @@
         <v>1660.337</v>
       </c>
       <c r="C4" t="n">
-        <v>2033.493600698011</v>
+        <v>14904.25868503291</v>
       </c>
       <c r="D4" t="n">
         <v>3.23599e-07</v>
@@ -704,10 +698,7 @@
         <v>-18694.04726858732</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.901129054328679e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2327.83135363464</v>
+        <v>-12597.41679765764</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -724,7 +715,7 @@
         <v>1625.349</v>
       </c>
       <c r="C5" t="n">
-        <v>1999.908874851046</v>
+        <v>15656.74347048804</v>
       </c>
       <c r="D5" t="n">
         <v>3.25831e-07</v>
@@ -757,10 +748,7 @@
         <v>-16278.73085870794</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.284194519695916e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2288.712561472484</v>
+        <v>-13393.50122503935</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -777,7 +765,7 @@
         <v>1587.723</v>
       </c>
       <c r="C6" t="n">
-        <v>1963.162848822801</v>
+        <v>15782.85790058864</v>
       </c>
       <c r="D6" t="n">
         <v>3.28003e-07</v>
@@ -810,10 +798,7 @@
         <v>-14454.60429870954</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.629721820495902e-13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2256.205389589224</v>
+        <v>-13553.85791453131</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -830,7 +815,7 @@
         <v>1567.936</v>
       </c>
       <c r="C7" t="n">
-        <v>1940.421843420092</v>
+        <v>696.1150616453991</v>
       </c>
       <c r="D7" t="n">
         <v>3.29857e-07</v>
@@ -863,16 +848,13 @@
         <v>-12602.99540603366</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.214984352901275e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2222.869071045858</v>
+        <v>501.0810453750826</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000019e-08</v>
+        <v>1.424387964313831e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.823443621170365</v>
+        <v>0.9869143089923199</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1549.315</v>
       </c>
       <c r="C8" t="n">
-        <v>1918.313577980136</v>
+        <v>15341.63580913807</v>
       </c>
       <c r="D8" t="n">
         <v>3.31574e-07</v>
@@ -916,10 +898,7 @@
         <v>-9728.877440864233</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.150855921476016e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2191.775370489228</v>
+        <v>-13164.93279576415</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001085e-08</v>
@@ -936,7 +915,7 @@
         <v>1513.606</v>
       </c>
       <c r="C9" t="n">
-        <v>1888.490272372503</v>
+        <v>15575.9424857543</v>
       </c>
       <c r="D9" t="n">
         <v>3.33588e-07</v>
@@ -969,10 +948,7 @@
         <v>-9004.028070926124</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.572198403157648e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2162.685098791999</v>
+        <v>-13430.06173857541</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -989,7 +965,7 @@
         <v>1492.513</v>
       </c>
       <c r="C10" t="n">
-        <v>1868.009192225542</v>
+        <v>15769.33711314567</v>
       </c>
       <c r="D10" t="n">
         <v>3.34989e-07</v>
@@ -1022,10 +998,7 @@
         <v>-7790.141647886042</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.50505628096771e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2135.956504251289</v>
+        <v>-13648.58214841385</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000012837e-08</v>
@@ -1042,7 +1015,7 @@
         <v>1474.663</v>
       </c>
       <c r="C11" t="n">
-        <v>1849.270879488455</v>
+        <v>670.8022516384762</v>
       </c>
       <c r="D11" t="n">
         <v>3.36729e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-3682.098932190307</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.018956099445599e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2110.764773032064</v>
+        <v>496.4403358360385</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.842077591379713e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8245305029910103</v>
+        <v>0.968385307791243</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>1706.695</v>
       </c>
       <c r="C2" t="n">
-        <v>2165.46282109952</v>
+        <v>17752.66948430648</v>
       </c>
       <c r="D2" t="n">
         <v>3.09071e-07</v>
@@ -1274,10 +1244,7 @@
         <v>-19007.55173147595</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.305487546816426e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2417.965521357722</v>
+        <v>-15347.19165625191</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000068e-08</v>
@@ -1294,7 +1261,7 @@
         <v>1580.673</v>
       </c>
       <c r="C3" t="n">
-        <v>2007.961490090597</v>
+        <v>713.775750955388</v>
       </c>
       <c r="D3" t="n">
         <v>3.18587e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-15991.10059884027</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.015821897910493e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2301.573766587481</v>
+        <v>549.8748458601864</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>1.206290329310884e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.817210022386449</v>
+        <v>0.9981590412570411</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1548.632</v>
       </c>
       <c r="C4" t="n">
-        <v>1971.872988501418</v>
+        <v>704.8245440827916</v>
       </c>
       <c r="D4" t="n">
         <v>3.21315e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-13168.14695762455</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.862163991411075e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2261.126882389999</v>
+        <v>554.5145678246272</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.139021727007833e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.817328364569441</v>
+        <v>0.9989959883367556</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1521.659</v>
       </c>
       <c r="C5" t="n">
-        <v>1946.210979886356</v>
+        <v>15350.75466929421</v>
       </c>
       <c r="D5" t="n">
         <v>3.22833e-07</v>
@@ -1433,10 +1394,7 @@
         <v>-12429.98792904282</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.451102402535445e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2232.736037910744</v>
+        <v>-13125.88975198714</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -1453,7 +1411,7 @@
         <v>1489.293</v>
       </c>
       <c r="C6" t="n">
-        <v>1919.416053393009</v>
+        <v>587.1422308328006</v>
       </c>
       <c r="D6" t="n">
         <v>3.24531e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-11647.80140229969</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.297928399771804e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2205.440712058308</v>
+        <v>739.428170017748</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.00000000003472e-08</v>
+        <v>1.319425768346611e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8176202860466265</v>
+        <v>0.8677474747538798</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1473.133</v>
       </c>
       <c r="C7" t="n">
-        <v>1901.711640029624</v>
+        <v>588.3867512271892</v>
       </c>
       <c r="D7" t="n">
         <v>3.26186e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-9436.252704124152</v>
       </c>
       <c r="Y7" t="n">
-        <v>125.3025939566045</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2209.799804394665</v>
+        <v>648.9815818335582</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.231638106498333e-08</v>
+        <v>1.79660378502676e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8117667617960486</v>
+        <v>0.9906211724194646</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1458.818</v>
       </c>
       <c r="C8" t="n">
-        <v>1881.963773609128</v>
+        <v>588.2685965250023</v>
       </c>
       <c r="D8" t="n">
         <v>3.27694e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-7251.208791127721</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.774349664341948e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2152.559998539048</v>
+        <v>645.8122493262707</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.528871520792631e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8181090089039726</v>
+        <v>0.9987418967308167</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1432.441</v>
       </c>
       <c r="C9" t="n">
-        <v>1859.011374040162</v>
+        <v>15242.61621830588</v>
       </c>
       <c r="D9" t="n">
         <v>3.29332e-07</v>
@@ -1645,10 +1594,7 @@
         <v>-7088.803743242986</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.944182475079335e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2127.274118260848</v>
+        <v>-13112.71153354432</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1665,7 +1611,7 @@
         <v>1406.501</v>
       </c>
       <c r="C10" t="n">
-        <v>1836.65844757893</v>
+        <v>590.1436319547522</v>
       </c>
       <c r="D10" t="n">
         <v>3.30992e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-5966.943088565754</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.396965877691165e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2102.88909854987</v>
+        <v>616.2067443663835</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.394310938687383e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8186983673655126</v>
+        <v>0.9997551580468077</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1388.331</v>
       </c>
       <c r="C11" t="n">
-        <v>1818.508999383328</v>
+        <v>15449.93769074055</v>
       </c>
       <c r="D11" t="n">
         <v>3.32542e-07</v>
@@ -1751,10 +1694,7 @@
         <v>-4505.986568045884</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.433486849496139e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2079.65642336472</v>
+        <v>-13366.95839351406</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1771,7 +1711,7 @@
         <v>1376.488</v>
       </c>
       <c r="C12" t="n">
-        <v>1802.095041525357</v>
+        <v>14914.31703064689</v>
       </c>
       <c r="D12" t="n">
         <v>3.33962e-07</v>
@@ -1804,10 +1744,7 @@
         <v>-1616.932975848739</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.784480943215926e-12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2057.527191636916</v>
+        <v>-12844.6645162028</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1824,7 +1761,7 @@
         <v>1352.049</v>
       </c>
       <c r="C13" t="n">
-        <v>1781.868507687502</v>
+        <v>15151.67916633041</v>
       </c>
       <c r="D13" t="n">
         <v>3.35429e-07</v>
@@ -1857,10 +1794,7 @@
         <v>-1602.722166044065</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.011136158609636e-11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2035.811585040424</v>
+        <v>-13106.39002926968</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1877,7 +1811,7 @@
         <v>1332.727</v>
       </c>
       <c r="C14" t="n">
-        <v>1762.406799978909</v>
+        <v>14696.79377936087</v>
       </c>
       <c r="D14" t="n">
         <v>3.36847e-07</v>
@@ -1910,10 +1844,7 @@
         <v>-390.1280970922538</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.305616843956753e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2014.774469124145</v>
+        <v>-12665.32723764413</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1930,7 +1861,7 @@
         <v>1325.684</v>
       </c>
       <c r="C15" t="n">
-        <v>1750.101055997032</v>
+        <v>14174.23395703603</v>
       </c>
       <c r="D15" t="n">
         <v>3.38341e-07</v>
@@ -1963,10 +1894,7 @@
         <v>5268.739025487145</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.163205638417968e-11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1994.147219145599</v>
+        <v>-12154.82556905762</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1983,7 +1911,7 @@
         <v>1303.442</v>
       </c>
       <c r="C16" t="n">
-        <v>1731.114104068098</v>
+        <v>13852.38165224137</v>
       </c>
       <c r="D16" t="n">
         <v>3.39545e-07</v>
@@ -2016,10 +1944,7 @@
         <v>4066.303261733255</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.176327724613628e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1973.157681957575</v>
+        <v>-11846.84621065017</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2036,7 +1961,7 @@
         <v>1293.281</v>
       </c>
       <c r="C17" t="n">
-        <v>1717.148538504679</v>
+        <v>14063.07232552971</v>
       </c>
       <c r="D17" t="n">
         <v>3.40946e-07</v>
@@ -2069,10 +1994,7 @@
         <v>9217.453206608392</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.157181690796733e-12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1952.948415790365</v>
+        <v>-12080.32030528603</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2089,7 +2011,7 @@
         <v>1272.355</v>
       </c>
       <c r="C18" t="n">
-        <v>1697.990309042169</v>
+        <v>13582.11624524332</v>
       </c>
       <c r="D18" t="n">
         <v>3.42359e-07</v>
@@ -2122,10 +2044,7 @@
         <v>7715.60251121063</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66133114213418e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1932.629378412675</v>
+        <v>-11610.60253626112</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000102e-08</v>
@@ -2142,7 +2061,7 @@
         <v>1256.646</v>
       </c>
       <c r="C19" t="n">
-        <v>1682.224331323963</v>
+        <v>13324.60644374723</v>
       </c>
       <c r="D19" t="n">
         <v>3.43612e-07</v>
@@ -2175,10 +2094,7 @@
         <v>9281.968402027896</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.445087443522884e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1912.442615431743</v>
+        <v>-11367.39403231928</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000669e-08</v>
@@ -2195,7 +2111,7 @@
         <v>1245.451</v>
       </c>
       <c r="C20" t="n">
-        <v>1668.136698600441</v>
+        <v>13096.76544146871</v>
       </c>
       <c r="D20" t="n">
         <v>3.45046e-07</v>
@@ -2228,10 +2144,7 @@
         <v>-6081.93013548339</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.633609001397241e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1891.887281090243</v>
+        <v>-11155.5524968483</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -2248,7 +2161,7 @@
         <v>1224.886</v>
       </c>
       <c r="C21" t="n">
-        <v>1648.966038630779</v>
+        <v>1603.726528193463</v>
       </c>
       <c r="D21" t="n">
         <v>3.46242e-07</v>
@@ -2281,10 +2194,7 @@
         <v>-5784.175344101349</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.706330029905297e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1871.62320880451</v>
+        <v>164.2948700943214</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000204e-08</v>
@@ -2301,7 +2211,7 @@
         <v>1216.132</v>
       </c>
       <c r="C22" t="n">
-        <v>1637.444020368364</v>
+        <v>11876.14306404255</v>
       </c>
       <c r="D22" t="n">
         <v>3.47565e-07</v>
@@ -2334,10 +2244,7 @@
         <v>-6100.36882643658</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.837006812737307e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1851.003755098749</v>
+        <v>-9947.852905498095</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000003e-08</v>
@@ -2500,7 +2407,7 @@
         <v>1829.528</v>
       </c>
       <c r="C2" t="n">
-        <v>2232.854733550869</v>
+        <v>17184.10850184025</v>
       </c>
       <c r="D2" t="n">
         <v>3.04926e-07</v>
@@ -2533,10 +2440,7 @@
         <v>-24017.42558936794</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.018961759963461e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2505.224868458088</v>
+        <v>-14694.78409417193</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000001e-08</v>
@@ -2553,7 +2457,7 @@
         <v>1707.352</v>
       </c>
       <c r="C3" t="n">
-        <v>2081.699584522211</v>
+        <v>745.9214312748757</v>
       </c>
       <c r="D3" t="n">
         <v>3.15374e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-20180.0408729663</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.132674585236267e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2390.069361808413</v>
+        <v>501.6402600775816</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>1.209439172934205e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8220182930970963</v>
+        <v>0.9877548306871301</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>1678.505</v>
       </c>
       <c r="C4" t="n">
-        <v>2047.176054452896</v>
+        <v>15741.7904066126</v>
       </c>
       <c r="D4" t="n">
         <v>3.18004e-07</v>
@@ -2639,10 +2540,7 @@
         <v>-18040.47114921402</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.170553018344547e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2352.29782171012</v>
+        <v>-13420.74630408899</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -2659,7 +2557,7 @@
         <v>1645.988</v>
       </c>
       <c r="C5" t="n">
-        <v>2020.295075895481</v>
+        <v>725.604729381393</v>
       </c>
       <c r="D5" t="n">
         <v>3.1971e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-16118.50102573419</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.148000360147535e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2324.863946572199</v>
+        <v>504.4511479506959</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.116346977408965e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.821995432473609</v>
+        <v>0.9931986434931952</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1629.336</v>
       </c>
       <c r="C6" t="n">
-        <v>2002.385141513267</v>
+        <v>717.8475471422794</v>
       </c>
       <c r="D6" t="n">
         <v>3.21371e-07</v>
@@ -2745,16 +2640,13 @@
         <v>-13041.40975842422</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.95081126143784e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2298.503304776806</v>
+        <v>524.3377703763264</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.918411780930514e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8221397714155021</v>
+        <v>0.9629445247700987</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1596.888</v>
       </c>
       <c r="C7" t="n">
-        <v>1975.172005524785</v>
+        <v>710.5691770822403</v>
       </c>
       <c r="D7" t="n">
         <v>3.23037e-07</v>
@@ -2798,16 +2690,13 @@
         <v>-12784.78656282724</v>
       </c>
       <c r="Y7" t="n">
-        <v>119.0294440445591</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2227.125863504964</v>
+        <v>514.2408672535411</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.196614208838177e-08</v>
+        <v>1.199469418748951e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8166596150155181</v>
+        <v>0.9957691814468386</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1579.441</v>
       </c>
       <c r="C8" t="n">
-        <v>1958.69036968718</v>
+        <v>703.1405731944894</v>
       </c>
       <c r="D8" t="n">
         <v>3.24435e-07</v>
@@ -2851,16 +2740,13 @@
         <v>-10921.49564717989</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.460346492402929e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2247.267598737305</v>
+        <v>504.2737677243399</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000557e-08</v>
+        <v>1.293300135299958e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8225843157073186</v>
+        <v>0.9950386629393102</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1562.146</v>
       </c>
       <c r="C9" t="n">
-        <v>1939.357780702128</v>
+        <v>696.6743834506924</v>
       </c>
       <c r="D9" t="n">
         <v>3.26033e-07</v>
@@ -2904,16 +2790,13 @@
         <v>-8784.80523251102</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.457567406465911e-13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2222.816833725593</v>
+        <v>491.9458782520906</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.054437546471424e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8228596173478033</v>
+        <v>0.9982207102058634</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1542.601</v>
       </c>
       <c r="C10" t="n">
-        <v>1919.144399165686</v>
+        <v>16006.59057836639</v>
       </c>
       <c r="D10" t="n">
         <v>3.2751e-07</v>
@@ -2957,10 +2840,7 @@
         <v>-7147.062839848233</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.549132589095633e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2199.248690266319</v>
+        <v>-13828.62082597449</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000036e-08</v>
@@ -2977,7 +2857,7 @@
         <v>1525.781</v>
       </c>
       <c r="C11" t="n">
-        <v>1900.682596455563</v>
+        <v>687.274522582303</v>
       </c>
       <c r="D11" t="n">
         <v>3.28981e-07</v>
@@ -3010,16 +2890,13 @@
         <v>-5613.012241345244</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.156015966963722e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2176.297211736432</v>
+        <v>504.4963415007163</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.293182408017821e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8234597107321138</v>
+        <v>0.9910667134067463</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2907,7 @@
         <v>1504.315</v>
       </c>
       <c r="C12" t="n">
-        <v>1880.305804373608</v>
+        <v>15055.09507841204</v>
       </c>
       <c r="D12" t="n">
         <v>3.30459e-07</v>
@@ -3063,10 +2940,7 @@
         <v>-5166.964550673434</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.770800010249129e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2154.008670540396</v>
+        <v>-12907.36867536205</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000002e-08</v>
@@ -3083,7 +2957,7 @@
         <v>1486.375</v>
       </c>
       <c r="C13" t="n">
-        <v>1862.778728723531</v>
+        <v>15459.3431375184</v>
       </c>
       <c r="D13" t="n">
         <v>3.31745e-07</v>
@@ -3116,10 +2990,7 @@
         <v>-3707.166244170628</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.582474068052654e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2132.535168681811</v>
+        <v>-13336.4285175279</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000368e-08</v>
@@ -3136,7 +3007,7 @@
         <v>1466.53</v>
       </c>
       <c r="C14" t="n">
-        <v>1843.816574812802</v>
+        <v>672.1731279158143</v>
       </c>
       <c r="D14" t="n">
         <v>3.33128e-07</v>
@@ -3169,16 +3040,13 @@
         <v>-3319.740469582753</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.699911127128245e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2111.570456908615</v>
+        <v>490.250064191011</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000115e-08</v>
+        <v>1.209675136856545e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8244241756078227</v>
+        <v>0.9990414456239499</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3057,7 @@
         <v>1453.219</v>
       </c>
       <c r="C15" t="n">
-        <v>1831.451831078917</v>
+        <v>14778.41487805173</v>
       </c>
       <c r="D15" t="n">
         <v>3.34492e-07</v>
@@ -3222,10 +3090,7 @@
         <v>-155.2162001030414</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.891140401836062e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2091.07144806103</v>
+        <v>-12685.24139645671</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -3242,7 +3107,7 @@
         <v>1433.583</v>
       </c>
       <c r="C16" t="n">
-        <v>1812.413390085947</v>
+        <v>14392.28412721401</v>
       </c>
       <c r="D16" t="n">
         <v>3.35929e-07</v>
@@ -3275,10 +3140,7 @@
         <v>499.2140144648812</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.985272942773469e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2070.557646823435</v>
+        <v>-12313.52495591631</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -3295,7 +3157,7 @@
         <v>1417.403</v>
       </c>
       <c r="C17" t="n">
-        <v>1796.747461141449</v>
+        <v>13941.82139675493</v>
       </c>
       <c r="D17" t="n">
         <v>3.37169e-07</v>
@@ -3328,10 +3190,7 @@
         <v>2155.805052559103</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.452523814215023e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2050.48155539346</v>
+        <v>-11875.27300120643</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000008798e-08</v>
@@ -3348,7 +3207,7 @@
         <v>1403.068</v>
       </c>
       <c r="C18" t="n">
-        <v>1782.260272155784</v>
+        <v>14059.87581334919</v>
       </c>
       <c r="D18" t="n">
         <v>3.38357e-07</v>
@@ -3381,10 +3240,7 @@
         <v>2697.432087641368</v>
       </c>
       <c r="Y18" t="n">
-        <v>107.908199366633</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2143.401149902774</v>
+        <v>-12012.30284170895</v>
       </c>
       <c r="AA18" t="n">
         <v>1.645355878914446e-08</v>
@@ -3401,7 +3257,7 @@
         <v>1392.533</v>
       </c>
       <c r="C19" t="n">
-        <v>1769.760248003048</v>
+        <v>14175.50708510583</v>
       </c>
       <c r="D19" t="n">
         <v>3.39616e-07</v>
@@ -3434,10 +3290,7 @@
         <v>7086.759727820572</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.107918707631474e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2011.351659247111</v>
+        <v>-12147.71821909612</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3454,7 +3307,7 @@
         <v>1377.431</v>
       </c>
       <c r="C20" t="n">
-        <v>1753.173570453875</v>
+        <v>14248.59230315142</v>
       </c>
       <c r="D20" t="n">
         <v>3.40596e-07</v>
@@ -3487,10 +3340,7 @@
         <v>7303.129144768417</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.847758214541238e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1991.949668606389</v>
+        <v>-12238.00953567365</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -3507,7 +3357,7 @@
         <v>1358.738</v>
       </c>
       <c r="C21" t="n">
-        <v>1736.692461542023</v>
+        <v>13253.0056858478</v>
       </c>
       <c r="D21" t="n">
         <v>3.42004e-07</v>
@@ -3540,10 +3390,7 @@
         <v>7082.456086213839</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.178067897774014e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1972.547613987283</v>
+        <v>-11245.83800324593</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3560,7 +3407,7 @@
         <v>1345.235</v>
       </c>
       <c r="C22" t="n">
-        <v>1721.743842360765</v>
+        <v>13369.31997474113</v>
       </c>
       <c r="D22" t="n">
         <v>3.43202e-07</v>
@@ -3593,10 +3440,7 @@
         <v>8562.696830682264</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.129758966349955e-12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1952.730681313109</v>
+        <v>-11382.23033871197</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -3759,7 +3603,7 @@
         <v>2170.048</v>
       </c>
       <c r="C2" t="n">
-        <v>2638.566975843747</v>
+        <v>13483.52522499638</v>
       </c>
       <c r="D2" t="n">
         <v>2.74941e-07</v>
@@ -3792,10 +3636,7 @@
         <v>-25281.55929627744</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.868591856394237e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2873.051711335656</v>
+        <v>-10542.13785589595</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000338e-08</v>
@@ -3812,7 +3653,7 @@
         <v>1863.008</v>
       </c>
       <c r="C3" t="n">
-        <v>2259.377683196543</v>
+        <v>15588.44255235817</v>
       </c>
       <c r="D3" t="n">
         <v>3.06186e-07</v>
@@ -3845,10 +3686,7 @@
         <v>-31411.76374128252</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.386941090141653e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2576.664866082346</v>
+        <v>-13043.49356660835</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000031913e-08</v>
@@ -3865,7 +3703,7 @@
         <v>1771.989</v>
       </c>
       <c r="C4" t="n">
-        <v>2165.72826407297</v>
+        <v>14892.1087647727</v>
       </c>
       <c r="D4" t="n">
         <v>3.12655e-07</v>
@@ -3898,10 +3736,7 @@
         <v>-25036.39938591619</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.67126040680553e-13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2500.221549416978</v>
+        <v>-12430.20586761987</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3918,7 +3753,7 @@
         <v>1740.698</v>
       </c>
       <c r="C5" t="n">
-        <v>2134.537846059957</v>
+        <v>15564.48053343707</v>
       </c>
       <c r="D5" t="n">
         <v>3.14783e-07</v>
@@ -3951,10 +3786,7 @@
         <v>-24126.26652424969</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.589610258755812e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2459.790101126679</v>
+        <v>-13151.13941851929</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000036e-08</v>
@@ -3971,7 +3803,7 @@
         <v>1713.602</v>
       </c>
       <c r="C6" t="n">
-        <v>2108.027874267371</v>
+        <v>753.9709258758684</v>
       </c>
       <c r="D6" t="n">
         <v>3.16504e-07</v>
@@ -4004,16 +3836,13 @@
         <v>-20255.63900181402</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.359960949912924e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2426.847221845132</v>
+        <v>529.8690328616109</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.039853657609148e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8179900902547043</v>
+        <v>0.9965095206460818</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1679.236</v>
       </c>
       <c r="C7" t="n">
-        <v>2077.577671332773</v>
+        <v>744.3475014268759</v>
       </c>
       <c r="D7" t="n">
         <v>3.17977e-07</v>
@@ -4057,16 +3886,13 @@
         <v>-16838.39833609839</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.760370553760807e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2396.315984342618</v>
+        <v>537.1190776304931</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.147185319599167e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8181250873035871</v>
+        <v>0.9989650589783265</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1659.663</v>
       </c>
       <c r="C8" t="n">
-        <v>2058.516417802642</v>
+        <v>14602.57525057932</v>
       </c>
       <c r="D8" t="n">
         <v>3.195e-07</v>
@@ -4110,10 +3936,7 @@
         <v>-13700.94313990342</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.846590310715652e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2366.057565798163</v>
+        <v>-12265.66767304473</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000005845e-08</v>
@@ -4130,7 +3953,7 @@
         <v>1626.902</v>
       </c>
       <c r="C9" t="n">
-        <v>2030.858335645932</v>
+        <v>14892.13270025098</v>
       </c>
       <c r="D9" t="n">
         <v>3.2094e-07</v>
@@ -4163,10 +3986,7 @@
         <v>-12385.14499795848</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.821215079699915e-13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2336.223801284917</v>
+        <v>-12584.84046173146</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4183,7 +4003,7 @@
         <v>1609.305</v>
       </c>
       <c r="C10" t="n">
-        <v>2011.305554211372</v>
+        <v>718.6961286401009</v>
       </c>
       <c r="D10" t="n">
         <v>3.22689e-07</v>
@@ -4216,16 +4036,13 @@
         <v>-6457.358030293683</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.885640927781418e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2308.217256683847</v>
+        <v>539.3650790705549</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000305e-08</v>
+        <v>1.453562420326199e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8187564695416385</v>
+        <v>0.9842184565395946</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1576.191</v>
       </c>
       <c r="C11" t="n">
-        <v>1983.181267054139</v>
+        <v>15477.84719749742</v>
       </c>
       <c r="D11" t="n">
         <v>3.23942e-07</v>
@@ -4269,10 +4086,7 @@
         <v>-9193.045938178606</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.555662023802641e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2280.936781745298</v>
+        <v>-13228.03000504263</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4435,7 +4249,7 @@
         <v>1770.221</v>
       </c>
       <c r="C2" t="n">
-        <v>2217.008184803722</v>
+        <v>15438.4900824518</v>
       </c>
       <c r="D2" t="n">
         <v>3.10092e-07</v>
@@ -4468,10 +4282,7 @@
         <v>-25270.9745077079</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.309946678020667e-13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2485.610650043614</v>
+        <v>-12932.45103870763</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4488,7 +4299,7 @@
         <v>1647.525</v>
       </c>
       <c r="C3" t="n">
-        <v>2068.531982575427</v>
+        <v>15241.163969195</v>
       </c>
       <c r="D3" t="n">
         <v>3.21803e-07</v>
@@ -4521,10 +4332,7 @@
         <v>-26112.59757183991</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.073045540896301e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2372.172733323586</v>
+        <v>-12886.11024192589</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -4541,7 +4349,7 @@
         <v>1609.344</v>
       </c>
       <c r="C4" t="n">
-        <v>2028.468404671067</v>
+        <v>724.3803662864003</v>
       </c>
       <c r="D4" t="n">
         <v>3.24336e-07</v>
@@ -4574,16 +4382,13 @@
         <v>-24600.01779766982</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.824996657782406e-13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2331.549221204692</v>
+        <v>566.8637219329694</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.373532305625376e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.817120919156286</v>
+        <v>0.9827430781512515</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1577.062</v>
       </c>
       <c r="C5" t="n">
-        <v>1998.43950285299</v>
+        <v>715.5761329662201</v>
       </c>
       <c r="D5" t="n">
         <v>3.26052e-07</v>
@@ -4627,16 +4432,13 @@
         <v>-21330.64729598035</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.555386667669817e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2299.858461579325</v>
+        <v>552.7480260008523</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001449e-08</v>
+        <v>1.499013310781591e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8172209515700588</v>
+        <v>0.9799041343612945</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1558.979</v>
       </c>
       <c r="C6" t="n">
-        <v>1978.690397929426</v>
+        <v>15513.83680795956</v>
       </c>
       <c r="D6" t="n">
         <v>3.27741e-07</v>
@@ -4680,10 +4482,7 @@
         <v>-20424.20110545467</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.109190749550578e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2270.18104004765</v>
+        <v>-13266.96467993241</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001782e-08</v>
@@ -4700,7 +4499,7 @@
         <v>1538.572</v>
       </c>
       <c r="C7" t="n">
-        <v>1957.891608196941</v>
+        <v>700.7047960888885</v>
       </c>
       <c r="D7" t="n">
         <v>3.29345e-07</v>
@@ -4733,16 +4532,13 @@
         <v>-18922.24803844098</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.549341362568593e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2241.100628829656</v>
+        <v>546.2795878508169</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.00000000000012e-08</v>
+        <v>1.146345443043199e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8176183870949866</v>
+        <v>0.9961066079619373</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1510.204</v>
       </c>
       <c r="C8" t="n">
-        <v>1932.999833010673</v>
+        <v>583.9394368765711</v>
       </c>
       <c r="D8" t="n">
         <v>3.30995e-07</v>
@@ -4786,16 +4582,13 @@
         <v>-16423.55133321817</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.402424305082267e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2212.917017104517</v>
+        <v>755.5733265375097</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000056e-08</v>
+        <v>1.481160826783407e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8178760123260773</v>
+        <v>0.8630131993453879</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1482.629</v>
       </c>
       <c r="C9" t="n">
-        <v>1906.888542324745</v>
+        <v>586.3747693000948</v>
       </c>
       <c r="D9" t="n">
         <v>3.32603e-07</v>
@@ -4839,16 +4632,13 @@
         <v>-15080.72249101161</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.053972134084737e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2186.593551621414</v>
+        <v>720.5917757758928</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.764957880085677e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8181415408158662</v>
+        <v>0.840720739296594</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1467.942</v>
       </c>
       <c r="C10" t="n">
-        <v>1891.350105230444</v>
+        <v>586.1396413140935</v>
       </c>
       <c r="D10" t="n">
         <v>3.34092e-07</v>
@@ -4892,16 +4682,13 @@
         <v>-12558.12680005444</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.260525917041039e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2162.173723793554</v>
+        <v>638.1492308831154</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000203e-08</v>
+        <v>1.492018431504286e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8184015568674078</v>
+        <v>0.9989165595291458</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1443.448</v>
       </c>
       <c r="C11" t="n">
-        <v>1867.741964053769</v>
+        <v>587.0591152443805</v>
       </c>
       <c r="D11" t="n">
         <v>3.35646e-07</v>
@@ -4945,16 +4732,13 @@
         <v>-11034.92547586477</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.567745128575015e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2138.299674143591</v>
+        <v>622.6398003077854</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000022e-08</v>
+        <v>1.701854951799272e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8186827246611407</v>
+        <v>0.9928606136899054</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4749,7 @@
         <v>1420.421</v>
       </c>
       <c r="C12" t="n">
-        <v>1846.25238494473</v>
+        <v>586.8784605890859</v>
       </c>
       <c r="D12" t="n">
         <v>3.36976e-07</v>
@@ -4998,16 +4782,13 @@
         <v>-10454.22567970742</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.389039415977951e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2115.391337621069</v>
+        <v>615.5199826740979</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000225e-08</v>
+        <v>1.371811971775096e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8189838946749735</v>
+        <v>0.9995400279692278</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4799,7 @@
         <v>1413.051</v>
       </c>
       <c r="C13" t="n">
-        <v>1833.671179969087</v>
+        <v>15237.04258980093</v>
       </c>
       <c r="D13" t="n">
         <v>3.3863e-07</v>
@@ -5051,10 +4832,7 @@
         <v>-4258.023366482982</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.155813984957102e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2092.927651858601</v>
+        <v>-13151.63921776254</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000008e-08</v>
@@ -5071,7 +4849,7 @@
         <v>1386.372</v>
       </c>
       <c r="C14" t="n">
-        <v>1811.403429574767</v>
+        <v>587.852028919268</v>
       </c>
       <c r="D14" t="n">
         <v>3.40057e-07</v>
@@ -5104,16 +4882,13 @@
         <v>-6855.007206655303</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.822896123862566e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2071.226138550229</v>
+        <v>611.7700336725101</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>1.509926447326293e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8196027443072182</v>
+        <v>0.9983004658422785</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4899,7 @@
         <v>1377.975</v>
       </c>
       <c r="C15" t="n">
-        <v>1798.854039583229</v>
+        <v>588.0392429854816</v>
       </c>
       <c r="D15" t="n">
         <v>3.41422e-07</v>
@@ -5157,16 +4932,13 @@
         <v>-1115.674699726089</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.04175754828238e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2050.369855721834</v>
+        <v>608.5035624212878</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>1.829446288885213e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8199163450473048</v>
+        <v>0.9838849867120502</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1351.625</v>
       </c>
       <c r="C16" t="n">
-        <v>1776.547617350616</v>
+        <v>14975.78491816788</v>
       </c>
       <c r="D16" t="n">
         <v>3.42764e-07</v>
@@ -5210,10 +4982,7 @@
         <v>-3000.043639337012</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.892824235530616e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2029.181306073275</v>
+        <v>-12945.86411642996</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5230,7 +4999,7 @@
         <v>1336.306</v>
       </c>
       <c r="C17" t="n">
-        <v>1760.461068443667</v>
+        <v>14390.22454033957</v>
       </c>
       <c r="D17" t="n">
         <v>3.4415e-07</v>
@@ -5263,10 +5032,7 @@
         <v>-1248.498711361743</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.240231171114659e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2008.1894650394</v>
+        <v>-12372.31980492303</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5283,7 +5049,7 @@
         <v>1330.848</v>
       </c>
       <c r="C18" t="n">
-        <v>1749.426332727932</v>
+        <v>14444.80060105272</v>
       </c>
       <c r="D18" t="n">
         <v>3.45598e-07</v>
@@ -5316,10 +5082,7 @@
         <v>6505.740889531367</v>
       </c>
       <c r="Y18" t="n">
-        <v>465.5936907559623</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1743.016283833224</v>
+        <v>-12447.05522842174</v>
       </c>
       <c r="AA18" t="n">
         <v>1.988629627763726e-08</v>
@@ -5336,7 +5099,7 @@
         <v>1305.144</v>
       </c>
       <c r="C19" t="n">
-        <v>1726.563335698608</v>
+        <v>14678.36913050407</v>
       </c>
       <c r="D19" t="n">
         <v>3.46799e-07</v>
@@ -5369,10 +5132,7 @@
         <v>1616.698489650714</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.787366203060401e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1967.176560805307</v>
+        <v>-12701.51036029127</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -5389,7 +5149,7 @@
         <v>1293.338</v>
       </c>
       <c r="C20" t="n">
-        <v>1713.861849146121</v>
+        <v>14276.38797132646</v>
       </c>
       <c r="D20" t="n">
         <v>3.48343e-07</v>
@@ -5422,10 +5182,7 @@
         <v>6905.369524495869</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.102194484601837e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1947.229307023899</v>
+        <v>-12313.75823815218</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -5442,7 +5199,7 @@
         <v>1281.105</v>
       </c>
       <c r="C21" t="n">
-        <v>1697.734957059718</v>
+        <v>13832.98683479592</v>
       </c>
       <c r="D21" t="n">
         <v>3.49556e-07</v>
@@ -5475,10 +5232,7 @@
         <v>7829.0071820168</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.799349272414639e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1927.511229689941</v>
+        <v>-11881.18331838315</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5495,7 +5249,7 @@
         <v>1261.615</v>
       </c>
       <c r="C22" t="n">
-        <v>1680.352044435787</v>
+        <v>13439.10002797133</v>
       </c>
       <c r="D22" t="n">
         <v>3.50962e-07</v>
@@ -5528,10 +5282,7 @@
         <v>7876.847570079973</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.579989602858862e-12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1907.721475918999</v>
+        <v>-11500.49309126698</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5694,7 +5445,7 @@
         <v>2010.608</v>
       </c>
       <c r="C2" t="n">
-        <v>2488.187217156694</v>
+        <v>13204.60831924</v>
       </c>
       <c r="D2" t="n">
         <v>2.88254e-07</v>
@@ -5727,10 +5478,7 @@
         <v>-21927.33982403725</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.531754418550794e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2682.331075286985</v>
+        <v>-10416.25060547603</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000009e-08</v>
@@ -5747,7 +5495,7 @@
         <v>1720.705</v>
       </c>
       <c r="C3" t="n">
-        <v>2120.719521190824</v>
+        <v>14934.29821424264</v>
       </c>
       <c r="D3" t="n">
         <v>3.20864e-07</v>
@@ -5780,10 +5528,7 @@
         <v>-27183.68093179626</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.567543483768303e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2418.552936682619</v>
+        <v>-12519.88859633902</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000131e-08</v>
@@ -5800,7 +5545,7 @@
         <v>1642.312</v>
       </c>
       <c r="C4" t="n">
-        <v>2041.481979996777</v>
+        <v>14563.99961644723</v>
       </c>
       <c r="D4" t="n">
         <v>3.26903e-07</v>
@@ -5833,10 +5578,7 @@
         <v>-23542.6158993587</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.414655296836617e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2351.00434950218</v>
+        <v>-12229.27013488815</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001422e-08</v>
@@ -5853,7 +5595,7 @@
         <v>1612.218</v>
       </c>
       <c r="C5" t="n">
-        <v>2009.385546974985</v>
+        <v>15249.14711695653</v>
       </c>
       <c r="D5" t="n">
         <v>3.29217e-07</v>
@@ -5886,10 +5628,7 @@
         <v>-22889.88801247129</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.074252383869141e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2311.64343558264</v>
+        <v>-12963.52868506071</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000516e-08</v>
@@ -5906,7 +5645,7 @@
         <v>1581.77</v>
       </c>
       <c r="C6" t="n">
-        <v>1981.768243524108</v>
+        <v>708.9536801433233</v>
       </c>
       <c r="D6" t="n">
         <v>3.30891e-07</v>
@@ -5939,16 +5678,13 @@
         <v>-20227.34755178795</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.219845479983952e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2277.875356554868</v>
+        <v>535.4779977713705</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000001422e-08</v>
+        <v>1.43383695751599e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8194427593292148</v>
+        <v>0.9852733769143368</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1548.466</v>
       </c>
       <c r="C7" t="n">
-        <v>1954.075724428917</v>
+        <v>14971.54347353232</v>
       </c>
       <c r="D7" t="n">
         <v>3.32649e-07</v>
@@ -5992,10 +5728,7 @@
         <v>-16713.45949904044</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.954266480573372e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2245.355227051818</v>
+        <v>-12747.14468417771</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000009e-08</v>
@@ -6012,7 +5745,7 @@
         <v>1524.622</v>
       </c>
       <c r="C8" t="n">
-        <v>1928.244455604551</v>
+        <v>692.3844604122884</v>
       </c>
       <c r="D8" t="n">
         <v>3.34175e-07</v>
@@ -6045,16 +5778,13 @@
         <v>-14842.73348834367</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.495896350373366e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2214.379935668665</v>
+        <v>518.7893354068352</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000007262e-08</v>
+        <v>1.275212486643369e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8198366291058186</v>
+        <v>0.9931065138027134</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1496.33</v>
       </c>
       <c r="C9" t="n">
-        <v>1904.093996290159</v>
+        <v>684.3596299205861</v>
       </c>
       <c r="D9" t="n">
         <v>3.35994e-07</v>
@@ -6098,16 +5828,13 @@
         <v>-12651.22439576775</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.516199958612458e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2184.161441616359</v>
+        <v>518.2068062608658</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000002123e-08</v>
+        <v>1.076381719250729e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.820084251692327</v>
+        <v>0.9983594974367569</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1472.461</v>
       </c>
       <c r="C10" t="n">
-        <v>1880.159041288339</v>
+        <v>677.0608782861307</v>
       </c>
       <c r="D10" t="n">
         <v>3.37649e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-9955.161489567143</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.243334346150276e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2155.090664404788</v>
+        <v>514.3408646437413</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.110022628583849e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8203513308286863</v>
+        <v>0.9987269657691619</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1454.528</v>
       </c>
       <c r="C11" t="n">
-        <v>1861.744587009153</v>
+        <v>14972.07944612777</v>
       </c>
       <c r="D11" t="n">
         <v>3.3946e-07</v>
@@ -6204,10 +5928,7 @@
         <v>-6556.328123392039</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.59161761483623e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2127.584134469996</v>
+        <v>-12856.94362460996</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000035e-08</v>
@@ -6370,7 +6091,7 @@
         <v>1754.182</v>
       </c>
       <c r="C2" t="n">
-        <v>2181.823583035389</v>
+        <v>14400.32843878396</v>
       </c>
       <c r="D2" t="n">
         <v>3.14633e-07</v>
@@ -6403,10 +6124,7 @@
         <v>-26266.44067188984</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.81803029116612e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2450.505382732978</v>
+        <v>-11922.21130409927</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -6423,7 +6141,7 @@
         <v>1632.782</v>
       </c>
       <c r="C3" t="n">
-        <v>2040.649786075043</v>
+        <v>14940.49649305138</v>
       </c>
       <c r="D3" t="n">
         <v>3.251e-07</v>
@@ -6456,10 +6174,7 @@
         <v>-23409.50289409664</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.085923516628149e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2347.688636653309</v>
+        <v>-12609.11630347354</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000184e-08</v>
@@ -6476,7 +6191,7 @@
         <v>1602.448</v>
       </c>
       <c r="C4" t="n">
-        <v>2006.74377425686</v>
+        <v>15771.4748926176</v>
       </c>
       <c r="D4" t="n">
         <v>3.27513e-07</v>
@@ -6509,10 +6224,7 @@
         <v>-22255.7748838759</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.265186523582785e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2309.481426074799</v>
+        <v>-13492.44183598181</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6529,7 +6241,7 @@
         <v>1576.056</v>
       </c>
       <c r="C5" t="n">
-        <v>1983.081242921831</v>
+        <v>14712.28059143698</v>
       </c>
       <c r="D5" t="n">
         <v>3.29049e-07</v>
@@ -6562,10 +6274,7 @@
         <v>-19500.89224602438</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.073219316667966e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2279.789276511653</v>
+        <v>-12451.53021782439</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -6582,7 +6291,7 @@
         <v>1557.45</v>
       </c>
       <c r="C6" t="n">
-        <v>1962.851284996393</v>
+        <v>702.5121216582867</v>
       </c>
       <c r="D6" t="n">
         <v>3.30636e-07</v>
@@ -6615,16 +6324,13 @@
         <v>-17734.64062313891</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.298161265587734e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2251.031850161536</v>
+        <v>527.7395435079732</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000003917e-08</v>
+        <v>1.085258736062588e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8187058255063128</v>
+        <v>0.998709130767064</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1521.223</v>
       </c>
       <c r="C7" t="n">
-        <v>1934.390900264862</v>
+        <v>15359.1992173104</v>
       </c>
       <c r="D7" t="n">
         <v>3.32519e-07</v>
@@ -6668,10 +6374,7 @@
         <v>-15418.20997681798</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.042972965399277e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2222.276373719201</v>
+        <v>-13158.49467151458</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000002e-08</v>
@@ -6688,7 +6391,7 @@
         <v>1501.749</v>
       </c>
       <c r="C8" t="n">
-        <v>1913.585525197995</v>
+        <v>687.5667510129019</v>
       </c>
       <c r="D8" t="n">
         <v>3.34312e-07</v>
@@ -6721,16 +6424,13 @@
         <v>-13086.25996492417</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.933617990239786e-13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2194.046159524713</v>
+        <v>535.224621703731</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.135444878326606e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8191920538596626</v>
+        <v>0.9991223116703301</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1476.246</v>
       </c>
       <c r="C9" t="n">
-        <v>1888.708046471417</v>
+        <v>681.1066459517169</v>
       </c>
       <c r="D9" t="n">
         <v>3.3612e-07</v>
@@ -6774,16 +6474,13 @@
         <v>-12093.72838407259</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.263239373616513e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2166.462163373291</v>
+        <v>534.4265081609258</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000004362e-08</v>
+        <v>1.557207870327161e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8194635650255985</v>
+        <v>0.979705448789327</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1455.254</v>
       </c>
       <c r="C10" t="n">
-        <v>1866.698473035864</v>
+        <v>576.1330495152583</v>
       </c>
       <c r="D10" t="n">
         <v>3.37954e-07</v>
@@ -6827,16 +6524,13 @@
         <v>-10551.16107144091</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.740060517801523e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2139.724830477282</v>
+        <v>721.9353721100846</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.393927436695554e-08</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8197604937916433</v>
+        <v>0.8673436035511763</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1431.631</v>
       </c>
       <c r="C11" t="n">
-        <v>1847.583463993273</v>
+        <v>15109.00224071193</v>
       </c>
       <c r="D11" t="n">
         <v>3.39762e-07</v>
@@ -6880,10 +6574,7 @@
         <v>-8339.406866685262</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.888759237023528e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2114.494610485073</v>
+        <v>-13005.24388174137</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6900,7 +6591,7 @@
         <v>1414.23</v>
       </c>
       <c r="C12" t="n">
-        <v>1828.027322595682</v>
+        <v>577.2600259406038</v>
       </c>
       <c r="D12" t="n">
         <v>3.41496e-07</v>
@@ -6933,16 +6624,13 @@
         <v>-6528.484747240417</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.693809161777374e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2090.244748072032</v>
+        <v>653.5886032445602</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000001333e-08</v>
+        <v>8.168537299661064e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8203531302882033</v>
+        <v>0.8843665872633597</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1395.136</v>
       </c>
       <c r="C13" t="n">
-        <v>1806.991798334985</v>
+        <v>578.1715297626305</v>
       </c>
       <c r="D13" t="n">
         <v>3.43213e-07</v>
@@ -6986,16 +6674,13 @@
         <v>-4907.951170024037</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.391034973962976e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2066.446967194479</v>
+        <v>613.4201513619859</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000208e-08</v>
+        <v>1.954659404463989e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8206453582175531</v>
+        <v>0.9804789262718624</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1371.555</v>
       </c>
       <c r="C14" t="n">
-        <v>1787.206329023053</v>
+        <v>13874.46435825728</v>
       </c>
       <c r="D14" t="n">
         <v>3.44883e-07</v>
@@ -7039,10 +6724,7 @@
         <v>-4011.884611853175</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.300316489939316e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2044.275253061377</v>
+        <v>-11821.20653926614</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000009e-08</v>
@@ -7059,7 +6741,7 @@
         <v>1353.532</v>
       </c>
       <c r="C15" t="n">
-        <v>1768.142256051785</v>
+        <v>14156.13839918438</v>
       </c>
       <c r="D15" t="n">
         <v>3.46501e-07</v>
@@ -7092,10 +6774,7 @@
         <v>-2001.451557276632</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.191286456926767e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2022.474701616153</v>
+        <v>-12127.27968614107</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -7112,7 +6791,7 @@
         <v>1343.273</v>
       </c>
       <c r="C16" t="n">
-        <v>1753.974413991728</v>
+        <v>13529.10302466671</v>
       </c>
       <c r="D16" t="n">
         <v>3.48013e-07</v>
@@ -7145,10 +6824,7 @@
         <v>1401.696019463868</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.182612958551111e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2000.97871736425</v>
+        <v>-11511.04303987523</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -7165,7 +6841,7 @@
         <v>1321.571</v>
       </c>
       <c r="C17" t="n">
-        <v>1733.439058392677</v>
+        <v>13778.21815166641</v>
       </c>
       <c r="D17" t="n">
         <v>3.49666e-07</v>
@@ -7198,10 +6874,7 @@
         <v>1872.9110975536</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.711685474233437e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1979.544298344718</v>
+        <v>-11784.31057169662</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -7218,7 +6891,7 @@
         <v>1311.858</v>
       </c>
       <c r="C18" t="n">
-        <v>1720.773387495169</v>
+        <v>13249.44205690319</v>
       </c>
       <c r="D18" t="n">
         <v>3.51121e-07</v>
@@ -7251,10 +6924,7 @@
         <v>5169.994898817462</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.799914322032931e-11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1958.74119708094</v>
+        <v>-11266.52194006772</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -7271,7 +6941,7 @@
         <v>1295.136</v>
       </c>
       <c r="C19" t="n">
-        <v>1705.620746222601</v>
+        <v>12978.54066123045</v>
       </c>
       <c r="D19" t="n">
         <v>3.5255e-07</v>
@@ -7304,10 +6974,7 @@
         <v>7053.334562523114</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.688386246057792e-12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1937.588282522877</v>
+        <v>-11011.07213566305</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -7324,7 +6991,7 @@
         <v>1280.185</v>
       </c>
       <c r="C20" t="n">
-        <v>1689.417897437787</v>
+        <v>13110.94449118068</v>
       </c>
       <c r="D20" t="n">
         <v>3.54098e-07</v>
@@ -7357,10 +7024,7 @@
         <v>8779.037450271646</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.76441651384682e-12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1916.581456870169</v>
+        <v>-11164.85139492709</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -7377,7 +7041,7 @@
         <v>1258.87</v>
       </c>
       <c r="C21" t="n">
-        <v>1671.737387785594</v>
+        <v>12736.91453451963</v>
       </c>
       <c r="D21" t="n">
         <v>3.55608e-07</v>
@@ -7410,10 +7074,7 @@
         <v>7825.69187997649</v>
       </c>
       <c r="Y21" t="n">
-        <v>461.2513999276247</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1696.838879881661</v>
+        <v>-10803.90066420787</v>
       </c>
       <c r="AA21" t="n">
         <v>1.754721301734316e-08</v>
@@ -7430,7 +7091,7 @@
         <v>1243.613</v>
       </c>
       <c r="C22" t="n">
-        <v>1655.201138344873</v>
+        <v>12874.51097831462</v>
       </c>
       <c r="D22" t="n">
         <v>3.57192e-07</v>
@@ -7463,10 +7124,7 @@
         <v>-5830.555360614539</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.467865674446815e-11</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1875.43471340691</v>
+        <v>-10963.31231103651</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -7629,7 +7287,7 @@
         <v>1974.047</v>
       </c>
       <c r="C2" t="n">
-        <v>2415.099627131626</v>
+        <v>12852.42630091122</v>
       </c>
       <c r="D2" t="n">
         <v>2.94187e-07</v>
@@ -7662,10 +7320,7 @@
         <v>-22388.80319877982</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.040828909659335e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2591.399615200155</v>
+        <v>-10129.47705952446</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000005124e-08</v>
@@ -7682,7 +7337,7 @@
         <v>1669.798</v>
       </c>
       <c r="C3" t="n">
-        <v>2039.931030640798</v>
+        <v>14939.51282747643</v>
       </c>
       <c r="D3" t="n">
         <v>3.27898e-07</v>
@@ -7715,10 +7370,7 @@
         <v>-26396.60937732317</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.883353722665607e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2321.20835883814</v>
+        <v>-12612.16584924851</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000022e-08</v>
@@ -7735,7 +7387,7 @@
         <v>1601.145</v>
       </c>
       <c r="C4" t="n">
-        <v>1967.588397631326</v>
+        <v>16017.56544145518</v>
       </c>
       <c r="D4" t="n">
         <v>3.33221e-07</v>
@@ -7768,10 +7420,7 @@
         <v>-22842.82970925371</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.410196628143468e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2253.115139858811</v>
+        <v>-13784.92058485734</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -7788,7 +7437,7 @@
         <v>1569.926</v>
       </c>
       <c r="C5" t="n">
-        <v>1932.88505797966</v>
+        <v>14177.64030589779</v>
       </c>
       <c r="D5" t="n">
         <v>3.35217e-07</v>
@@ -7821,10 +7470,7 @@
         <v>-16938.41615410658</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.355990394307768e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2213.466860077176</v>
+        <v>-11968.47706269392</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000068331e-08</v>
@@ -7841,7 +7487,7 @@
         <v>1533.049</v>
       </c>
       <c r="C6" t="n">
-        <v>1900.743158813034</v>
+        <v>14587.32621711396</v>
       </c>
       <c r="D6" t="n">
         <v>3.36806e-07</v>
@@ -7874,10 +7520,7 @@
         <v>-13298.13547812229</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.743619582382439e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2179.268045470058</v>
+        <v>-12415.18643040783</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000063e-08</v>
@@ -7894,7 +7537,7 @@
         <v>1502.28</v>
       </c>
       <c r="C7" t="n">
-        <v>1872.726034253964</v>
+        <v>16085.53384864354</v>
       </c>
       <c r="D7" t="n">
         <v>3.38812e-07</v>
@@ -7927,10 +7570,7 @@
         <v>-10260.82528673172</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.470805315339147e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2146.054531081825</v>
+        <v>-13960.72857358604</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000087e-08</v>
@@ -7947,7 +7587,7 @@
         <v>1469.375</v>
       </c>
       <c r="C8" t="n">
-        <v>1846.28784329965</v>
+        <v>14252.06891795928</v>
       </c>
       <c r="D8" t="n">
         <v>3.40612e-07</v>
@@ -7980,10 +7620,7 @@
         <v>-7605.695436689388</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.780358642101849e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2114.055675517818</v>
+        <v>-12137.04347094299</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000025e-08</v>
@@ -8000,7 +7637,7 @@
         <v>1444.824</v>
       </c>
       <c r="C9" t="n">
-        <v>1822.796514274516</v>
+        <v>15535.74500287473</v>
       </c>
       <c r="D9" t="n">
         <v>3.42607e-07</v>
@@ -8033,10 +7670,7 @@
         <v>-5445.0274526308</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.73992650562642e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2082.746494416246</v>
+        <v>-13464.51395073428</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002658e-08</v>
@@ -8053,7 +7687,7 @@
         <v>1421.813</v>
       </c>
       <c r="C10" t="n">
-        <v>1800.000473124783</v>
+        <v>13326.51188644854</v>
       </c>
       <c r="D10" t="n">
         <v>3.44569e-07</v>
@@ -8086,10 +7720,7 @@
         <v>-2702.963308183399</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.498870308889907e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2053.725834070181</v>
+        <v>-11255.07441016674</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -8106,7 +7737,7 @@
         <v>1403.842</v>
       </c>
       <c r="C11" t="n">
-        <v>1781.291563797772</v>
+        <v>13508.79857827323</v>
       </c>
       <c r="D11" t="n">
         <v>3.46292e-07</v>
@@ -8139,10 +7770,7 @@
         <v>1256.841685910484</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.863599503820712e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2026.031721643197</v>
+        <v>-11464.75570632983</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005478e-08</v>
@@ -8305,7 +7933,7 @@
         <v>1753.193</v>
       </c>
       <c r="C2" t="n">
-        <v>2177.629856735957</v>
+        <v>14846.16703824037</v>
       </c>
       <c r="D2" t="n">
         <v>3.14726e-07</v>
@@ -8338,10 +7966,7 @@
         <v>-26828.37751742029</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.945528969817851e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2424.07613736572</v>
+        <v>-12389.87750804695</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000125e-08</v>
@@ -8358,7 +7983,7 @@
         <v>1620.097</v>
       </c>
       <c r="C3" t="n">
-        <v>2022.021685136089</v>
+        <v>718.7829545353895</v>
       </c>
       <c r="D3" t="n">
         <v>3.25872e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-22740.02872814703</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.667653178952902e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2308.935672098836</v>
+        <v>513.0280271116942</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000033749e-08</v>
+        <v>1.029454937620177e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8202379931327785</v>
+        <v>0.9993758256731362</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1586.794</v>
       </c>
       <c r="C4" t="n">
-        <v>1983.840222782687</v>
+        <v>708.2058337643219</v>
       </c>
       <c r="D4" t="n">
         <v>3.28245e-07</v>
@@ -8444,16 +8066,13 @@
         <v>-19956.30977812716</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.462409081477049e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2271.735300960781</v>
+        <v>546.8110818968744</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>2.080156913091757e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8202760045559823</v>
+        <v>0.9580331030472117</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1559.819</v>
       </c>
       <c r="C5" t="n">
-        <v>1961.528565715493</v>
+        <v>700.9348432752289</v>
       </c>
       <c r="D5" t="n">
         <v>3.29792e-07</v>
@@ -8497,16 +8116,13 @@
         <v>-18308.84051384599</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.617557587630218e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2245.239778973065</v>
+        <v>531.943283887285</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000057e-08</v>
+        <v>1.127590887647291e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8203445327519937</v>
+        <v>0.996376418865542</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1534.044</v>
       </c>
       <c r="C6" t="n">
-        <v>1936.530048235078</v>
+        <v>694.3353671803783</v>
       </c>
       <c r="D6" t="n">
         <v>3.31247e-07</v>
@@ -8550,16 +8166,13 @@
         <v>-16694.66620275111</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.437707714253742e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2219.411129374885</v>
+        <v>525.9297676012435</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.384670848165437e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8204929258916049</v>
+        <v>0.9846457390804015</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1518.468</v>
       </c>
       <c r="C7" t="n">
-        <v>1920.664010257213</v>
+        <v>687.728191476942</v>
       </c>
       <c r="D7" t="n">
         <v>3.33109e-07</v>
@@ -8603,16 +8216,13 @@
         <v>-14521.8051493096</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.787847203415164e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2194.750305082619</v>
+        <v>529.7028658406447</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.575623328577527e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8206972511395739</v>
+        <v>0.9798515157879408</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1500.94</v>
       </c>
       <c r="C8" t="n">
-        <v>1902.041843157619</v>
+        <v>15433.15390218332</v>
       </c>
       <c r="D8" t="n">
         <v>3.34663e-07</v>
@@ -8656,10 +8266,7 @@
         <v>-13269.73746493533</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.502112230666082e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2171.177977453772</v>
+        <v>-13272.67967974091</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8676,7 +8283,7 @@
         <v>1481.147</v>
       </c>
       <c r="C9" t="n">
-        <v>1882.131795377778</v>
+        <v>14679.72641404224</v>
       </c>
       <c r="D9" t="n">
         <v>3.36424e-07</v>
@@ -8709,10 +8316,7 @@
         <v>-11214.57245444018</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.176966877862571e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2148.020677728776</v>
+        <v>-12532.59880583419</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000972e-08</v>
@@ -8729,7 +8333,7 @@
         <v>1463.616</v>
       </c>
       <c r="C10" t="n">
-        <v>1865.681548701116</v>
+        <v>670.5735803796205</v>
       </c>
       <c r="D10" t="n">
         <v>3.38049e-07</v>
@@ -8762,16 +8366,13 @@
         <v>-9725.398204445482</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.287214376077713e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2126.353981522449</v>
+        <v>504.4669651813443</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.00000000000074e-08</v>
+        <v>1.124246357922617e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8214255365798371</v>
+        <v>0.9988799477338586</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1440.428</v>
       </c>
       <c r="C11" t="n">
-        <v>1843.582081332437</v>
+        <v>14952.06386967177</v>
       </c>
       <c r="D11" t="n">
         <v>3.39585e-07</v>
@@ -8815,10 +8416,7 @@
         <v>-8935.4587760678</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.291454818469938e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2105.199455352495</v>
+        <v>-12848.3673407017</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000004e-08</v>
@@ -8835,7 +8433,7 @@
         <v>1432.094</v>
       </c>
       <c r="C12" t="n">
-        <v>1830.271970797333</v>
+        <v>563.5690345604278</v>
       </c>
       <c r="D12" t="n">
         <v>3.41123e-07</v>
@@ -8868,16 +8466,13 @@
         <v>-5674.162228133481</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.966514247220899e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2084.414270177135</v>
+        <v>631.9855923326477</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.00000000000003e-08</v>
+        <v>2.355304215175579e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8219854570824879</v>
+        <v>0.9766982648843491</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1409.932</v>
       </c>
       <c r="C13" t="n">
-        <v>1811.046269992676</v>
+        <v>563.8550978981607</v>
       </c>
       <c r="D13" t="n">
         <v>3.42596e-07</v>
@@ -8921,16 +8516,13 @@
         <v>-5368.021292083731</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.083413885404588e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2064.244919235202</v>
+        <v>622.0789440722789</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000098e-08</v>
+        <v>1.836307592875965e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8222747325284969</v>
+        <v>0.9901871102215074</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1382.546</v>
       </c>
       <c r="C14" t="n">
-        <v>1789.446639315326</v>
+        <v>14519.17829925917</v>
       </c>
       <c r="D14" t="n">
         <v>3.44129e-07</v>
@@ -8974,10 +8566,7 @@
         <v>-6107.818877749405</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.927002076461528e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2044.298649405384</v>
+        <v>-12467.88859939131</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -8994,7 +8583,7 @@
         <v>1377.792</v>
       </c>
       <c r="C15" t="n">
-        <v>1776.422981836055</v>
+        <v>13743.19016304413</v>
       </c>
       <c r="D15" t="n">
         <v>3.4564e-07</v>
@@ -9027,10 +8616,7 @@
         <v>-3482.671990874283</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.076747928480313e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2024.673744779838</v>
+        <v>-11700.31222206818</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000794e-08</v>
@@ -9047,7 +8633,7 @@
         <v>1367.065</v>
       </c>
       <c r="C16" t="n">
-        <v>1764.997622112465</v>
+        <v>13917.20353488009</v>
       </c>
       <c r="D16" t="n">
         <v>3.47052e-07</v>
@@ -9080,10 +8666,7 @@
         <v>-328.387019495245</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.279216371395521e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2005.24249818509</v>
+        <v>-11894.97823309984</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000003e-08</v>
@@ -9100,7 +8683,7 @@
         <v>1350.783</v>
       </c>
       <c r="C17" t="n">
-        <v>1750.516151263335</v>
+        <v>14103.80296112348</v>
       </c>
       <c r="D17" t="n">
         <v>3.48488e-07</v>
@@ -9133,10 +8716,7 @@
         <v>1172.469699247953</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.944392334971067e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1985.935182710915</v>
+        <v>-12101.98947410409</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -9153,7 +8733,7 @@
         <v>1328.941</v>
       </c>
       <c r="C18" t="n">
-        <v>1730.883096934075</v>
+        <v>13567.86934751679</v>
       </c>
       <c r="D18" t="n">
         <v>3.49741e-07</v>
@@ -9186,10 +8766,7 @@
         <v>-1235.474705142059</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.268326875040545e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1966.762201431688</v>
+        <v>-11575.64234075944</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9206,7 +8783,7 @@
         <v>1322.094</v>
       </c>
       <c r="C19" t="n">
-        <v>1721.648686934279</v>
+        <v>13758.60709643689</v>
       </c>
       <c r="D19" t="n">
         <v>3.51216e-07</v>
@@ -9239,10 +8816,7 @@
         <v>4320.004066215066</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.512479130005232e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1947.623851993005</v>
+        <v>-11787.30498045537</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9259,7 +8833,7 @@
         <v>1298.512</v>
       </c>
       <c r="C20" t="n">
-        <v>1704.33091592751</v>
+        <v>13263.98434855846</v>
       </c>
       <c r="D20" t="n">
         <v>3.52769e-07</v>
@@ -9292,10 +8866,7 @@
         <v>3490.250535860603</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.177546872564243e-12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1928.492748216604</v>
+        <v>-11303.92093873921</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -9312,7 +8883,7 @@
         <v>1291.598</v>
       </c>
       <c r="C21" t="n">
-        <v>1692.652379878525</v>
+        <v>12753.50851489439</v>
       </c>
       <c r="D21" t="n">
         <v>3.541e-07</v>
@@ -9345,10 +8916,7 @@
         <v>7403.073278594797</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.291644411025263e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1909.218863983835</v>
+        <v>-10802.35572915828</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -9365,7 +8933,7 @@
         <v>1271.381</v>
       </c>
       <c r="C22" t="n">
-        <v>1674.16157758049</v>
+        <v>12914.63772315594</v>
       </c>
       <c r="D22" t="n">
         <v>3.55412e-07</v>
@@ -9398,10 +8966,7 @@
         <v>6199.55822260074</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.590795143356186e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1890.459693166599</v>
+        <v>-10983.70313265976</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -9564,7 +9129,7 @@
         <v>1483.47</v>
       </c>
       <c r="C2" t="n">
-        <v>2066.063085128366</v>
+        <v>9959.884435843085</v>
       </c>
       <c r="D2" t="n">
         <v>3.32062e-07</v>
@@ -9597,10 +9162,7 @@
         <v>-18661.78018724119</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.131801177028946e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2112.413326485524</v>
+        <v>-7608.732495363399</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -9617,7 +9179,7 @@
         <v>1220.564</v>
       </c>
       <c r="C3" t="n">
-        <v>1698.472395683319</v>
+        <v>1060.014503639551</v>
       </c>
       <c r="D3" t="n">
         <v>3.56222e-07</v>
@@ -9650,16 +9212,13 @@
         <v>-20851.07949251159</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.400859152752665e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1895.102039855793</v>
+        <v>118.3130170538961</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>2.070181124236112e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8186695257787544</v>
+        <v>0.9019301165289858</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1161.111</v>
       </c>
       <c r="C4" t="n">
-        <v>1629.669829606613</v>
+        <v>1084.797832313173</v>
       </c>
       <c r="D4" t="n">
         <v>3.5748e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-16414.50398004065</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.260402274030566e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1839.135513088014</v>
+        <v>82.06488856436964</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001192e-08</v>
+        <v>2.387802922725682e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8188227417856027</v>
+        <v>0.8879521766429054</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1131.448</v>
       </c>
       <c r="C5" t="n">
-        <v>1600.056500087459</v>
+        <v>1092.793165854748</v>
       </c>
       <c r="D5" t="n">
         <v>3.57369e-07</v>
@@ -9756,16 +9312,13 @@
         <v>-13082.17204302591</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.602179346621871e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1806.943526198307</v>
+        <v>66.53584547688968</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000005129e-08</v>
+        <v>2.574941904985335e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8189578561440372</v>
+        <v>0.8808537779491978</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1115.07</v>
       </c>
       <c r="C6" t="n">
-        <v>1583.061275403915</v>
+        <v>1089.681876803194</v>
       </c>
       <c r="D6" t="n">
         <v>3.57601e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-10050.72522303196</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.346683637406767</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1907.220431516589</v>
+        <v>59.59453958936644</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.51883301213593e-08</v>
+        <v>2.545856647593131e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7890356792397567</v>
+        <v>0.8796397050276947</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1082.491</v>
       </c>
       <c r="C7" t="n">
-        <v>1553.812980561614</v>
+        <v>1078.166632204556</v>
       </c>
       <c r="D7" t="n">
         <v>3.58108e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-8986.067495305362</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.732442839492702e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1751.145691773412</v>
+        <v>61.50355720968639</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000063e-08</v>
+        <v>2.633605782399592e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8192865498640411</v>
+        <v>0.8775652194875539</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1065.059</v>
       </c>
       <c r="C8" t="n">
-        <v>1533.619470434819</v>
+        <v>1135.118847495048</v>
       </c>
       <c r="D8" t="n">
         <v>3.59288e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-6965.624355708699</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.958784315320988e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1723.454014588223</v>
+        <v>5.773819043584769</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000039e-08</v>
+        <v>3.050298099068041e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8195503098821437</v>
+        <v>0.862207723123278</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>1043.966</v>
       </c>
       <c r="C9" t="n">
-        <v>1514.17109381599</v>
+        <v>1163.019129622635</v>
       </c>
       <c r="D9" t="n">
         <v>3.60394e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-5118.32328526468</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.300005257000134e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1696.018140351011</v>
+        <v>0.4351289520876954</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>4.837141054602839e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8198595087628128</v>
+        <v>0.8293907295926464</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>1020.695</v>
       </c>
       <c r="C10" t="n">
-        <v>1493.98594376344</v>
+        <v>1153.245908055492</v>
       </c>
       <c r="D10" t="n">
         <v>3.61266e-07</v>
@@ -10021,16 +9562,13 @@
         <v>-4046.337269879557</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.736013423185014e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1670.48590028759</v>
+        <v>0.4421218679322925</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>5.227019924940758e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8201887806134781</v>
+        <v>0.8238066429063116</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>1003.49</v>
       </c>
       <c r="C11" t="n">
-        <v>1479.095000796789</v>
+        <v>1069.105270704331</v>
       </c>
       <c r="D11" t="n">
         <v>3.62456e-07</v>
@@ -10074,16 +9612,13 @@
         <v>-2373.947858626498</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.893808886928976e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1646.944710328125</v>
+        <v>32.55231195170695</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.00000000000007e-08</v>
+        <v>2.939870324808779e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8205033760807476</v>
+        <v>0.8696392888240709</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,18 +645,6 @@
       <c r="G3" t="n">
         <v>-59.437</v>
       </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
       <c r="L3" t="n">
         <v>7.154960209335949</v>
       </c>
@@ -925,18 +913,6 @@
       <c r="G8" t="n">
         <v>-62.13</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -1124,6 +1100,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8245305029910103</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1740.956</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2081.821942333744</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.17859e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-58.554</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07266602502405951</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8454022988505475</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.555994256999213</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.290491923641691</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.781353702259</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.94867250983305</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-23178.24023521944</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>42.81529642877967</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000742e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8223847912655973</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1704.67</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9791574284473588</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2031.988248663366</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9760624611274327</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.21029e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-59.437</v>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>7.154960209335949</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.57848864456533</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10.53667018594114</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-21796.42237363628</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>44.48865930955503</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000122e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8226058930129354</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1660.337</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9536926837898257</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1997.052710856393</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9592812287383601</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.23599e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-60.13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.03899159663866206</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5478220574605841</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.897486252945944</v>
+      </c>
+      <c r="K14" t="n">
+        <v>231.6316516931672</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.297663788725042</v>
+      </c>
+      <c r="M14" t="n">
+        <v>83.83042443673912</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.250905860654612</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-18694.04726858732</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>43.32531161503641</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8228147166386627</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1625.349</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.933595679615108</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1964.711415914138</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9437461369590892</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.25831e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-60.728</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08493353028065175</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.68775862068974</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.041478599221797</v>
+      </c>
+      <c r="K15" t="n">
+        <v>675.7308617234859</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.480870917573931</v>
+      </c>
+      <c r="M15" t="n">
+        <v>83.07162700835414</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.229383810777586</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-16278.73085870794</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>42.47496853432381</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8230321595261403</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1587.723</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9119834160082161</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1931.45372461965</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.927770855587424</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.28003e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-61.248</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.05288640595902749</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4151675485008757</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.240799256505666</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.635645933014421</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>82.36197485878387</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.456897644967356</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14454.60429870954</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.37835891408065</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8231931885969932</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1567.936</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9006178214727999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1904.644895680225</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9148932754283005</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.29857e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-61.701</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1745253164556875</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.270411392404985</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.130775254502606</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.889757709251244</v>
+      </c>
+      <c r="M17" t="n">
+        <v>81.43053702847548</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.636111229355053</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-12602.99540603366</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>44.16197479714697</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.823443621170365</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1549.315</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.889921973903993</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1879.055540920027</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9026014678342695</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.31574e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.13</v>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v/>
+      </c>
+      <c r="K18" t="n">
+        <v/>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>79.281078070878</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.282786958013472</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9728.877440864233</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>43.50073232828902</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000001085e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8237228001495134</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1513.606</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8694108294523238</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1857.162386298481</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8920851243486189</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.33588e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-62.571</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.277572559366735</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2684343434343661</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.613992537313464</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1575.687727272639</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.072037184651951</v>
+      </c>
+      <c r="M19" t="n">
+        <v>78.59841228995109</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.958738167826652</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9004.028070926124</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>41.89471675869311</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8239724135541396</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1492.513</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8572950723625409</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1836.765799909306</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8822876551345562</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.34989e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-62.929</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4283082077051611</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.758064516128983</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.36522593320236</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.146366262172829</v>
+      </c>
+      <c r="M20" t="n">
+        <v>77.15390158802263</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.385182514387092</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7790.141647886042</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>40.41212228567497</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000012837e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8242502393606477</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1474.663</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8470420849234558</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1815.358121801944</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8720045095532563</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.36729e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-63.275</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6925000000000469</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.053614457831325</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1022.759475218544</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.751132884262002</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.681403828623322</v>
+      </c>
+      <c r="M21" t="n">
+        <v>66.38860652072991</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.287669458763684</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-3682.098932190307</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>40.46433221261236</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8245305029910103</v>
       </c>
     </row>
@@ -1138,7 +1674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +2992,1182 @@
         <v>1.000000000000003e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8226451432599715</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1706.695</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2123.809232028679</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.09071e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-59.81</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6376404494381592</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5165341812400905</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.265190365190394</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.696681922196772</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.63707276303212</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.967577436002831</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-19007.55173147595</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>21.97555293010646</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000068e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8168320739197017</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1580.673</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9261602102308848</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1970.856459492486</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9279818685079869</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.18587e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-61.546</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2971524288107054</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7575289575289127</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.881240768094066</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.580922431865992</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>82.92801880106893</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.060615349379423</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-15991.10059884027</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>42.150891456409</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.817210022386449</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1548.632</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9073864984663339</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1931.652146970269</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9095224363089992</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.21315e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-62.14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6701257861634687</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9975552968567982</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.393843594010008</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6.334776264591477</v>
+      </c>
+      <c r="M25" t="n">
+        <v>81.66510725083067</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6.825648183267987</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-13168.14695762455</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>43.22795052104834</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.817328364569441</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1521.659</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.891582268653743</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1906.91847603905</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8978765358400606</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.22833e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.485</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5620027434841786</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.210056497175135</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.645073108709474</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.859163818038425</v>
+      </c>
+      <c r="M26" t="n">
+        <v>81.30848418582072</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6.541507475214534</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-12429.98792904282</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>43.61919800680062</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8174367910607843</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1489.293</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.87261813036307</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1886.072744728731</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8880612798387452</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.24531e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-62.851</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9558252427183097</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.418530351437592</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.099649941656921</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.049861687413649</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>80.85566924505827</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6.212425880600651</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-11647.80140229969</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>42.28167904968143</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.00000000003472e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8176202860466265</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1473.133</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8631495375565054</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1860.182769322322</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8758709309995139</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.26186e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.182</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.335465116279018</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9635294117646016</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.513490725126441</v>
+      </c>
+      <c r="K28" t="n">
+        <v>755.3242105263836</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.862280872829913</v>
+      </c>
+      <c r="M28" t="n">
+        <v>79.02287130917607</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.155540620960839</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9436.252704124152</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>43.60750504227667</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.231638106498333e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8117667617960486</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1458.818</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8547619814905416</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1842.125736608866</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.867368739540346</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.27694e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-63.485</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.305555555555213</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.339294117647086</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.393704006541225</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7.334842519685082</v>
+      </c>
+      <c r="M29" t="n">
+        <v>76.28232249545654</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.096671401867356</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7251.208791127721</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>42.09576921137511</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8181090089039726</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1432.441</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8393069646304699</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1817.902062003387</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8559629719035134</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.29332e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-63.805</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.503048780487412</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.152461538461491</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.639688715953254</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.952630670523457</v>
+      </c>
+      <c r="M30" t="n">
+        <v>76.11669083330794</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4.045866336559725</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7088.803743242986</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>43.35499907676183</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8183901725500929</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1406.501</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8241079982070609</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1798.768700886328</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8469539889739202</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.30992e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-64.126</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.001965601965592399</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5176600441500913</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.448847262248051</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1120.314197530886</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.461960130828181</v>
+      </c>
+      <c r="M31" t="n">
+        <v>73.98840073679317</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.484751726182765</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-5966.943088565754</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>42.39961325740683</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8186983673655126</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1388.331</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8134616905774025</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1780.233597822886</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8382266970948202</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.32542e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-64.408</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5159292035399017</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.885692068429163</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.619616519174046</v>
+      </c>
+      <c r="K32" t="n">
+        <v>16502.60454546017</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.439550785471499</v>
+      </c>
+      <c r="M32" t="n">
+        <v>69.93700535867382</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.738106809484905</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-4505.986568045884</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>41.87786911680189</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8189941214962757</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1376.488</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8065225479655123</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1763.325318031866</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8302653983416034</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.33962e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-64.666</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6072796934865594</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.91385281385291</v>
+      </c>
+      <c r="J33" t="n">
+        <v>522.1587982832361</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.128762805358507</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6.272716693170258</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50.63635627834223</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.218996133234133</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-1616.932975848739</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>41.06705066844586</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8193086481249999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1352.049</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7922030591289011</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1745.186862348596</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8217248687075251</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.35429e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-64.961</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3901176470588205</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5634146341463008</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.938660578386608</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.57931049535379</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50.34960190914557</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.206629765195123</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-1602.722166044065</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>41.05287007262939</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8196316094150542</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1332.727</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7808817627051112</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1726.722677042778</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8130309686022972</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.36847e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-65.262</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.04594127806563606</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4100746268656913</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.233734939758915</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.146382381884076</v>
+      </c>
+      <c r="M35" t="n">
+        <v>28.04471875508875</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.5327109930503482</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-390.1280970922538</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>41.34824420748726</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8199528728551371</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1325.684</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7767550734021016</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1710.723288333672</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8054976231078794</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.38341e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-65.515</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.4403153153152414</v>
+      </c>
+      <c r="I36" t="n">
+        <v>865.2611764706293</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.635428571428569</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.302306425041181</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.689574515194247</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-68.79314964519257</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-2.577239926784001</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5268.739025487145</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>41.0117626274631</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8202790426016185</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1303.442</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7637228678820761</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1691.144109132606</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7962787258049592</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.39545e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-65.777</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09896480331262744</v>
+      </c>
+      <c r="I37" t="n">
+        <v>682.1659259258889</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.27651515151463</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.476094570928323</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.974838535065031</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-62.86804767742596</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-1.95148696353566</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4066.303261733255</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>41.7403145715532</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8206022729769485</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1293.281</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7577692557838395</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1676.824104960248</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7895361220171986</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.40946e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-66.051</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.323415977961259</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.291428571428577</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.551027397260216</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.168787640018143</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-78.39695937242601</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-4.870307937627723</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>9217.453206608392</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>40.56034810695348</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8209299096788133</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1272.355</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7455081312126653</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1661.479648477489</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7823111527255348</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.42359e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-66.30500000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.07055335968377502</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.110351562499998</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.212186788154648</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.164308476413271</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-76.25317310947334</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-4.087643211434847</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7715.60251121063</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>39.81142371261205</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000102e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8212643456604716</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1256.646</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.736303791831581</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1646.555440136036</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7752840581464245</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.43612e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-66.569</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1776.058173076901</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.02544031311154667</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.7716312056737723</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.869265536723112</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.312381655834283</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-78.77424625186011</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-5.038481808364024</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>9281.968402027896</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>38.74675283358704</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000669e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8215986142005532</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1245.451</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7297443304163895</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1629.635946418287</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7673174792924531</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.45046e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-66.864</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1326086956521597</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8270479134467421</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.436050955413843</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.521247892074185</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.854858554066007</v>
+      </c>
+      <c r="M41" t="n">
+        <v>74.98267765672875</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3.727542621691137</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-6081.93013548339</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>37.99404133104622</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8219455825502736</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1224.886</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7176947257711541</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1617.534006604879</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7616192557275016</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.46242e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-67.111</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3775238095237933</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8143750000000557</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.300742115027954</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.224183006535814</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.336423597400287</v>
+      </c>
+      <c r="M42" t="n">
+        <v>74.44158083602571</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>3.591658864458969</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-5784.175344101349</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>35.40265506899163</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000204e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8222885947173718</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1216.132</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.712565514049083</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1600.305175523738</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7535070247317428</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.47565e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-67.371</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.061904761904809</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.385057471264362</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.945255474452626</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.618134715025692</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.917683002882264</v>
+      </c>
+      <c r="M43" t="n">
+        <v>75.30292114361427</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3.812565189279494</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-6100.36882643658</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>34.95714186960709</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8226451432599715</v>
       </c>
     </row>
@@ -2470,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2749,18 +4461,6 @@
       <c r="G4" t="n">
         <v>-60.705</v>
       </c>
-      <c r="H4" t="n">
-        <v/>
-      </c>
-      <c r="I4" t="n">
-        <v/>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -2861,18 +4561,6 @@
       <c r="G6" t="n">
         <v>-61.448</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -3788,6 +5476,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8271434006221668</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1829.528</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2197.633613507595</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.04926e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-58.214</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.04644696189495512</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6047662694775062</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.619613075383694</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.890705734089445</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.74538630669684</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.87331222080123</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-24017.42558936794</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>25.50476970571322</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8218558078482964</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1707.352</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9332199343218577</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2048.371121737536</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9320803564103551</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.15374e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-60.08</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.03797054009819028</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8841448189762631</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.26974137931004</v>
+      </c>
+      <c r="K24" t="n">
+        <v>173.0477318548305</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6.018503658248576</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.13147163907111</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.729062230346807</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-20180.0408729663</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>43.32403445795944</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8220182930970963</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1678.505</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.917452479546637</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2009.179236334013</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9142466806044185</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.18004e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-60.705</v>
+      </c>
+      <c r="H25" t="n">
+        <v/>
+      </c>
+      <c r="I25" t="n">
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v/>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.57752631034326</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.883743071332535</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-18040.47114921402</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>45.59588616477538</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.821973648606483</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1645.988</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8996790429006823</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1987.48413304915</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9043746513673724</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.1971e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-61.094</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1359477124183026</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7293293293293914</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.715991763898412</v>
+      </c>
+      <c r="K26" t="n">
+        <v>713.6562886598233</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.65386804657168</v>
+      </c>
+      <c r="M26" t="n">
+        <v>82.93088605358636</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>8.063918194323405</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-16118.50102573419</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>44.67556053157045</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.821995432473609</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1629.336</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8905772417803935</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1963.218864401364</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8933331071815529</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.21371e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-61.448</v>
+      </c>
+      <c r="H27" t="n">
+        <v/>
+      </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v/>
+      </c>
+      <c r="K27" t="n">
+        <v/>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>81.46822795171664</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6.66586849835438</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-13041.40975842422</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>45.381123724085</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8221397714155021</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1596.888</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8728415197799649</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1944.265008183551</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8847084410400657</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.23037e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-61.788</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4662745098038931</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6736093143595919</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.191355932203389</v>
+      </c>
+      <c r="K28" t="n">
+        <v>292.66503322259</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.947805810316715</v>
+      </c>
+      <c r="M28" t="n">
+        <v>81.38561440072588</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.600982078730866</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-12784.78656282724</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>44.13227767293483</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.196614208838177e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8166596150155181</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1579.441</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.863305180352528</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1921.767024247012</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8744710730828882</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.24435e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-62.117</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3178205128205296</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.039636363636344</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.194574898785436</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7.220375034984794</v>
+      </c>
+      <c r="M29" t="n">
+        <v>80.13937701828618</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5.7530834835997</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10921.49564717989</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>44.1764701792996</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000557e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8225843157073186</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1562.146</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8538519224630615</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1902.671026119411</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8657817274111488</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.26033e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-62.442</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1526717557252051</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.239229422066519</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.784963887065014</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.144047619047588</v>
+      </c>
+      <c r="M30" t="n">
+        <v>78.09361849994475</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4.742722040825522</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8784.80523251102</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>43.37610282286698</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8228596173478033</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1542.601</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.843168839176006</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1883.303547329499</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8569688485623401</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.2751e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-62.735</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6097014925373273</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.003682719546728</v>
+      </c>
+      <c r="J31" t="n">
+        <v>299.8491596638792</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.132101167315206</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.423043603811694</v>
+      </c>
+      <c r="M31" t="n">
+        <v>75.83637764747112</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.962538992795366</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7147.062839848233</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>43.26028865989156</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.823170328854244</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1525.781</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.833975211092697</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1863.070409352266</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.84776206456847</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.28981e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-63.019</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4302290076335862</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.24875816993474</v>
+      </c>
+      <c r="J32" t="n">
+        <v>367.562860082289</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.873760580411096</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.549518248175215</v>
+      </c>
+      <c r="M32" t="n">
+        <v>72.73986747606965</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>3.218516401070234</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-5613.012241345244</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>43.56675320462841</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8234597107321138</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1504.315</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8222421302106335</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1846.706255326292</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8403158033148228</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.30459e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-63.313</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.06406533575317329</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.171212121212403</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.007351077313182</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6.106843921660651</v>
+      </c>
+      <c r="M33" t="n">
+        <v>71.59047861190733</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.004443841302589</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-5166.964550673434</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>42.21678453899381</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8237716845670795</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1486.375</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8124363223738581</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1830.646628702258</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8330081126582346</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.31745e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-63.592</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1065573770491746</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.034165366614693</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.590749306198065</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.280710140450405</v>
+      </c>
+      <c r="M34" t="n">
+        <v>66.23152262048305</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.270686163714053</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-3707.166244170628</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>41.09902077217328</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000368e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8240962852574766</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1466.53</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.801589262367124</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1812.852551472609</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8249111864371034</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.33128e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-63.878</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2197994987468596</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1180043383948174</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.328846153846242</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.700469604320364</v>
+      </c>
+      <c r="M35" t="n">
+        <v>64.25475203196149</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.073654076586092</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-3319.740469582753</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>41.0215258646241</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000115e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8244241756078227</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1453.219</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7943136153149882</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1799.749634084184</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8189489016832256</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.34492e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-64.126</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.475775656324579</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8960817717205903</v>
+      </c>
+      <c r="J36" t="n">
+        <v>961.1973333335477</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.537706422018219</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.71337122689763</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22.92762099042951</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.4229847510692788</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-155.2162001030414</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>38.66053212784846</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8247571507709734</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1433.583</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7835807924229635</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1783.471318653242</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8115416999864151</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.35929e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-64.416</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.281329113924048</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5151773049646078</v>
+      </c>
+      <c r="J37" t="n">
+        <v>723.7262000000411</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.490900195694669</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.768283675387803</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.249891039188775</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.05678220727091689</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>499.2140144648812</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>38.0850022529512</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8250851309788773</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1417.403</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7747369813416356</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1768.155636624358</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8045725300871435</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.37169e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-64.68600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1200374531835111</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.786549062844572</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5.694616680889813</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-40.10971874740019</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.8423681365908554</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2155.805052559103</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>37.14845644670208</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000008798e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8254201358440191</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1403.068</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7669016270863304</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1753.424993164463</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7978695731568554</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.38357e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-64.90600000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2024671052631591</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2546811397557736</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.190197568389069</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5.859668034322323</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-48.93478791313917</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-1.14772750959925</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2697.432087641368</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>35.86707104233437</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.645355878914446e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.7977635727290978</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1392.533</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7611433112802864</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1740.139084822946</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7918240211322339</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.39616e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-65.164</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1636641221374012</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3460.560952381193</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.830323679727472</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.984615384615495</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.25589051771197</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-74.31068098453683</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-3.56016083577585</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>7086.759727820572</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>34.44704561416813</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8260997385674429</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1377.431</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7528887232116698</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1725.009961216924</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7849397418269706</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.40596e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-65.38</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5144366197183463</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7280.824000007189</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.324057217165128</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.303342128408208</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.155306601443777</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-74.92991744729504</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-3.713874024733899</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>7303.129144768417</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>33.89300049894553</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8264401375421431</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1358.738</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7426713338085014</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1710.428195888302</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7783045296428301</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.42004e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-65.67</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1907563025209764</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.089017341040608</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.105840286054973</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.149077612360673</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-74.68593886394015</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-3.651862930883819</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7082.456086213839</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>32.78503035693655</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8267866329088928</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1345.235</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7352907416557712</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1697.525526032713</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7724333645058008</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.43202e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-65.934</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.9834645669283</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.70421686746988</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.71260964912276</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.234339058086627</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-77.55052566930308</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-4.529607859471222</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8562.696830682264</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>30.56193340391314</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8271434006221668</v>
       </c>
     </row>
@@ -3802,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,18 +6833,6 @@
       <c r="G2" t="n">
         <v>-50.76</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>14.31272237605167</v>
       </c>
@@ -4025,18 +6877,6 @@
       <c r="G3" t="n">
         <v>-55.863</v>
       </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
       <c r="L3" t="n">
         <v>24.86816400349119</v>
       </c>
@@ -4137,18 +6977,6 @@
       <c r="G5" t="n">
         <v>-58.64</v>
       </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
       <c r="L5" t="n">
         <v>10.82771692946659</v>
       </c>
@@ -4193,18 +7021,6 @@
       <c r="G6" t="n">
         <v>-59.358</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="n">
         <v>3.605843934693717</v>
       </c>
@@ -4305,18 +7121,6 @@
       <c r="G8" t="n">
         <v>-60.465</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -4417,18 +7221,6 @@
       <c r="G10" t="n">
         <v>-61.402</v>
       </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="I10" t="n">
-        <v/>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -4504,6 +7296,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8190014781508426</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2170.048</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2593.713978188062</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.74941e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-50.76</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>14.31272237605167</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.16452626865906</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.784558052165991</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-25281.55929627744</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.550593496846886</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000338e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8167954678996261</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1863.008</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8585100421741821</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2216.37767617262</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8545189233706312</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.06186e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-55.863</v>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>24.86816400349119</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.8553839247722</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.80002561372089</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-31411.76374128252</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>38.75659042626626</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000031913e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8176372014494299</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1771.989</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8165667303211726</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2131.390373335034</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8217522792640374</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.12655e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-57.638</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0568383658969819</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.884408602150504</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.590213299874558</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.231161266836523</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.02398593840023</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.48542876141742</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-25036.39938591619</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>45.51508559874401</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8177944184019432</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1740.698</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8021472336095792</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2094.559987339496</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8075524151675085</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.14783e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-58.64</v>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v/>
+      </c>
+      <c r="K15" t="n">
+        <v/>
+      </c>
+      <c r="L15" t="n">
+        <v>10.82771692946659</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.92742135131648</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.26567136449748</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-24126.26652424969</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>45.91605069770526</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8178713931785201</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1713.602</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7896608738608546</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2067.82478814122</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7972447253362059</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.16504e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-59.358</v>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v/>
+      </c>
+      <c r="K16" t="n">
+        <v/>
+      </c>
+      <c r="L16" t="n">
+        <v>3.605843934693717</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.07790794279029</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.640444233848433</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-20255.63900181402</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.03589624280426</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8179900902547043</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1679.236</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7738243578022237</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2043.126676269126</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.787722429477914</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.17977e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-59.958</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.05108695652174629</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8838156484458758</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.80767085076704</v>
+      </c>
+      <c r="K17" t="n">
+        <v>431.6069796954685</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.327464258841156</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83.02287756366351</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.171318407695193</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16838.39833609839</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>44.72214207744935</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8181250873035871</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1659.663</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7648047416462675</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2018.656549046622</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7782880325365836</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.195e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-60.465</v>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v/>
+      </c>
+      <c r="K18" t="n">
+        <v/>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>81.63012528882994</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.796712991659272</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-13700.94313990342</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>43.91516249648043</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000005845e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.818312761072743</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1626.902</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7497078405638953</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1992.674364327893</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7682706655727518</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.2094e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-60.931</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3912152269399652</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8622699386503391</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.92730654761915</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.875473741202016</v>
+      </c>
+      <c r="M19" t="n">
+        <v>80.90383505785877</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.245885605420618</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-12385.14499795848</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>44.24151532321173</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.818528385163658</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1609.305</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7415988033444421</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1972.031350205151</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7603118026077759</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.22689e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-61.402</v>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v/>
+      </c>
+      <c r="K20" t="n">
+        <v/>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>73.92006560510514</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.469140709124173</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-6457.358030293683</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42.83662131763765</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000305e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8187564695416385</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1576.191</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7263392330492227</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1947.967134953213</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7510339040213058</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.23942e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-61.771</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.001533742331278218</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.57278195488721</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.229681429681473</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2144.093902438646</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.868411749411718</v>
+      </c>
+      <c r="M21" t="n">
+        <v>78.28458178914315</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.822282046526968</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9193.045938178606</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>43.08601441287237</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8190014781508426</v>
       </c>
     </row>
@@ -4518,7 +7870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4965,18 +8317,6 @@
       <c r="G7" t="n">
         <v>-61.114</v>
       </c>
-      <c r="H7" t="n">
-        <v/>
-      </c>
-      <c r="I7" t="n">
-        <v/>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
       <c r="L7" t="n">
         <v>1.489958471674933</v>
       </c>
@@ -5836,6 +9176,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8221280741698642</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1770.221</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2174.076602163396</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.10092e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-55.355</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2514180024660839</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6165171898355895</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.376092544987198</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.740621156211487</v>
+      </c>
+      <c r="L23" t="n">
+        <v>60.34913681484709</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.0078829532745</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.4481931601502</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-25270.9745077079</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>23.07063658822108</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8167342242464068</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1647.525</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9306888800889833</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2028.010045618475</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.932814438829077</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.21803e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-58.328</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1888551165147031</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.852417582417607</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.722464261402293</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.151264044943887</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.44063142246873</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.54006748820524</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-26112.59757183991</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>41.48689625149154</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8170490155736816</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1609.344</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.909120386663586</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1992.787650967893</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9166133562105839</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.24336e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-59.42</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2587179487179455</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.1512315270935</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.782717770034861</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.381811432813535</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.26229246737196</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.06599072710019</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-24600.01779766982</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>41.48503712102024</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.817120919156286</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1577.062</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8908842455264061</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1963.285246535779</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9030432711442359</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.26052e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-60.111</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2081632653060857</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5652366863905042</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.784381778741892</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.263569682151629</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.63861690599957</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.65554400894035</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21330.64729598035</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>42.66904761527451</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001449e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8172209515700588</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1558.979</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.880669136791395</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1939.441448210995</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8920759490631938</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.27741e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-60.661</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1256465517241314</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.627245949926214</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.083797054009655</v>
+      </c>
+      <c r="K27" t="n">
+        <v>171.6967708867249</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6.468534932221158</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.47579681114158</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.33961419755706</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-20424.20110545467</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>41.99526469865566</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000001782e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8173996952703181</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1538.572</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8691411976244773</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1917.206671278342</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8818487211400712</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.29345e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-61.114</v>
+      </c>
+      <c r="H28" t="n">
+        <v/>
+      </c>
+      <c r="I28" t="n">
+        <v/>
+      </c>
+      <c r="J28" t="n">
+        <v/>
+      </c>
+      <c r="K28" t="n">
+        <v/>
+      </c>
+      <c r="L28" t="n">
+        <v>1.489958471674933</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.12649034663309</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.720753047561018</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-18922.24803844098</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>40.84229556032267</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8176183870949866</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1510.204</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8531160798566958</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1888.340376748607</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8685712246153345</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.30995e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-61.559</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4861850443599199</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7768056968464074</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.944799405646406</v>
+      </c>
+      <c r="K29" t="n">
+        <v>468.7793342579591</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.923371964679976</v>
+      </c>
+      <c r="M29" t="n">
+        <v>83.35567793304396</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8.584579653801629</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-16423.55133321817</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>42.86972364338214</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000056e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8178760123260773</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1482.629</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8375389287552232</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1867.294490572318</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8588908452968937</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.32603e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-61.957</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4308762169680136</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.298639455782133</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.408739255014039</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.560752386299837</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>82.87607870025458</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.00124248383432</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-15080.72249101161</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>42.42663630048457</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8181415408158662</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1467.942</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8292422245584026</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1849.973602910011</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8509238363860434</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.34092e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-62.344</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5121330724071017</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.291359593392545</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.046991622239052</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.066016949152591</v>
+      </c>
+      <c r="M31" t="n">
+        <v>81.62960740627466</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>6.796286431008581</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-12558.12680005444</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>40.84607067699562</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000203e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8184015568674078</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1443.448</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8154055341112776</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1830.926363177155</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.842162765265595</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.35646e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-62.692</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6437499999998734</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6625931445603584</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.420709570957189</v>
+      </c>
+      <c r="K32" t="n">
+        <v>447.2802069857748</v>
+      </c>
+      <c r="L32" t="n">
+        <v>6.083921834091353</v>
+      </c>
+      <c r="M32" t="n">
+        <v>80.64484665020996</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>6.069992211960154</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11034.92547586477</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>40.41253520549697</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8186827246611407</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1420.421</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8023975537517632</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1809.403093230309</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8322628059332384</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.36976e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-63.003</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1546551724137936</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2388203017832695</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.386949924127521</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.98369065849927</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>80.25023565861777</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>5.819800615889765</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10454.22567970742</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>41.42907718812796</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000225e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8189838946749735</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1413.051</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7982342317710613</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1792.020426627623</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8242673808477615</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.3863e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-63.37</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3950391644908563</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.396853625170928</v>
+      </c>
+      <c r="J34" t="n">
+        <v>559.0311501597982</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.70965476887078</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.99060317460327</v>
+      </c>
+      <c r="M34" t="n">
+        <v>69.02407399548717</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.608364302778769</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-4258.023366482982</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>40.7771474434652</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.81930686553524</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1386.372</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.783163232161408</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1772.503415765187</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8152902312648005</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.40057e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-63.625</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1488778054862764</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3365432098765073</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.035224839400389</v>
+      </c>
+      <c r="K35" t="n">
+        <v>632.1379061371605</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.617272773975338</v>
+      </c>
+      <c r="M35" t="n">
+        <v>75.9714115717095</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>4.002272510476752</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-6855.007206655303</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>41.22272211930954</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8196027443072182</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1377.975</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.778419756629257</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1758.436694421908</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8088200262456758</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.41422e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-63.926</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.120076481835704</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.372352941176593</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21928.76875007322</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.114602960968979</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.277387594355332</v>
+      </c>
+      <c r="M36" t="n">
+        <v>43.8615558925129</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.9610299937090596</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-1115.674699726089</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>39.83819055119636</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8199163450473048</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1351.625</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7635346095205062</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1739.294195551249</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8000151392184152</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.42764e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-64.227</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1874003189792677</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4128161888701668</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9775429326287423</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.797422298877806</v>
+      </c>
+      <c r="M37" t="n">
+        <v>63.04135340473545</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.966117303975074</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-3000.043639337012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>40.45336684005565</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8202251617307426</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1336.306</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7548808877535629</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1720.217101354969</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7912403360779482</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.4415e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-64.51600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2428160919540046</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8942184154175432</v>
+      </c>
+      <c r="J38" t="n">
+        <v>407.2284730195304</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.712903225806429</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5.912226717717449</v>
+      </c>
+      <c r="M38" t="n">
+        <v>45.43448501065251</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.015282571619792</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-1248.498711361743</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>41.01642779161091</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8205317402125414</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1330.848</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7517976569027257</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1706.880353881015</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7851058937769352</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.45598e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-64.80200000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.221767241379039</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1013.37600000013</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.571525096525088</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.122997946612007</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.203778429934081</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-72.92742366345705</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-3.256095338395242</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>6505.740889531367</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>39.09776340099143</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.988629627763726e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8104549672848965</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1305.144</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7372774359811571</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1690.59611441889</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7776157071634913</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.46799e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-65.047</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1480769230769218</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.929367088607466</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3171.006249999553</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.000237247923998</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.125782004698159</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-30.26983426558344</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-0.5836467645861675</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1616.698489650714</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>38.78540718146144</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.821172340440002</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1293.338</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7306082121949746</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1673.582888516348</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7697902120150629</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.48343e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-65.33</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6420886075950309</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7121.86799999687</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.64834437086085</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.581578947368499</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.444519231348877</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-74.38969936980901</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-3.579113167266549</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>6905.369524495869</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>38.78832405146773</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8214865399228338</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1281.105</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7236977755884717</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1657.383197520283</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7623389147700876</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.49556e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-65.568</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1822134387351736</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.154888888888864</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.437760416666724</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.566605033009353</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-76.43617560078853</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-4.144953568440815</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7829.0071820168</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>38.68855496283538</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8218035756252783</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1261.615</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.712687850838963</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1646.048360317384</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7571252819148238</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.50962e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-65.88200000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3931818181817581</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.002539682539694</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.312389380530971</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.442711439445589</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-76.73571255951464</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-4.242106379727296</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>7876.847570079973</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>35.72079937406227</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8221280741698642</v>
       </c>
     </row>
@@ -5850,7 +10366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6017,18 +10533,6 @@
       <c r="G2" t="n">
         <v>-50.613</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>12.43674644283627</v>
       </c>
@@ -6073,18 +10577,6 @@
       <c r="G3" t="n">
         <v>-56.02</v>
       </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
       <c r="L3" t="n">
         <v>20.03131900592901</v>
       </c>
@@ -6552,6 +11044,566 @@
         <v>1.000000000000035e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8206519868547215</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2010.608</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2437.939296112774</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.88254e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-50.613</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>12.43674644283627</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.68508640050176</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.036321548134451</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-21927.33982403725</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-5.921499972752599</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8183122528011395</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1720.705</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8558132664348298</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2081.201856258652</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.85367255024646</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.20864e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-56.02</v>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>20.03131900592901</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.49846534058848</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.70185507930735</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-27183.68093179626</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>40.68237097343354</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.819074510111525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1642.312</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.816823567796408</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2009.405360258612</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8242228850663148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.26903e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-57.982</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1135964912280912</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6118768328445769</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.302312138728322</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.163583252190833</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.51621400089732</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.00571262187555</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.44319292846364</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-23542.6158993587</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>45.23590717054105</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000001422e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8192163352940676</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1612.218</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8018559560093267</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1974.590651383112</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8099425012474846</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.29217e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-59.097</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2300300300300309</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8684115523465604</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.861916461916429</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.298701298701271</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.95371298669677</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.32467361721992</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-22889.88801247129</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>45.38993988075072</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000516e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8193185792260768</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1581.77</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7867122780770792</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1946.077338711634</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7982468397857978</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.30891e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-59.927</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1373152709359659</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.059462616822412</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.067324388318875</v>
+      </c>
+      <c r="K16" t="n">
+        <v>147.1462370437064</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.033891108891233</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.39779243039936</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.19474436953413</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-20227.34755178795</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.13295147489384</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000001422e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8194427593292148</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1548.466</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7701481342956957</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1919.089453359682</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7871768818934974</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.32649e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-60.588</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1846153846153714</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6113573407201842</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.08202396804274</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.372947368420997</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83.36981504542359</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.603048958290429</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16713.45949904044</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>44.45238728327774</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8196257578649878</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1524.622</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7582890349585797</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1893.700267127042</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7767626823795385</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.34175e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-61.166</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2578014184396784</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.036601307189489</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.851376146789074</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.626985040276252</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>82.67269415750867</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7.776812830372212</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-14842.73348834367</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>44.16775496086063</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000007262e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8198366291058186</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1496.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7442176694810725</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1867.042088559798</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7658279644356789</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.35994e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-61.656</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2242158092848061</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.272301425661841</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.173502722323061</v>
+      </c>
+      <c r="K19" t="n">
+        <v>259.9384319753958</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.474772542807293</v>
+      </c>
+      <c r="M19" t="n">
+        <v>81.59169219635113</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.765198806685627</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-12651.22439576775</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>44.42276144769119</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000002123e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.820084251692327</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1472.461</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7323461360941567</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1845.669233764841</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7570611937334571</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.37649e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-62.149</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.596706586826347</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8336492890996244</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.291514143094856</v>
+      </c>
+      <c r="K20" t="n">
+        <v>653.398653846112</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.721246669950677</v>
+      </c>
+      <c r="M20" t="n">
+        <v>79.62069416838311</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.459676907538616</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9955.161489567143</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42.73216970384306</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8203513308286863</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1454.528</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7234269434917199</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1820.932440970525</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7469145945815594</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.3946e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-62.553</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3200221238937945</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.61591263650556</v>
+      </c>
+      <c r="J21" t="n">
+        <v>276.2913917940495</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.842035928143885</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.255435101084105</v>
+      </c>
+      <c r="M21" t="n">
+        <v>75.1224995448122</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.76422437885523</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-6556.328123392039</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>43.38773506168047</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000035e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8206519868547215</v>
       </c>
     </row>
@@ -6566,7 +11618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6733,18 +11785,6 @@
       <c r="G2" t="n">
         <v>-55.334</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>18.11669994310894</v>
       </c>
@@ -6957,18 +11997,6 @@
       <c r="G6" t="n">
         <v>-60.752</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="n">
         <v>0.9440814176407966</v>
       </c>
@@ -7884,6 +12912,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.823550779313926</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1754.182</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2135.679102849154</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.14633e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-55.334</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>18.11669994310894</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.25101179123476</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.03719813107754</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26266.44067188984</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>28.52604061098555</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8180927730493248</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1632.782</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9307939541051042</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2007.672270762228</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9400627032796474</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.251e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-58.469</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.006786703601104252</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3150268336314803</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8527007299270027</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.204079601990086</v>
+      </c>
+      <c r="L24" t="n">
+        <v>17.20089894166334</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.98704961183948</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.40037341705818</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-23409.50289409664</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>43.30898605848211</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8183457305185744</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1602.448</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9135015636917946</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1969.650114448377</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9222593936611156</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.27513e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-59.584</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1459541984732713</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.926535087719225</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.797562626946508</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.576778733385329</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.82604301641445</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.04376290704604</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-22255.7748838759</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>45.3152275688675</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8184161549734839</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1576.056</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8984563745381037</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1944.963151618698</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9107000902073596</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.29049e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-60.277</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4692889561270771</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9116977225673216</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.815850144092205</v>
+      </c>
+      <c r="K26" t="n">
+        <v>173.9439537329087</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.021182506718702</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.20005825457285</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.844916128231484</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-19500.89224602438</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>44.90417779128791</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8185314720472997</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1557.45</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8878497214086108</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1921.732655045074</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8998227554323774</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.30636e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-60.752</v>
+      </c>
+      <c r="H27" t="n">
+        <v/>
+      </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v/>
+      </c>
+      <c r="K27" t="n">
+        <v/>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9440814176407966</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.72363765750833</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.092275950907407</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-17734.64062313891</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44.58939962821523</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000003917e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8187058255063128</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1521.223</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8671979304313918</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1899.730246217678</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8895204544930447</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.32519e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-61.21</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2500770416024655</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4604651162790542</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.71813361611883</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.559489456159805</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>82.91530875048139</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>8.046006418355486</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-15418.20997681798</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>43.31733611813252</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8189326649600858</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1501.749</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8560964597744133</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1875.423187523042</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8781390355044859</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.34312e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-61.653</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3191794871794817</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.640834575260764</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.172555746140719</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.879716981132042</v>
+      </c>
+      <c r="M29" t="n">
+        <v>81.82888160635306</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.964385214785362</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-13086.25996492417</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>43.59186777802745</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8191920538596626</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1476.246</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.841558059540002</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1852.525896736657</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8674177193873603</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.3612e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-62.013</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.567500000000028</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.075768535262141</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.51779964221831</v>
+      </c>
+      <c r="K30" t="n">
+        <v>292.7091143594105</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.667149493518808</v>
+      </c>
+      <c r="M30" t="n">
+        <v>81.29782815404234</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6.533372937607274</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-12093.72838407259</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>43.23863551646991</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000004362e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8194635650255985</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1455.254</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8295912282761994</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1830.247790260619</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.856986327121398</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.37954e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-62.373</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6559210526315982</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8984952120382679</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.350042408821053</v>
+      </c>
+      <c r="K31" t="n">
+        <v>564.6109271523191</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.713717801351708</v>
+      </c>
+      <c r="M31" t="n">
+        <v>80.23500153666801</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>5.810543488692669</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10551.16107144091</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>43.13565479461715</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8197604937916433</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1431.631</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8161245526404899</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1812.458806691139</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8486568999402506</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.39762e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-62.731</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2037453183520762</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.238876404494462</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.346649029982357</v>
+      </c>
+      <c r="K32" t="n">
+        <v>11390.30999998893</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.821237857540497</v>
+      </c>
+      <c r="M32" t="n">
+        <v>78.01720259259039</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>4.711585593391511</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8339.406866685262</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>41.12580431505228</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8200546022365006</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1414.23</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8062048293734628</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1789.988084437263</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8381353181989215</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.41496e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-63.049</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3843800322061</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.530796460177017</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.891521739130549</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6.005970416552191</v>
+      </c>
+      <c r="M33" t="n">
+        <v>75.25192574559955</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.798784631991308</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-6528.484747240417</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>42.05094627906567</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000001333e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8203531302882033</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1395.136</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7953199839013282</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1771.182708680618</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8293299804814913</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.43213e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-63.364</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2459412780656477</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7463380281690878</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.704994903159933</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.121494783008797</v>
+      </c>
+      <c r="M34" t="n">
+        <v>71.39174275552924</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.970023898174118</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-4907.951170024037</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>41.59480463320779</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000208e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8206453582175531</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1371.555</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7818772510492068</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1751.093632850568</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8199235692827069</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.44883e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-63.687</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2079326923076946</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.882362204724447</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.318309270614921</v>
+      </c>
+      <c r="M35" t="n">
+        <v>68.20342119189704</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.500611385362059</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-4011.884611853175</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>42.1510973110677</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8209498127938462</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1353.532</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7716029465585668</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1733.76645455972</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8118103755600489</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.46501e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-63.988</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1392197125256601</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.52917431192662</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.422280471821686</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.515123601871113</v>
+      </c>
+      <c r="M36" t="n">
+        <v>54.84148549150882</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.419771704861776</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-2001.451557276632</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>41.83414477949441</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8212629292047802</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1343.273</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.765754636634055</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1715.285158655724</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8031567834172306</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.48013e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-64.258</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3359173126615216</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6720588235294519</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.220303756994377</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.379581017918847</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-23.63536197186177</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-0.4376244417697306</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1401.696019463868</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>42.04091299659012</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8215734390118673</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1321.571</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7533830583143595</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1699.359857577175</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7956999978648961</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.49666e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-64.566</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.02359999999999986</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7093489148580715</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2605.043283580649</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.583666061705995</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5.773100922539091</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-36.01505624880785</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.7269440984999576</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1872.9110975536</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>40.97589468234094</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8218871171799974</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1311.858</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.747846004576492</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1685.428636826946</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7891769107907921</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.51121e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-64.82299999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1123209169054632</v>
+      </c>
+      <c r="I39" t="n">
+        <v>883.7073232323244</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.425930232558231</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.482765335929903</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.73105770764128</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-68.81653130893991</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-2.580361879013001</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5169.994898817462</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>39.26859832576054</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8222087567964652</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1295.136</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7383133563108045</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1669.223278815416</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7815889927417223</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.5255e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-65.11499999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7019999999999325</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.293315858453439</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.100254452926099</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.136919366292168</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-74.81551650009332</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-3.684554891064483</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>7053.334562523114</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>37.82101622784387</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8225421938164377</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1280.185</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7297902954197454</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1653.104135524818</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7740414434544283</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.54098e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-65.384</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6063231850118003</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.248702101359796</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.549525616698344</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.286854447512148</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-78.03794608922435</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-4.719998978962239</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>8779.037450271646</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>36.75067109641191</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8228727225789749</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1258.87</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7176393327488252</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1640.034643766745</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7679218481741088</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.55608e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-65.66800000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3681362725451663</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9428822495605768</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.236293436293487</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.196409828974637</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-76.73231190597836</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-4.240979233174182</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7825.69187997649</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>34.05595977558517</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.754721301734316e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8259443670313199</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1243.613</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.708941831577339</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1621.153982972246</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.75908125935657</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.57192e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-65.953</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3356725146198866</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7418524871354636</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.667121212121131</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.803703703703512</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.333713407990969</v>
+      </c>
+      <c r="M43" t="n">
+        <v>74.49474938169908</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3.604600745001127</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-5830.555360614539</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>34.89338088492991</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.823550779313926</v>
       </c>
     </row>
@@ -7898,7 +14102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8065,18 +14269,6 @@
       <c r="G2" t="n">
         <v>-51.14</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>13.69580238676602</v>
       </c>
@@ -8121,18 +14313,6 @@
       <c r="G3" t="n">
         <v>-57.557</v>
       </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
       <c r="L3" t="n">
         <v>20.15736461012811</v>
       </c>
@@ -8177,18 +14357,6 @@
       <c r="G4" t="n">
         <v>-59.642</v>
       </c>
-      <c r="H4" t="n">
-        <v/>
-      </c>
-      <c r="I4" t="n">
-        <v/>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
       <c r="L4" t="n">
         <v>12.35927601205413</v>
       </c>
@@ -8233,18 +14401,6 @@
       <c r="G5" t="n">
         <v>-60.738</v>
       </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
       <c r="L5" t="n">
         <v>0.810913572756554</v>
       </c>
@@ -8600,6 +14756,566 @@
         <v>1.000000000005478e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8251534583632906</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1974.047</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2363.651728966493</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.94187e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-51.14</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>13.69580238676602</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.96946972824345</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.465842002254481</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-22388.80319877982</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.219665348677154</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000005124e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8225864766707481</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1669.798</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8458755034707888</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2003.691230768251</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8477100099871164</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.27898e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-57.557</v>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>20.15736461012811</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.53954779932567</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.81932459788951</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-26396.60937732317</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>42.5058958694118</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8234048628961428</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1601.145</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8110977094263713</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1930.106504654328</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8165782128563699</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.33221e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-59.642</v>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v/>
+      </c>
+      <c r="K14" t="n">
+        <v/>
+      </c>
+      <c r="L14" t="n">
+        <v>12.35927601205413</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.04865534310625</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.54294140083858</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-22842.82970925371</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>47.34136725390283</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8235695509221728</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1569.926</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7952829897160503</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1896.320466620974</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8022842127635024</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.35217e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-60.738</v>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v/>
+      </c>
+      <c r="K15" t="n">
+        <v/>
+      </c>
+      <c r="L15" t="n">
+        <v>0.810913572756554</v>
+      </c>
+      <c r="M15" t="n">
+        <v>83.52834704789227</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.815662882784993</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-16938.41615410658</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>46.81151095140024</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000068331e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8236929932369786</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1533.049</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7766020768502472</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1869.080206867656</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7907595624017384</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.36806e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-61.461</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.111538461538285</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.099029126213587</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.138233054074499</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2221.532214764973</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.131373530147696</v>
+      </c>
+      <c r="M16" t="n">
+        <v>81.98602521586047</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.102799040974584</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-13298.13547812229</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.67281070837896</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8238621482507884</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1502.28</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7610153152381883</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1842.761057867262</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7796246102098171</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.38812e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-62.068</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5806366047744882</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8970430107527364</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.47830637488106</v>
+      </c>
+      <c r="K17" t="n">
+        <v>403.0279236276496</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.309353274992665</v>
+      </c>
+      <c r="M17" t="n">
+        <v>79.93270674439823</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.632589437901719</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10260.82528673172</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>44.29203743915991</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000087e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8240555537218642</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1469.375</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7443465125197121</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1816.389924288336</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7684676646853356</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.40612e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.597</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4242494226327956</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5970027247956328</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.787431693988916</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5223.416923074484</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.598506859201136</v>
+      </c>
+      <c r="M18" t="n">
+        <v>76.96888144100916</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.320768072165426</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7605.695436689388</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>43.86608099654677</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8243048022491064</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1444.824</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7319096252520837</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1792.727449258273</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.758456682635789</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.42607e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-63.053</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3615646258503517</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8495522388060159</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.284954280964136</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.689521479569689</v>
+      </c>
+      <c r="M19" t="n">
+        <v>72.80696309005485</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.231868389029313</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-5445.0274526308</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>41.67592625730913</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000002658e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8245733819663018</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1421.813</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7202528612540634</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1771.001469195651</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7492649815927076</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.44569e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-63.487</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2295197740112858</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6112984822934435</v>
+      </c>
+      <c r="J20" t="n">
+        <v>399.3817551962897</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.335656108597199</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.838067248680737</v>
+      </c>
+      <c r="M20" t="n">
+        <v>60.86448546867136</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.794027646419339</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-2702.963308183399</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>39.91293178344995</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8248636158348125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1403.842</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7111492279565785</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1748.134401261793</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7395905157424207</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.46292e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-63.859</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.383333333334092</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.154151624548844</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.703608847497197</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.530267965895247</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-18.15268803265198</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.3278685073504194</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1256.841685910484</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>39.08859617447285</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000005478e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8251534583632906</v>
       </c>
     </row>
@@ -8614,7 +15330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8781,18 +15497,6 @@
       <c r="G2" t="n">
         <v>-56.353</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>19.38498010593134</v>
       </c>
@@ -9932,6 +16636,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8251086426222195</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1753.193</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2126.597016148888</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.14726e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-56.353</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>19.38498010593134</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.38198389171703</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.38013344779855</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26828.37751742029</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>24.63059122381696</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8199851919565687</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1620.097</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9240836576463629</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1981.532074069313</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9317854106923009</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.25872e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-59.507</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.308009422850403</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8328431372548774</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.122504091653089</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.338336347197144</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.91485694832897</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.23768990782095</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-22740.02872814703</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>40.87641236694765</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000033749e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8202379931327785</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1586.794</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9050880308100705</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1942.460456977535</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.913412575220852</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.28245e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-60.381</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9141361256544275</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8769628099173143</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.833357717629965</v>
+      </c>
+      <c r="K25" t="n">
+        <v>142.7481943250273</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.937863145258136</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.33357356445418</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10.07846112782562</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-19956.30977812716</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>43.50517459507932</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8202760045559823</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1559.819</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8897018183394526</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1918.753650909284</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9022648091475306</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.29792e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-60.832</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2020768431983517</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.036260330578504</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.91253918495291</v>
+      </c>
+      <c r="K26" t="n">
+        <v>224.9227088948739</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.08892164087448</v>
+      </c>
+      <c r="M26" t="n">
+        <v>83.91562640302743</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.381449906243233</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-18308.84051384599</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>43.89412864200256</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8203445327519937</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1534.044</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8750000712984822</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1898.968305164549</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8929610503279283</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.31247e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-61.244</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03830548926013796</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.093220338982955</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.15626984126985</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.722546103509673</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.42670931435386</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.678177576855584</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16694.66620275111</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>42.86287391087865</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8204929258916049</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1518.468</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8661157100216577</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1877.777504526595</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8829963976565306</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.33109e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-61.596</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.306286549707623</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.562730627306267</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.971620612397284</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1234.577573529507</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6.778893109061333</v>
+      </c>
+      <c r="M28" t="n">
+        <v>82.57540916369737</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7.673785607154372</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-14521.8051493096</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>42.85416204549267</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8206972511395739</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1500.94</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8561179516459397</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1858.333601673499</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8738531971792218</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.34663e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-61.908</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2817002881844403</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.155047821466561</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.237425404944574</v>
+      </c>
+      <c r="K29" t="n">
+        <v>112119.4333325042</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.626852099491773</v>
+      </c>
+      <c r="M29" t="n">
+        <v>81.99637270391783</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7.112102684443761</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-13269.73746493533</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>42.53463518444153</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8209178833731177</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1481.147</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8448282647717621</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1836.448907459028</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8635622515753846</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.36424e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-62.217</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3871093749999261</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9506643046944263</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.766031987814212</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6.738913043478221</v>
+      </c>
+      <c r="M30" t="n">
+        <v>80.72897074396093</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6.126057264935233</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11214.57245444018</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>43.5923722049165</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000972e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8211662549472581</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1463.616</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8348287952324701</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1821.48625608479</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8565262916541514</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.38049e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-62.497</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4017374517374492</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.26008583690985</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.224400684931585</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6.99437095412321</v>
+      </c>
+      <c r="M31" t="n">
+        <v>79.52783502169258</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>5.410184223599325</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9725.398204445482</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>41.91804808806228</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.00000000000074e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8214255365798371</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1440.428</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8216026415802481</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1803.824320401841</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8482210342175857</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.39585e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-62.784</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1506641366223918</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6927304964538441</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.541446208112873</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1709.757999999496</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.868388573956533</v>
+      </c>
+      <c r="M32" t="n">
+        <v>78.76880552389031</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.035977400135164</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8935.4587760678</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>42.03165298647559</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8217033429359762</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1432.094</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8168490291713463</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1786.397904458126</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.84002652636707</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.41123e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-63.066</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4281138790035462</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.312233285917384</v>
+      </c>
+      <c r="J33" t="n">
+        <v>330.6118887823631</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.687955993051528</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.493623451193612</v>
+      </c>
+      <c r="M33" t="n">
+        <v>73.43323657420989</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.36155452585845</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-5674.162228133481</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>41.95780956185206</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8219854570824879</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1409.932</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8042080934614729</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1768.064040311933</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8314053047595111</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.42596e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-63.348</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1232914923291428</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.36311569301263</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.32188019966725</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.030746267733815</v>
+      </c>
+      <c r="M34" t="n">
+        <v>72.71956515545914</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3.214496065197946</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-5368.021292083731</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>42.43710023149026</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000098e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8222747325284969</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1382.546</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7885874515812007</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1753.319651352848</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.824471979429362</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.44129e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-63.608</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3254041570438689</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3886494252873395</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8826548672566261</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.520977011494161</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>74.58429760798448</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.626594717795229</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-6107.818877749405</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>41.47710627657625</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8225724399148835</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1377.792</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7858758277040805</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1738.683644521344</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8175896191512453</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.4564e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-63.88</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0791935483870929</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2133555926544215</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.383493810178837</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.333103540397866</v>
+      </c>
+      <c r="M36" t="n">
+        <v>65.83595470154087</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.228840598736393</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-3482.671990874283</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>40.56075168671248</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000794e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8228728451387118</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1367.065</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7797572771508898</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1724.426549022601</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8108854361817039</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.47052e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-64.137</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1811463046757076</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8685601056803796</v>
+      </c>
+      <c r="J37" t="n">
+        <v>909.962827225143</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.242078364565547</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.378344915662903</v>
+      </c>
+      <c r="M37" t="n">
+        <v>27.52461027105345</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.5211131013699194</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-328.387019495245</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>39.28078343082097</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8231814522867867</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1350.783</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7704702220462892</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1709.964800342826</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.804085018157059</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.48488e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-64.378</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1554809843400395</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.020277777777849</v>
+      </c>
+      <c r="J38" t="n">
+        <v>8482.382926825059</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.414725069897545</v>
+      </c>
+      <c r="L38" t="n">
+        <v>6.430423228090625</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-17.26249288163301</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.3107473341642026</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1172.469699247953</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>38.05545982776903</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8234970103522875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1328.941</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7580118104509886</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1694.678436318947</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7968968372709779</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.49741e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-64.628</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6134433962264116</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1633245382585726</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.052777777777718</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5.007588279310649</v>
+      </c>
+      <c r="M39" t="n">
+        <v>45.25799158971661</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.009046400662567</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-1235.474705142059</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>37.41296396813527</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8238135155774827</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1322.094</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7541063647869916</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1681.721232432731</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7908039086212045</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.51216e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-64.874</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0715821812595967</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.831372549019604</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.336851520572438</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.518871021079078</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-64.57295199316155</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-2.103431817874846</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4320.004066215066</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>35.55419782203069</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8241244208803208</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1298.512</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.740655478318702</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1665.57084197461</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7832094324061629</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.52769e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-65.133</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.115000000000002</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.3848120300751967</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.489920424403127</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5.90649180316512</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-59.11177625396401</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-1.6716578646309</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3490.250535860603</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>35.40077587396183</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8244536716799277</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1291.598</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7367118166682162</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1652.465363569323</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7770467799121703</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.541e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-65.38500000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4890322580645503</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.490776699029215</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.044499178981979</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.954561668839922</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-75.71666965056761</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-3.927930591105219</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7403.073278594797</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>33.60535885843967</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8247730757494215</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1271.381</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7251802853422299</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1641.802406376534</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7720326859809664</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.55412e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-65.63500000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3913953488371869</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3852.91098901098</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.114653784219079</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.333633093525165</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.83198675839066</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-73.08906196034226</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-3.289129958966575</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>6199.55822260074</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>31.1387846866362</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8251086426222195</v>
       </c>
     </row>
@@ -9946,7 +17826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18531,566 @@
         <v>0.8205033760807476</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1483.47</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1977.782049581569</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.32062e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-56.251</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1442961165048552</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8743421052631835</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.258320000000041</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.044751908397064</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18.95192980577479</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.02635672175349</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.556651234098043</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-18661.78018724119</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-30.45258394690745</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.818023149798667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1220.564</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8227763284731069</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1663.140752445626</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.840912047309505</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.56222e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-62.968</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02130365659776961</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1078549848942542</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9628620102213769</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.452154398563648</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.19664631545549</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.37214446279282</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.35369719285699</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-20851.07949251159</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>22.0081394783989</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8186695257787544</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1161.111</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7826993468017553</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1634.600441853732</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8264815843583762</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.5748e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-64.93000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1555066079295477</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1941068139962854</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8233979135617905</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.791917591125088</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.064672098686874</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.37694364448107</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.15670254258108</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-16414.50398004065</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.163650472296581</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000001192e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8188227417856027</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1131.448</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7627036610110078</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1572.237990248534</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7949500758089931</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.57369e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-65.857</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.02426850258175494</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.405607476635465</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9432282003710352</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.630025445292553</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>83.13626690366171</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.307641982282108</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-13082.17204302591</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>27.55211690899466</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000005129e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8189578561440372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1115.07</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7516633298954478</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1549.099945604063</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7832510897405504</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.57601e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-66.48099999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7377094972066865</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.084462151394417</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.873888091822141</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.207916986933048</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>81.33681676392436</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.563232418309902</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10050.72522303196</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>27.12387230050228</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.51883301213593e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.7890356792397567</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1082.491</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7297019825139706</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1521.60734588161</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7693503670960761</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.58108e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-66.998</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.03327932475838208</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5479498530074235</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.668420172831819</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12.90349678608272</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.41854747130174</v>
+      </c>
+      <c r="M17" t="n">
+        <v>80.50229486478456</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.977235050476501</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8986.067495305362</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>29.25768452454258</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8192865498640411</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1065.059</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7179511550621178</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1506.247946124453</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7615843952285458</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.59288e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-67.44</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2589958158995792</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2702702702702569</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9154981549814504</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.917049180327905</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>78.18563593405783</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.780742256901767</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-6965.624355708699</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>24.78772807217729</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8195503098821437</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1043.966</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7037324650987213</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1486.815582339048</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7517590639745201</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.60394e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-67.877</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3961240310077724</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.393096234309656</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.317835671342571</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.687535816618758</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>74.6982300161572</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.654940738289015</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-5118.32328526468</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>21.8539550443561</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8198595087628128</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1020.695</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6880455957990387</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1468.108193694099</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.742300292393037</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.61266e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-68.25700000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3763157894736899</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8636363636364613</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8702460850112506</v>
+      </c>
+      <c r="K20" t="n">
+        <v>543.2853695324141</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.653156911152102</v>
+      </c>
+      <c r="M20" t="n">
+        <v>71.57503328686998</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.001743117900863</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-4046.337269879557</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>19.49638783254318</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8201887806134781</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1003.49</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6764477879566152</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1455.300307597462</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7358244089157112</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.62456e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-68.602</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.102197802197874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4770562770562493</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.239691714836004</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1316.630291970661</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.73206022516489</v>
+      </c>
+      <c r="M21" t="n">
+        <v>62.55343621990598</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.925364211937832</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-2373.947858626498</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>14.1544318291119</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.00000000000007e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8205033760807476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 35.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,18 +1181,6 @@
       <c r="G13" t="n">
         <v>-59.437</v>
       </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="n">
         <v>7.154960209335949</v>
       </c>
@@ -1461,18 +1449,6 @@
       <c r="G18" t="n">
         <v>-62.13</v>
       </c>
-      <c r="H18" t="n">
-        <v/>
-      </c>
-      <c r="I18" t="n">
-        <v/>
-      </c>
-      <c r="J18" t="n">
-        <v/>
-      </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -1660,6 +1636,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8245305029910103</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1740.956</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2081.821942333744</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.17859e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-58.554</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.07266602502405951</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8454022988505475</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.555994256999213</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.290491923641691</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.781353702259</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.94867250983305</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-23178.24023521944</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>42.81529642877967</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000000742e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8223847912655973</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1704.67</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9791574284473588</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2031.988248663366</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9760624611274327</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.21029e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-59.437</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>7.154960209335949</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.57848864456533</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.53667018594114</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-21796.42237363628</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>44.48865930955503</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000122e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8226058930129354</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1660.337</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9536926837898257</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1997.052710856393</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9592812287383601</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.23599e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-60.13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.03899159663866206</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5478220574605841</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.897486252945944</v>
+      </c>
+      <c r="K24" t="n">
+        <v>231.6316516931672</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6.297663788725042</v>
+      </c>
+      <c r="M24" t="n">
+        <v>83.83042443673912</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.250905860654612</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-18694.04726858732</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>43.32531161503641</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8228147166386627</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1625.349</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.933595679615108</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1964.711415914138</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9437461369590892</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.25831e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-60.728</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.08493353028065175</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.68775862068974</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.041478599221797</v>
+      </c>
+      <c r="K25" t="n">
+        <v>675.7308617234859</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6.480870917573931</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.07162700835414</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.229383810777586</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-16278.73085870794</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>42.47496853432381</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8230321595261403</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1587.723</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9119834160082161</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1931.45372461965</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.927770855587424</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.28003e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-61.248</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.05288640595902749</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4151675485008757</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.240799256505666</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.635645933014421</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>82.36197485878387</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.456897644967356</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-14454.60429870954</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>45.37835891408065</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8231931885969932</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1567.936</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9006178214727999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1904.644895680225</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9148932754283005</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.29857e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-61.701</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1745253164556875</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.270411392404985</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.130775254502606</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6.889757709251244</v>
+      </c>
+      <c r="M27" t="n">
+        <v>81.43053702847548</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6.636111229355053</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-12602.99540603366</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44.16197479714697</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.823443621170365</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1549.315</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.889921973903993</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1879.055540920027</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9026014678342695</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.31574e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-62.13</v>
+      </c>
+      <c r="H28" t="n">
+        <v/>
+      </c>
+      <c r="I28" t="n">
+        <v/>
+      </c>
+      <c r="J28" t="n">
+        <v/>
+      </c>
+      <c r="K28" t="n">
+        <v/>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>79.281078070878</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.282786958013472</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9728.877440864233</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>43.50073232828902</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000001085e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8237228001495134</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1513.606</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8694108294523238</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1857.162386298481</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8920851243486189</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.33588e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-62.571</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.277572559366735</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2684343434343661</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.613992537313464</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1575.687727272639</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.072037184651951</v>
+      </c>
+      <c r="M29" t="n">
+        <v>78.59841228995109</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.958738167826652</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9004.028070926124</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>41.89471675869311</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8239724135541396</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1492.513</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8572950723625409</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1836.765799909306</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8822876551345562</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.34989e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-62.929</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4283082077051611</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.758064516128983</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.36522593320236</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6.146366262172829</v>
+      </c>
+      <c r="M30" t="n">
+        <v>77.15390158802263</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4.385182514387092</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7790.141647886042</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>40.41212228567497</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000012837e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8242502393606477</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1474.663</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8470420849234558</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1815.358121801944</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8720045095532563</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.36729e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-63.275</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6925000000000469</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.053614457831325</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1022.759475218544</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.751132884262002</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.681403828623322</v>
+      </c>
+      <c r="M31" t="n">
+        <v>66.38860652072991</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.287669458763684</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-3682.098932190307</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>40.46433221261236</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8245305029910103</v>
       </c>
     </row>
@@ -1674,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4168,6 +4704,1182 @@
         <v>1.000000000000003e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8226451432599715</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1706.695</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2123.809232028679</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.09071e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-59.81</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6376404494381592</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5165341812400905</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.265190365190394</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.696681922196772</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>83.63707276303212</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>8.967577436002831</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-19007.55173147595</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>21.97555293010646</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000000000068e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8168320739197017</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1580.673</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9261602102308848</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1970.856459492486</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9279818685079869</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.18587e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-61.546</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2971524288107054</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.7575289575289127</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.881240768094066</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.580922431865992</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>82.92801880106893</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>8.060615349379423</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-15991.10059884027</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>42.150891456409</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.817210022386449</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1548.632</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9073864984663339</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1931.652146970269</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9095224363089992</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.21315e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-62.14</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6701257861634687</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9975552968567982</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.393843594010008</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>6.334776264591477</v>
+      </c>
+      <c r="M46" t="n">
+        <v>81.66510725083067</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>6.825648183267987</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-13168.14695762455</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>43.22795052104834</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.817328364569441</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1521.659</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.891582268653743</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1906.91847603905</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8978765358400606</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.22833e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-62.485</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5620027434841786</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.210056497175135</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.645073108709474</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.859163818038425</v>
+      </c>
+      <c r="M47" t="n">
+        <v>81.30848418582072</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>6.541507475214534</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-12429.98792904282</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>43.61919800680062</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8174367910607843</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1489.293</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.87261813036307</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1886.072744728731</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8880612798387452</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.24531e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-62.851</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9558252427183097</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.418530351437592</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.099649941656921</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.049861687413649</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>80.85566924505827</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>6.212425880600651</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-11647.80140229969</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>42.28167904968143</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.00000000003472e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8176202860466265</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1473.133</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8631495375565054</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1860.182769322322</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8758709309995139</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.26186e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-63.182</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.335465116279018</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9635294117646016</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.513490725126441</v>
+      </c>
+      <c r="K49" t="n">
+        <v>755.3242105263836</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5.862280872829913</v>
+      </c>
+      <c r="M49" t="n">
+        <v>79.02287130917607</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>5.155540620960839</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-9436.252704124152</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>43.60750504227667</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.231638106498333e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8117667617960486</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1458.818</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8547619814905416</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1842.125736608866</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.867368739540346</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.27694e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-63.485</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.305555555555213</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.339294117647086</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.393704006541225</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>7.334842519685082</v>
+      </c>
+      <c r="M50" t="n">
+        <v>76.28232249545654</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>4.096671401867356</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-7251.208791127721</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>42.09576921137511</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8181090089039726</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1432.441</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8393069646304699</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1817.902062003387</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8559629719035134</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.29332e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-63.805</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.503048780487412</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.152461538461491</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.639688715953254</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5.952630670523457</v>
+      </c>
+      <c r="M51" t="n">
+        <v>76.11669083330794</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>4.045866336559725</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-7088.803743242986</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>43.35499907676183</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8183901725500929</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1406.501</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8241079982070609</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1798.768700886328</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8469539889739202</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.30992e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-64.126</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.001965601965592399</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5176600441500913</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.448847262248051</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1120.314197530886</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.461960130828181</v>
+      </c>
+      <c r="M52" t="n">
+        <v>73.98840073679317</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>3.484751726182765</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-5966.943088565754</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>42.39961325740683</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8186983673655126</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1388.331</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8134616905774025</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1780.233597822886</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8382266970948202</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.32542e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-64.408</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.5159292035399017</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.885692068429163</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.619616519174046</v>
+      </c>
+      <c r="K53" t="n">
+        <v>16502.60454546017</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5.439550785471499</v>
+      </c>
+      <c r="M53" t="n">
+        <v>69.93700535867382</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.738106809484905</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-4505.986568045884</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>41.87786911680189</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8189941214962757</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1376.488</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8065225479655123</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1763.325318031866</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8302653983416034</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.33962e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-64.666</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6072796934865594</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.91385281385291</v>
+      </c>
+      <c r="J54" t="n">
+        <v>522.1587982832361</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.128762805358507</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.272716693170258</v>
+      </c>
+      <c r="M54" t="n">
+        <v>50.63635627834223</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.218996133234133</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-1616.932975848739</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>41.06705066844586</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8193086481249999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1352.049</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7922030591289011</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1745.186862348596</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8217248687075251</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.35429e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-64.961</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3901176470588205</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.5634146341463008</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.938660578386608</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5.57931049535379</v>
+      </c>
+      <c r="M55" t="n">
+        <v>50.34960190914557</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.206629765195123</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-1602.722166044065</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>41.05287007262939</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8196316094150542</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1332.727</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7808817627051112</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1726.722677042778</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8130309686022972</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.36847e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-65.262</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.04594127806563606</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4100746268656913</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.233734939758915</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.146382381884076</v>
+      </c>
+      <c r="M56" t="n">
+        <v>28.04471875508875</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.5327109930503482</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-390.1280970922538</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>41.34824420748726</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8199528728551371</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1325.684</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7767550734021016</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1710.723288333672</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8054976231078794</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.38341e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-65.515</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.4403153153152414</v>
+      </c>
+      <c r="I57" t="n">
+        <v>865.2611764706293</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.635428571428569</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.302306425041181</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6.689574515194247</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-68.79314964519257</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-2.577239926784001</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>5268.739025487145</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>41.0117626274631</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8202790426016185</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1303.442</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7637228678820761</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1691.144109132606</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7962787258049592</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.39545e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-65.777</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.09896480331262744</v>
+      </c>
+      <c r="I58" t="n">
+        <v>682.1659259258889</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.27651515151463</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.476094570928323</v>
+      </c>
+      <c r="L58" t="n">
+        <v>5.974838535065031</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-62.86804767742596</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-1.95148696353566</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>4066.303261733255</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>41.7403145715532</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8206022729769485</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1293.281</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7577692557838395</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1676.824104960248</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7895361220171986</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.40946e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-66.051</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.323415977961259</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.291428571428577</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.551027397260216</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7.168787640018143</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-78.39695937242601</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-4.870307937627723</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>9217.453206608392</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>40.56034810695348</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8209299096788133</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1272.355</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7455081312126653</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1661.479648477489</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7823111527255348</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.42359e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-66.30500000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.07055335968377502</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.110351562499998</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.212186788154648</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.164308476413271</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-76.25317310947334</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-4.087643211434847</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>7715.60251121063</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>39.81142371261205</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000000102e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8212643456604716</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1256.646</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.736303791831581</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1646.555440136036</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7752840581464245</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.43612e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-66.569</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1776.058173076901</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.02544031311154667</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7716312056737723</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.869265536723112</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.312381655834283</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-78.77424625186011</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-5.038481808364024</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>9281.968402027896</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>38.74675283358704</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000000669e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8215986142005532</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1245.451</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7297443304163895</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1629.635946418287</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7673174792924531</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.45046e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-66.864</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1326086956521597</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8270479134467421</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.436050955413843</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.521247892074185</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.854858554066007</v>
+      </c>
+      <c r="M62" t="n">
+        <v>74.98267765672875</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>3.727542621691137</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-6081.93013548339</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>37.99404133104622</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8219455825502736</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1224.886</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7176947257711541</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1617.534006604879</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7616192557275016</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.46242e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-67.111</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.3775238095237933</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8143750000000557</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.300742115027954</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.224183006535814</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.336423597400287</v>
+      </c>
+      <c r="M63" t="n">
+        <v>74.44158083602571</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>3.591658864458969</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-5784.175344101349</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>35.40265506899163</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000000204e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8222885947173718</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1216.132</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.712565514049083</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1600.305175523738</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7535070247317428</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.47565e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-67.371</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.061904761904809</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.385057471264362</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.945255474452626</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.618134715025692</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7.917683002882264</v>
+      </c>
+      <c r="M64" t="n">
+        <v>75.30292114361427</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>3.812565189279494</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-6100.36882643658</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>34.95714186960709</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8226451432599715</v>
       </c>
     </row>
@@ -4182,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5613,18 +7325,6 @@
       <c r="G25" t="n">
         <v>-60.705</v>
       </c>
-      <c r="H25" t="n">
-        <v/>
-      </c>
-      <c r="I25" t="n">
-        <v/>
-      </c>
-      <c r="J25" t="n">
-        <v/>
-      </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
@@ -5725,18 +7425,6 @@
       <c r="G27" t="n">
         <v>-61.448</v>
       </c>
-      <c r="H27" t="n">
-        <v/>
-      </c>
-      <c r="I27" t="n">
-        <v/>
-      </c>
-      <c r="J27" t="n">
-        <v/>
-      </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
@@ -6652,6 +8340,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8271434006221668</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1829.528</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2197.633613507595</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.04926e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-58.214</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.04644696189495512</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6047662694775062</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.619613075383694</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.890705734089445</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>84.74538630669684</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>10.87331222080123</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-24017.42558936794</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>25.50476970571322</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8218558078482964</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1707.352</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9332199343218577</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2048.371121737536</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9320803564103551</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.15374e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-60.08</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.03797054009819028</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8841448189762631</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.26974137931004</v>
+      </c>
+      <c r="K45" t="n">
+        <v>173.0477318548305</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.018503658248576</v>
+      </c>
+      <c r="M45" t="n">
+        <v>84.13147163907111</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>9.729062230346807</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-20180.0408729663</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>43.32403445795944</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8220182930970963</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1678.505</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.917452479546637</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2009.179236334013</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9142466806044185</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.18004e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-60.705</v>
+      </c>
+      <c r="H46" t="n">
+        <v/>
+      </c>
+      <c r="I46" t="n">
+        <v/>
+      </c>
+      <c r="J46" t="n">
+        <v/>
+      </c>
+      <c r="K46" t="n">
+        <v/>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>83.57752631034326</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>8.883743071332535</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-18040.47114921402</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>45.59588616477538</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.821973648606483</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1645.988</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8996790429006823</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1987.48413304915</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9043746513673724</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.1971e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-61.094</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1359477124183026</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.7293293293293914</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.715991763898412</v>
+      </c>
+      <c r="K47" t="n">
+        <v>713.6562886598233</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.65386804657168</v>
+      </c>
+      <c r="M47" t="n">
+        <v>82.93088605358636</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>8.063918194323405</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-16118.50102573419</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>44.67556053157045</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.821995432473609</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1629.336</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8905772417803935</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1963.218864401364</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8933331071815529</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.21371e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-61.448</v>
+      </c>
+      <c r="H48" t="n">
+        <v/>
+      </c>
+      <c r="I48" t="n">
+        <v/>
+      </c>
+      <c r="J48" t="n">
+        <v/>
+      </c>
+      <c r="K48" t="n">
+        <v/>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>81.46822795171664</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>6.66586849835438</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-13041.40975842422</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>45.381123724085</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8221397714155021</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1596.888</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8728415197799649</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1944.265008183551</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8847084410400657</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.23037e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-61.788</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.4662745098038931</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6736093143595919</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.191355932203389</v>
+      </c>
+      <c r="K49" t="n">
+        <v>292.66503322259</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5.947805810316715</v>
+      </c>
+      <c r="M49" t="n">
+        <v>81.38561440072588</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>6.600982078730866</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-12784.78656282724</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>44.13227767293483</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.196614208838177e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8166596150155181</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1579.441</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.863305180352528</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1921.767024247012</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8744710730828882</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.24435e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-62.117</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3178205128205296</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.039636363636344</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.194574898785436</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>7.220375034984794</v>
+      </c>
+      <c r="M50" t="n">
+        <v>80.13937701828618</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>5.7530834835997</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-10921.49564717989</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>44.1764701792996</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000000000557e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8225843157073186</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1562.146</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8538519224630615</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1902.671026119411</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8657817274111488</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.26033e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-62.442</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1526717557252051</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.239229422066519</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.784963887065014</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7.144047619047588</v>
+      </c>
+      <c r="M51" t="n">
+        <v>78.09361849994475</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>4.742722040825522</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-8784.80523251102</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>43.37610282286698</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8228596173478033</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1542.601</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.843168839176006</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1883.303547329499</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8569688485623401</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.2751e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-62.735</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.6097014925373273</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.003682719546728</v>
+      </c>
+      <c r="J52" t="n">
+        <v>299.8491596638792</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.132101167315206</v>
+      </c>
+      <c r="L52" t="n">
+        <v>7.423043603811694</v>
+      </c>
+      <c r="M52" t="n">
+        <v>75.83637764747112</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>3.962538992795366</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-7147.062839848233</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>43.26028865989156</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.823170328854244</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1525.781</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.833975211092697</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1863.070409352266</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.84776206456847</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.28981e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-63.019</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.4302290076335862</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.24875816993474</v>
+      </c>
+      <c r="J53" t="n">
+        <v>367.562860082289</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.873760580411096</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7.549518248175215</v>
+      </c>
+      <c r="M53" t="n">
+        <v>72.73986747606965</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>3.218516401070234</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-5613.012241345244</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>43.56675320462841</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8234597107321138</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1504.315</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8222421302106335</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1846.706255326292</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8403158033148228</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.30459e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-63.313</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.06406533575317329</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.171212121212403</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.007351077313182</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.106843921660651</v>
+      </c>
+      <c r="M54" t="n">
+        <v>71.59047861190733</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>3.004443841302589</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-5166.964550673434</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>42.21678453899381</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8237716845670795</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1486.375</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8124363223738581</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1830.646628702258</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8330081126582346</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.31745e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-63.592</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1065573770491746</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.034165366614693</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.590749306198065</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.280710140450405</v>
+      </c>
+      <c r="M55" t="n">
+        <v>66.23152262048305</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.270686163714053</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-3707.166244170628</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>41.09902077217328</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000000368e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8240962852574766</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1466.53</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.801589262367124</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1812.852551472609</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8249111864371034</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.33128e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-63.878</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.2197994987468596</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1180043383948174</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.328846153846242</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.700469604320364</v>
+      </c>
+      <c r="M56" t="n">
+        <v>64.25475203196149</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.073654076586092</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-3319.740469582753</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>41.0215258646241</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000000000115e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8244241756078227</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1453.219</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7943136153149882</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1799.749634084184</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8189489016832256</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.34492e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-64.126</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.475775656324579</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8960817717205903</v>
+      </c>
+      <c r="J57" t="n">
+        <v>961.1973333335477</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.537706422018219</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6.71337122689763</v>
+      </c>
+      <c r="M57" t="n">
+        <v>22.92762099042951</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.4229847510692788</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-155.2162001030414</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>38.66053212784846</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8247571507709734</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1433.583</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7835807924229635</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1783.471318653242</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8115416999864151</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.35929e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-64.416</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.281329113924048</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5151773049646078</v>
+      </c>
+      <c r="J58" t="n">
+        <v>723.7262000000411</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.490900195694669</v>
+      </c>
+      <c r="L58" t="n">
+        <v>5.768283675387803</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.249891039188775</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.05678220727091689</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>499.2140144648812</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>38.0850022529512</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8250851309788773</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1417.403</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7747369813416356</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1768.155636624358</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8045725300871435</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.37169e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-64.68600000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1200374531835111</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.786549062844572</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.694616680889813</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-40.10971874740019</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-0.8423681365908554</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2155.805052559103</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>37.14845644670208</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000008798e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8254201358440191</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1403.068</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7669016270863304</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1753.424993164463</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7978695731568554</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.38357e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-64.90600000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.2024671052631591</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2546811397557736</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.190197568389069</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5.859668034322323</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-48.93478791313917</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-1.14772750959925</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2697.432087641368</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>35.86707104233437</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.645355878914446e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.7977635727290978</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1392.533</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7611433112802864</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1740.139084822946</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7918240211322339</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.39616e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-65.164</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1636641221374012</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3460.560952381193</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.830323679727472</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.984615384615495</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.25589051771197</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-74.31068098453683</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-3.56016083577585</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>7086.759727820572</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>34.44704561416813</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8260997385674429</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1377.431</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7528887232116698</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1725.009961216924</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7849397418269706</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.40596e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-65.38</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.5144366197183463</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7280.824000007189</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.324057217165128</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.303342128408208</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.155306601443777</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-74.92991744729504</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-3.713874024733899</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>7303.129144768417</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>33.89300049894553</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8264401375421431</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1358.738</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7426713338085014</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1710.428195888302</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7783045296428301</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.42004e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-65.67</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1907563025209764</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.089017341040608</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.105840286054973</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.149077612360673</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-74.68593886394015</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-3.651862930883819</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>7082.456086213839</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>32.78503035693655</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8267866329088928</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1345.235</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7352907416557712</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1697.525526032713</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7724333645058008</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.43202e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-65.934</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.9834645669283</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.70421686746988</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.71260964912276</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.234339058086627</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-77.55052566930308</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-4.529607859471222</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>8562.696830682264</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>30.56193340391314</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8271434006221668</v>
       </c>
     </row>
@@ -6666,7 +9530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7321,18 +10185,6 @@
       <c r="G12" t="n">
         <v>-50.76</v>
       </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
       <c r="L12" t="n">
         <v>14.31272237605167</v>
       </c>
@@ -7377,18 +10229,6 @@
       <c r="G13" t="n">
         <v>-55.863</v>
       </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="n">
         <v>24.86816400349119</v>
       </c>
@@ -7489,18 +10329,6 @@
       <c r="G15" t="n">
         <v>-58.64</v>
       </c>
-      <c r="H15" t="n">
-        <v/>
-      </c>
-      <c r="I15" t="n">
-        <v/>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
       <c r="L15" t="n">
         <v>10.82771692946659</v>
       </c>
@@ -7545,18 +10373,6 @@
       <c r="G16" t="n">
         <v>-59.358</v>
       </c>
-      <c r="H16" t="n">
-        <v/>
-      </c>
-      <c r="I16" t="n">
-        <v/>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
       <c r="L16" t="n">
         <v>3.605843934693717</v>
       </c>
@@ -7657,18 +10473,6 @@
       <c r="G18" t="n">
         <v>-60.465</v>
       </c>
-      <c r="H18" t="n">
-        <v/>
-      </c>
-      <c r="I18" t="n">
-        <v/>
-      </c>
-      <c r="J18" t="n">
-        <v/>
-      </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -7769,18 +10573,6 @@
       <c r="G20" t="n">
         <v>-61.402</v>
       </c>
-      <c r="H20" t="n">
-        <v/>
-      </c>
-      <c r="I20" t="n">
-        <v/>
-      </c>
-      <c r="J20" t="n">
-        <v/>
-      </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
@@ -7856,6 +10648,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8190014781508426</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2170.048</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2593.713978188062</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.74941e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-50.76</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v/>
+      </c>
+      <c r="K22" t="n">
+        <v/>
+      </c>
+      <c r="L22" t="n">
+        <v>14.31272237605167</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.16452626865906</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.784558052165991</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-25281.55929627744</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.550593496846886</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000000338e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8167954678996261</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1863.008</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8585100421741821</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2216.37767617262</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8545189233706312</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.06186e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-55.863</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>24.86816400349119</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.8553839247722</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.80002561372089</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-31411.76374128252</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>38.75659042626626</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000031913e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8176372014494299</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1771.989</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8165667303211726</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2131.390373335034</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8217522792640374</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.12655e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-57.638</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0568383658969819</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.884408602150504</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.590213299874558</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.231161266836523</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.02398593840023</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.48542876141742</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-25036.39938591619</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>45.51508559874401</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8177944184019432</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1740.698</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8021472336095792</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2094.559987339496</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8075524151675085</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.14783e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-58.64</v>
+      </c>
+      <c r="H25" t="n">
+        <v/>
+      </c>
+      <c r="I25" t="n">
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v/>
+      </c>
+      <c r="L25" t="n">
+        <v>10.82771692946659</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.92742135131648</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.26567136449748</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-24126.26652424969</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>45.91605069770526</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8178713931785201</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1713.602</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7896608738608546</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2067.82478814122</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7972447253362059</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.16504e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-59.358</v>
+      </c>
+      <c r="H26" t="n">
+        <v/>
+      </c>
+      <c r="I26" t="n">
+        <v/>
+      </c>
+      <c r="J26" t="n">
+        <v/>
+      </c>
+      <c r="K26" t="n">
+        <v/>
+      </c>
+      <c r="L26" t="n">
+        <v>3.605843934693717</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.07790794279029</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.640444233848433</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20255.63900181402</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>45.03589624280426</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8179900902547043</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1679.236</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7738243578022237</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2043.126676269126</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.787722429477914</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.17977e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-59.958</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.05108695652174629</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8838156484458758</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.80767085076704</v>
+      </c>
+      <c r="K27" t="n">
+        <v>431.6069796954685</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6.327464258841156</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.02287756366351</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.171318407695193</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16838.39833609839</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44.72214207744935</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8181250873035871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1659.663</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7648047416462675</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2018.656549046622</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7782880325365836</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.195e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-60.465</v>
+      </c>
+      <c r="H28" t="n">
+        <v/>
+      </c>
+      <c r="I28" t="n">
+        <v/>
+      </c>
+      <c r="J28" t="n">
+        <v/>
+      </c>
+      <c r="K28" t="n">
+        <v/>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>81.63012528882994</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.796712991659272</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-13700.94313990342</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>43.91516249648043</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000005845e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.818312761072743</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1626.902</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7497078405638953</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1992.674364327893</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7682706655727518</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.2094e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-60.931</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3912152269399652</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8622699386503391</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.92730654761915</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.875473741202016</v>
+      </c>
+      <c r="M29" t="n">
+        <v>80.90383505785877</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.245885605420618</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-12385.14499795848</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>44.24151532321173</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.818528385163658</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1609.305</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7415988033444421</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1972.031350205151</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7603118026077759</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.22689e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-61.402</v>
+      </c>
+      <c r="H30" t="n">
+        <v/>
+      </c>
+      <c r="I30" t="n">
+        <v/>
+      </c>
+      <c r="J30" t="n">
+        <v/>
+      </c>
+      <c r="K30" t="n">
+        <v/>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>73.92006560510514</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.469140709124173</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-6457.358030293683</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>42.83662131763765</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000305e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8187564695416385</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1576.191</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7263392330492227</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1947.967134953213</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7510339040213058</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.23942e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-61.771</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.001533742331278218</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.57278195488721</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.229681429681473</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2144.093902438646</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.868411749411718</v>
+      </c>
+      <c r="M31" t="n">
+        <v>78.28458178914315</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4.822282046526968</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9193.045938178606</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>43.08601441287237</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8190014781508426</v>
       </c>
     </row>
@@ -7870,7 +11222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9481,18 +12833,6 @@
       <c r="G28" t="n">
         <v>-61.114</v>
       </c>
-      <c r="H28" t="n">
-        <v/>
-      </c>
-      <c r="I28" t="n">
-        <v/>
-      </c>
-      <c r="J28" t="n">
-        <v/>
-      </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
       <c r="L28" t="n">
         <v>1.489958471674933</v>
       </c>
@@ -10352,6 +13692,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8221280741698642</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1770.221</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2174.076602163396</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.10092e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-55.355</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.2514180024660839</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6165171898355895</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.376092544987198</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.740621156211487</v>
+      </c>
+      <c r="L44" t="n">
+        <v>60.34913681484709</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.0078829532745</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>11.4481931601502</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-25270.9745077079</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>23.07063658822108</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8167342242464068</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1647.525</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9306888800889833</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2028.010045618475</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.932814438829077</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.21803e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-58.328</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1888551165147031</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.852417582417607</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.722464261402293</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.151264044943887</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>85.44063142246873</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>12.54006748820524</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-26112.59757183991</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>41.48689625149154</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8170490155736816</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1609.344</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.909120386663586</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1992.787650967893</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9166133562105839</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.24336e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-59.42</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2587179487179455</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.1512315270935</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.782717770034861</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.381811432813535</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>85.26229246737196</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>12.06599072710019</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-24600.01779766982</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>41.48503712102024</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.817120919156286</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1577.062</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8908842455264061</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1963.285246535779</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9030432711442359</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.26052e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-60.111</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2081632653060857</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.5652366863905042</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.784381778741892</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.263569682151629</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>84.63861690599957</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>10.65554400894035</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-21330.64729598035</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>42.66904761527451</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000001449e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8172209515700588</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1558.979</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.880669136791395</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1939.441448210995</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8920759490631938</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.27741e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-60.661</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1256465517241314</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.627245949926214</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.083797054009655</v>
+      </c>
+      <c r="K48" t="n">
+        <v>171.6967708867249</v>
+      </c>
+      <c r="L48" t="n">
+        <v>6.468534932221158</v>
+      </c>
+      <c r="M48" t="n">
+        <v>84.47579681114158</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>10.33961419755706</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-20424.20110545467</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>41.99526469865566</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000000001782e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8173996952703181</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1538.572</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8691411976244773</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1917.206671278342</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8818487211400712</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.29345e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-61.114</v>
+      </c>
+      <c r="H49" t="n">
+        <v/>
+      </c>
+      <c r="I49" t="n">
+        <v/>
+      </c>
+      <c r="J49" t="n">
+        <v/>
+      </c>
+      <c r="K49" t="n">
+        <v/>
+      </c>
+      <c r="L49" t="n">
+        <v>1.489958471674933</v>
+      </c>
+      <c r="M49" t="n">
+        <v>84.12649034663309</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>9.720753047561018</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-18922.24803844098</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>40.84229556032267</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8176183870949866</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1510.204</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8531160798566958</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1888.340376748607</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8685712246153345</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.30995e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-61.559</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4861850443599199</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7768056968464074</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.944799405646406</v>
+      </c>
+      <c r="K50" t="n">
+        <v>468.7793342579591</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.923371964679976</v>
+      </c>
+      <c r="M50" t="n">
+        <v>83.35567793304396</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>8.584579653801629</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-16423.55133321817</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>42.86972364338214</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000000000056e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8178760123260773</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1482.629</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8375389287552232</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1867.294490572318</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8588908452968937</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.32603e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-61.957</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4308762169680136</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.298639455782133</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.408739255014039</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.560752386299837</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>82.87607870025458</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>8.00124248383432</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-15080.72249101161</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>42.42663630048457</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8181415408158662</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1467.942</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8292422245584026</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1849.973602910011</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8509238363860434</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.34092e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-62.344</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.5121330724071017</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.291359593392545</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.046991622239052</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>7.066016949152591</v>
+      </c>
+      <c r="M52" t="n">
+        <v>81.62960740627466</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>6.796286431008581</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-12558.12680005444</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>40.84607067699562</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000000203e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8184015568674078</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1443.448</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8154055341112776</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1830.926363177155</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.842162765265595</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.35646e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-62.692</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6437499999998734</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6625931445603584</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.420709570957189</v>
+      </c>
+      <c r="K53" t="n">
+        <v>447.2802069857748</v>
+      </c>
+      <c r="L53" t="n">
+        <v>6.083921834091353</v>
+      </c>
+      <c r="M53" t="n">
+        <v>80.64484665020996</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>6.069992211960154</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-11034.92547586477</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>40.41253520549697</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8186827246611407</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1420.421</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8023975537517632</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1809.403093230309</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8322628059332384</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.36976e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-63.003</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1546551724137936</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.2388203017832695</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.386949924127521</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1.98369065849927</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>80.25023565861777</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>5.819800615889765</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-10454.22567970742</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>41.42907718812796</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000000225e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8189838946749735</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1413.051</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7982342317710613</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1792.020426627623</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8242673808477615</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.3863e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-63.37</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3950391644908563</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.396853625170928</v>
+      </c>
+      <c r="J55" t="n">
+        <v>559.0311501597982</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.70965476887078</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7.99060317460327</v>
+      </c>
+      <c r="M55" t="n">
+        <v>69.02407399548717</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.608364302778769</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-4258.023366482982</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>40.7771474434652</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.81930686553524</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1386.372</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.783163232161408</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1772.503415765187</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8152902312648005</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.40057e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-63.625</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1488778054862764</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.3365432098765073</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.035224839400389</v>
+      </c>
+      <c r="K56" t="n">
+        <v>632.1379061371605</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.617272773975338</v>
+      </c>
+      <c r="M56" t="n">
+        <v>75.9714115717095</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>4.002272510476752</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-6855.007206655303</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>41.22272211930954</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8196027443072182</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1377.975</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.778419756629257</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1758.436694421908</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8088200262456758</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.41422e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-63.926</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.120076481835704</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.372352941176593</v>
+      </c>
+      <c r="J57" t="n">
+        <v>21928.76875007322</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.114602960968979</v>
+      </c>
+      <c r="L57" t="n">
+        <v>8.277387594355332</v>
+      </c>
+      <c r="M57" t="n">
+        <v>43.8615558925129</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.9610299937090596</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-1115.674699726089</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>39.83819055119636</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8199163450473048</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1351.625</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7635346095205062</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1739.294195551249</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8000151392184152</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.42764e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-64.227</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1874003189792677</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.4128161888701668</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9775429326287423</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>5.797422298877806</v>
+      </c>
+      <c r="M58" t="n">
+        <v>63.04135340473545</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.966117303975074</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-3000.043639337012</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>40.45336684005565</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8202251617307426</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1336.306</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7548808877535629</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1720.217101354969</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7912403360779482</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.4415e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-64.51600000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.2428160919540046</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8942184154175432</v>
+      </c>
+      <c r="J59" t="n">
+        <v>407.2284730195304</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.712903225806429</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.912226717717449</v>
+      </c>
+      <c r="M59" t="n">
+        <v>45.43448501065251</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.015282571619792</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-1248.498711361743</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>41.01642779161091</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8205317402125414</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1330.848</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7517976569027257</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1706.880353881015</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7851058937769352</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.45598e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-64.80200000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.221767241379039</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1013.37600000013</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.571525096525088</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.122997946612007</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9.203778429934081</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-72.92742366345705</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-3.256095338395242</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>6505.740889531367</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>39.09776340099143</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.988629627763726e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8104549672848965</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1305.144</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7372774359811571</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1690.59611441889</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7776157071634913</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.46799e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-65.047</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1480769230769218</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.929367088607466</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3171.006249999553</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.000237247923998</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.125782004698159</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-30.26983426558344</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-0.5836467645861675</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1616.698489650714</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>38.78540718146144</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.821172340440002</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1293.338</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7306082121949746</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1673.582888516348</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7697902120150629</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.48343e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-65.33</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6420886075950309</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7121.86799999687</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.64834437086085</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.581578947368499</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.444519231348877</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-74.38969936980901</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-3.579113167266549</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>6905.369524495869</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>38.78832405146773</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8214865399228338</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1281.105</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7236977755884717</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1657.383197520283</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7623389147700876</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.49556e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-65.568</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1822134387351736</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.154888888888864</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.437760416666724</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7.566605033009353</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-76.43617560078853</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-4.144953568440815</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>7829.0071820168</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>38.68855496283538</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8218035756252783</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1261.615</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.712687850838963</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1646.048360317384</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7571252819148238</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.50962e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-65.88200000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.3931818181817581</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.002539682539694</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.312389380530971</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.442711439445589</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-76.73571255951464</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-4.242106379727296</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>7876.847570079973</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>35.72079937406227</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8221280741698642</v>
       </c>
     </row>
@@ -10366,7 +14882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11069,18 +15585,6 @@
       <c r="G12" t="n">
         <v>-50.613</v>
       </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
       <c r="L12" t="n">
         <v>12.43674644283627</v>
       </c>
@@ -11125,18 +15629,6 @@
       <c r="G13" t="n">
         <v>-56.02</v>
       </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="n">
         <v>20.03131900592901</v>
       </c>
@@ -11604,6 +16096,566 @@
         <v>1.000000000000035e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8206519868547215</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2010.608</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2437.939296112774</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.88254e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-50.613</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v/>
+      </c>
+      <c r="K22" t="n">
+        <v/>
+      </c>
+      <c r="L22" t="n">
+        <v>12.43674644283627</v>
+      </c>
+      <c r="M22" t="n">
+        <v>83.68508640050176</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.036321548134451</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-21927.33982403725</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-5.921499972752599</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8183122528011395</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1720.705</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8558132664348298</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2081.201856258652</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.85367255024646</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.20864e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-56.02</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>20.03131900592901</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.49846534058848</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.70185507930735</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-27183.68093179626</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>40.68237097343354</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.819074510111525</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1642.312</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.816823567796408</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2009.405360258612</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8242228850663148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.26903e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-57.982</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1135964912280912</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6118768328445769</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.302312138728322</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.163583252190833</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.51621400089732</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.00571262187555</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.44319292846364</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-23542.6158993587</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>45.23590717054105</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000001422e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8192163352940676</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1612.218</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8018559560093267</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1974.590651383112</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8099425012474846</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.29217e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-59.097</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2300300300300309</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8684115523465604</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.861916461916429</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.298701298701271</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.95371298669677</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.32467361721992</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-22889.88801247129</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>45.38993988075072</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000516e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8193185792260768</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1581.77</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7867122780770792</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1946.077338711634</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7982468397857978</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.30891e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-59.927</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1373152709359659</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.059462616822412</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.067324388318875</v>
+      </c>
+      <c r="K26" t="n">
+        <v>147.1462370437064</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.033891108891233</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.39779243039936</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.19474436953413</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20227.34755178795</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>45.13295147489384</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001422e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8194427593292148</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1548.466</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7701481342956957</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1919.089453359682</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7871768818934974</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.32649e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-60.588</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1846153846153714</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6113573407201842</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.08202396804274</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.372947368420997</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.36981504542359</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.603048958290429</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16713.45949904044</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44.45238728327774</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8196257578649878</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1524.622</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7582890349585797</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1893.700267127042</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7767626823795385</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.34175e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-61.166</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2578014184396784</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.036601307189489</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.851376146789074</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.626985040276252</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>82.67269415750867</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7.776812830372212</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-14842.73348834367</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>44.16775496086063</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000007262e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8198366291058186</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1496.33</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7442176694810725</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1867.042088559798</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7658279644356789</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.35994e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-61.656</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2242158092848061</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.272301425661841</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.173502722323061</v>
+      </c>
+      <c r="K29" t="n">
+        <v>259.9384319753958</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.474772542807293</v>
+      </c>
+      <c r="M29" t="n">
+        <v>81.59169219635113</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.765198806685627</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-12651.22439576775</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>44.42276144769119</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000002123e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.820084251692327</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1472.461</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7323461360941567</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1845.669233764841</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7570611937334571</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.37649e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-62.149</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.596706586826347</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8336492890996244</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.291514143094856</v>
+      </c>
+      <c r="K30" t="n">
+        <v>653.398653846112</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.721246669950677</v>
+      </c>
+      <c r="M30" t="n">
+        <v>79.62069416838311</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>5.459676907538616</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9955.161489567143</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>42.73216970384306</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8203513308286863</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1454.528</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7234269434917199</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1820.932440970525</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7469145945815594</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.3946e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-62.553</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3200221238937945</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.61591263650556</v>
+      </c>
+      <c r="J31" t="n">
+        <v>276.2913917940495</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.842035928143885</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.255435101084105</v>
+      </c>
+      <c r="M31" t="n">
+        <v>75.1224995448122</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.76422437885523</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-6556.328123392039</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>43.38773506168047</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000035e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8206519868547215</v>
       </c>
     </row>
@@ -11618,7 +16670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12937,18 +17989,6 @@
       <c r="G23" t="n">
         <v>-55.334</v>
       </c>
-      <c r="H23" t="n">
-        <v/>
-      </c>
-      <c r="I23" t="n">
-        <v/>
-      </c>
-      <c r="J23" t="n">
-        <v/>
-      </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
       <c r="L23" t="n">
         <v>18.11669994310894</v>
       </c>
@@ -13161,18 +18201,6 @@
       <c r="G27" t="n">
         <v>-60.752</v>
       </c>
-      <c r="H27" t="n">
-        <v/>
-      </c>
-      <c r="I27" t="n">
-        <v/>
-      </c>
-      <c r="J27" t="n">
-        <v/>
-      </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
       <c r="L27" t="n">
         <v>0.9440814176407966</v>
       </c>
@@ -14088,6 +19116,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.823550779313926</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1754.182</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2135.679102849154</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.14633e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-55.334</v>
+      </c>
+      <c r="H44" t="n">
+        <v/>
+      </c>
+      <c r="I44" t="n">
+        <v/>
+      </c>
+      <c r="J44" t="n">
+        <v/>
+      </c>
+      <c r="K44" t="n">
+        <v/>
+      </c>
+      <c r="L44" t="n">
+        <v>18.11669994310894</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.25101179123476</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.03719813107754</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-26266.44067188984</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>28.52604061098555</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8180927730493248</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1632.782</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9307939541051042</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2007.672270762228</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9400627032796474</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.251e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-58.469</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.006786703601104252</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.3150268336314803</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8527007299270027</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.204079601990086</v>
+      </c>
+      <c r="L45" t="n">
+        <v>17.20089894166334</v>
+      </c>
+      <c r="M45" t="n">
+        <v>84.98704961183948</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>11.40037341705818</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-23409.50289409664</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>43.30898605848211</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8183457305185744</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1602.448</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9135015636917946</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1969.650114448377</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9222593936611156</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.27513e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-59.584</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1459541984732713</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.926535087719225</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.797562626946508</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.576778733385329</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>84.82604301641445</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>11.04376290704604</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-22255.7748838759</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>45.3152275688675</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8184161549734839</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1576.056</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8984563745381037</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1944.963151618698</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9107000902073596</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.29049e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-60.277</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4692889561270771</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9116977225673216</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.815850144092205</v>
+      </c>
+      <c r="K47" t="n">
+        <v>173.9439537329087</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.021182506718702</v>
+      </c>
+      <c r="M47" t="n">
+        <v>84.20005825457285</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>9.844916128231484</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-19500.89224602438</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>44.90417779128791</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8185314720472997</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1557.45</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8878497214086108</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1921.732655045074</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8998227554323774</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.30636e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-60.752</v>
+      </c>
+      <c r="H48" t="n">
+        <v/>
+      </c>
+      <c r="I48" t="n">
+        <v/>
+      </c>
+      <c r="J48" t="n">
+        <v/>
+      </c>
+      <c r="K48" t="n">
+        <v/>
+      </c>
+      <c r="L48" t="n">
+        <v>0.9440814176407966</v>
+      </c>
+      <c r="M48" t="n">
+        <v>83.72363765750833</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>9.092275950907407</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-17734.64062313891</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>44.58939962821523</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000000003917e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8187058255063128</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1521.223</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8671979304313918</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1899.730246217678</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8895204544930447</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.32519e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-61.21</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2500770416024655</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.4604651162790542</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.71813361611883</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.559489456159805</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>82.91530875048139</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>8.046006418355486</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-15418.20997681798</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>43.31733611813252</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8189326649600858</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1501.749</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8560964597744133</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1875.423187523042</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8781390355044859</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.34312e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-61.653</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3191794871794817</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.640834575260764</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.172555746140719</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.879716981132042</v>
+      </c>
+      <c r="M50" t="n">
+        <v>81.82888160635306</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>6.964385214785362</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-13086.25996492417</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>43.59186777802745</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8191920538596626</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1476.246</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.841558059540002</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1852.525896736657</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8674177193873603</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.3612e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-62.013</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.567500000000028</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.075768535262141</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.51779964221831</v>
+      </c>
+      <c r="K51" t="n">
+        <v>292.7091143594105</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5.667149493518808</v>
+      </c>
+      <c r="M51" t="n">
+        <v>81.29782815404234</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>6.533372937607274</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-12093.72838407259</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>43.23863551646991</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.000000000004362e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8194635650255985</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1455.254</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8295912282761994</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1830.247790260619</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.856986327121398</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.37954e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-62.373</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.6559210526315982</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8984952120382679</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.350042408821053</v>
+      </c>
+      <c r="K52" t="n">
+        <v>564.6109271523191</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.713717801351708</v>
+      </c>
+      <c r="M52" t="n">
+        <v>80.23500153666801</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>5.810543488692669</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-10551.16107144091</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>43.13565479461715</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8197604937916433</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1431.631</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8161245526404899</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1812.458806691139</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8486568999402506</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.39762e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-62.731</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2037453183520762</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.238876404494462</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.346649029982357</v>
+      </c>
+      <c r="K53" t="n">
+        <v>11390.30999998893</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5.821237857540497</v>
+      </c>
+      <c r="M53" t="n">
+        <v>78.01720259259039</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>4.711585593391511</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-8339.406866685262</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>41.12580431505228</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8200546022365006</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1414.23</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8062048293734628</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1789.988084437263</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8381353181989215</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.41496e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-63.049</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3843800322061</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.530796460177017</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.891521739130549</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.005970416552191</v>
+      </c>
+      <c r="M54" t="n">
+        <v>75.25192574559955</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>3.798784631991308</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-6528.484747240417</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>42.05094627906567</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000001333e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8203531302882033</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1395.136</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7953199839013282</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1771.182708680618</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8293299804814913</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.43213e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-63.364</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2459412780656477</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7463380281690878</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.704994903159933</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.121494783008797</v>
+      </c>
+      <c r="M55" t="n">
+        <v>71.39174275552924</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.970023898174118</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-4907.951170024037</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>41.59480463320779</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000000208e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8206453582175531</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1371.555</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7818772510492068</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1751.093632850568</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8199235692827069</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.44883e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-63.687</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.2079326923076946</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.882362204724447</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.318309270614921</v>
+      </c>
+      <c r="M56" t="n">
+        <v>68.20342119189704</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.500611385362059</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-4011.884611853175</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>42.1510973110677</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8209498127938462</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1353.532</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7716029465585668</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1733.76645455972</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8118103755600489</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.46501e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-63.988</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1392197125256601</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.52917431192662</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.422280471821686</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5.515123601871113</v>
+      </c>
+      <c r="M57" t="n">
+        <v>54.84148549150882</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.419771704861776</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-2001.451557276632</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>41.83414477949441</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8212629292047802</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1343.273</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.765754636634055</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1715.285158655724</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8031567834172306</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.48013e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-64.258</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.3359173126615216</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.6720588235294519</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.220303756994377</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6.379581017918847</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-23.63536197186177</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-0.4376244417697306</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1401.696019463868</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>42.04091299659012</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8215734390118673</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1321.571</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7533830583143595</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1699.359857577175</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7956999978648961</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.49666e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-64.566</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.02359999999999986</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.7093489148580715</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2605.043283580649</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.583666061705995</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.773100922539091</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-36.01505624880785</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-0.7269440984999576</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1872.9110975536</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>40.97589468234094</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8218871171799974</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1311.858</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.747846004576492</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1685.428636826946</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7891769107907921</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.51121e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-64.82299999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1123209169054632</v>
+      </c>
+      <c r="I60" t="n">
+        <v>883.7073232323244</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.425930232558231</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.482765335929903</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.73105770764128</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-68.81653130893991</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-2.580361879013001</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>5169.994898817462</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>39.26859832576054</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8222087567964652</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1295.136</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7383133563108045</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1669.223278815416</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7815889927417223</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.5255e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-65.11499999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7019999999999325</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.293315858453439</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.100254452926099</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.136919366292168</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-74.81551650009332</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-3.684554891064483</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>7053.334562523114</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>37.82101622784387</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8225421938164377</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1280.185</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7297902954197454</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1653.104135524818</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7740414434544283</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.54098e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-65.384</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6063231850118003</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.248702101359796</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.549525616698344</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.286854447512148</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-78.03794608922435</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-4.719998978962239</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>8779.037450271646</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>36.75067109641191</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8228727225789749</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1258.87</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7176393327488252</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1640.034643766745</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7679218481741088</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.55608e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-65.66800000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.3681362725451663</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9428822495605768</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.236293436293487</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.196409828974637</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-76.73231190597836</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-4.240979233174182</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>7825.69187997649</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>34.05595977558517</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.754721301734316e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8259443670313199</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1243.613</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.708941831577339</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1621.153982972246</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.75908125935657</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.57192e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-65.953</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.3356725146198866</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.7418524871354636</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.667121212121131</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.803703703703512</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7.333713407990969</v>
+      </c>
+      <c r="M64" t="n">
+        <v>74.49474938169908</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>3.604600745001127</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-5830.555360614539</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>34.89338088492991</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.823550779313926</v>
       </c>
     </row>
@@ -14102,7 +20306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14781,18 +20985,6 @@
       <c r="G12" t="n">
         <v>-51.14</v>
       </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
       <c r="L12" t="n">
         <v>13.69580238676602</v>
       </c>
@@ -14837,18 +21029,6 @@
       <c r="G13" t="n">
         <v>-57.557</v>
       </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="n">
         <v>20.15736461012811</v>
       </c>
@@ -14893,18 +21073,6 @@
       <c r="G14" t="n">
         <v>-59.642</v>
       </c>
-      <c r="H14" t="n">
-        <v/>
-      </c>
-      <c r="I14" t="n">
-        <v/>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
       <c r="L14" t="n">
         <v>12.35927601205413</v>
       </c>
@@ -14949,18 +21117,6 @@
       <c r="G15" t="n">
         <v>-60.738</v>
       </c>
-      <c r="H15" t="n">
-        <v/>
-      </c>
-      <c r="I15" t="n">
-        <v/>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
       <c r="L15" t="n">
         <v>0.810913572756554</v>
       </c>
@@ -15316,6 +21472,566 @@
         <v>1.000000000005478e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8251534583632906</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1974.047</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2363.651728966493</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.94187e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-51.14</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v/>
+      </c>
+      <c r="K22" t="n">
+        <v/>
+      </c>
+      <c r="L22" t="n">
+        <v>13.69580238676602</v>
+      </c>
+      <c r="M22" t="n">
+        <v>83.96946972824345</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.465842002254481</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-22388.80319877982</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.219665348677154</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000005124e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8225864766707481</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1669.798</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8458755034707888</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2003.691230768251</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8477100099871164</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.27898e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-57.557</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>20.15736461012811</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.53954779932567</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.81932459788951</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26396.60937732317</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>42.5058958694118</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8234048628961428</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1601.145</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8110977094263713</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1930.106504654328</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8165782128563699</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.33221e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-59.642</v>
+      </c>
+      <c r="H24" t="n">
+        <v/>
+      </c>
+      <c r="I24" t="n">
+        <v/>
+      </c>
+      <c r="J24" t="n">
+        <v/>
+      </c>
+      <c r="K24" t="n">
+        <v/>
+      </c>
+      <c r="L24" t="n">
+        <v>12.35927601205413</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.04865534310625</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.54294140083858</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-22842.82970925371</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>47.34136725390283</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8235695509221728</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1569.926</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7952829897160503</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1896.320466620974</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8022842127635024</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.35217e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-60.738</v>
+      </c>
+      <c r="H25" t="n">
+        <v/>
+      </c>
+      <c r="I25" t="n">
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v/>
+      </c>
+      <c r="L25" t="n">
+        <v>0.810913572756554</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.52834704789227</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.815662882784993</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-16938.41615410658</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>46.81151095140024</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000068331e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8236929932369786</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1533.049</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7766020768502472</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1869.080206867656</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7907595624017384</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.36806e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-61.461</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.111538461538285</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.099029126213587</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.138233054074499</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2221.532214764973</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.131373530147696</v>
+      </c>
+      <c r="M26" t="n">
+        <v>81.98602521586047</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.102799040974584</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-13298.13547812229</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>45.67281070837896</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8238621482507884</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1502.28</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7610153152381883</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1842.761057867262</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7796246102098171</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.38812e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-62.068</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5806366047744882</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8970430107527364</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.47830637488106</v>
+      </c>
+      <c r="K27" t="n">
+        <v>403.0279236276496</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5.309353274992665</v>
+      </c>
+      <c r="M27" t="n">
+        <v>79.93270674439823</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>5.632589437901719</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10260.82528673172</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44.29203743915991</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000087e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8240555537218642</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1469.375</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7443465125197121</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1816.389924288336</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7684676646853356</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.40612e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-62.597</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4242494226327956</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5970027247956328</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.787431693988916</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5223.416923074484</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.598506859201136</v>
+      </c>
+      <c r="M28" t="n">
+        <v>76.96888144100916</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4.320768072165426</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7605.695436689388</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>43.86608099654677</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8243048022491064</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1444.824</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7319096252520837</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1792.727449258273</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.758456682635789</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.42607e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-63.053</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3615646258503517</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8495522388060159</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.284954280964136</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.689521479569689</v>
+      </c>
+      <c r="M29" t="n">
+        <v>72.80696309005485</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>3.231868389029313</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-5445.0274526308</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>41.67592625730913</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000002658e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8245733819663018</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1421.813</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7202528612540634</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1771.001469195651</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7492649815927076</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.44569e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-63.487</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2295197740112858</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6112984822934435</v>
+      </c>
+      <c r="J30" t="n">
+        <v>399.3817551962897</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.335656108597199</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.838067248680737</v>
+      </c>
+      <c r="M30" t="n">
+        <v>60.86448546867136</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.794027646419339</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-2702.963308183399</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>39.91293178344995</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8248636158348125</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1403.842</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7111492279565785</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1748.134401261793</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7395905157424207</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.46292e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-63.859</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.383333333334092</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.154151624548844</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.703608847497197</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.530267965895247</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-18.15268803265198</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.3278685073504194</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1256.841685910484</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>39.08859617447285</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000005478e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8251534583632906</v>
       </c>
     </row>
@@ -15330,7 +22046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16661,18 +23377,6 @@
       <c r="G23" t="n">
         <v>-56.353</v>
       </c>
-      <c r="H23" t="n">
-        <v/>
-      </c>
-      <c r="I23" t="n">
-        <v/>
-      </c>
-      <c r="J23" t="n">
-        <v/>
-      </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
       <c r="L23" t="n">
         <v>19.38498010593134</v>
       </c>
@@ -17812,6 +24516,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8251086426222195</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1753.193</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2126.597016148888</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.14726e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-56.353</v>
+      </c>
+      <c r="H44" t="n">
+        <v/>
+      </c>
+      <c r="I44" t="n">
+        <v/>
+      </c>
+      <c r="J44" t="n">
+        <v/>
+      </c>
+      <c r="K44" t="n">
+        <v/>
+      </c>
+      <c r="L44" t="n">
+        <v>19.38498010593134</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.38198389171703</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.38013344779855</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-26828.37751742029</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>24.63059122381696</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8199851919565687</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1620.097</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9240836576463629</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1981.532074069313</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9317854106923009</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.25872e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-59.507</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.308009422850403</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8328431372548774</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.122504091653089</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.338336347197144</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>84.91485694832897</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>11.23768990782095</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-22740.02872814703</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>40.87641236694765</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.000000000033749e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8202379931327785</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1586.794</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9050880308100705</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1942.460456977535</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.913412575220852</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.28245e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-60.381</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.9141361256544275</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8769628099173143</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.833357717629965</v>
+      </c>
+      <c r="K46" t="n">
+        <v>142.7481943250273</v>
+      </c>
+      <c r="L46" t="n">
+        <v>5.937863145258136</v>
+      </c>
+      <c r="M46" t="n">
+        <v>84.33357356445418</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10.07846112782562</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-19956.30977812716</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>43.50517459507932</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8202760045559823</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1559.819</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8897018183394526</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1918.753650909284</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9022648091475306</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.29792e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-60.832</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2020768431983517</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.036260330578504</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.91253918495291</v>
+      </c>
+      <c r="K47" t="n">
+        <v>224.9227088948739</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.08892164087448</v>
+      </c>
+      <c r="M47" t="n">
+        <v>83.91562640302743</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>9.381449906243233</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-18308.84051384599</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>43.89412864200256</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8203445327519937</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1534.044</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8750000712984822</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1898.968305164549</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8929610503279283</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.31247e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-61.244</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.03830548926013796</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.093220338982955</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.15626984126985</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.722546103509673</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>83.42670931435386</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>8.678177576855584</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-16694.66620275111</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>42.86287391087865</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8204929258916049</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1518.468</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8661157100216577</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1877.777504526595</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8829963976565306</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.33109e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-61.596</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.306286549707623</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.562730627306267</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.971620612397284</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1234.577573529507</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6.778893109061333</v>
+      </c>
+      <c r="M49" t="n">
+        <v>82.57540916369737</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>7.673785607154372</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-14521.8051493096</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>42.85416204549267</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8206972511395739</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1500.94</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8561179516459397</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1858.333601673499</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8738531971792218</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.34663e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-61.908</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2817002881844403</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.155047821466561</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.237425404944574</v>
+      </c>
+      <c r="K50" t="n">
+        <v>112119.4333325042</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.626852099491773</v>
+      </c>
+      <c r="M50" t="n">
+        <v>81.99637270391783</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>7.112102684443761</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-13269.73746493533</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>42.53463518444153</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8209178833731177</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1481.147</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8448282647717621</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1836.448907459028</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8635622515753846</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.36424e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-62.217</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.3871093749999261</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9506643046944263</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.766031987814212</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6.738913043478221</v>
+      </c>
+      <c r="M51" t="n">
+        <v>80.72897074396093</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>6.126057264935233</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-11214.57245444018</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>43.5923722049165</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.000000000000972e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8211662549472581</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1463.616</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8348287952324701</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1821.48625608479</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8565262916541514</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.38049e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-62.497</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4017374517374492</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.26008583690985</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.224400684931585</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6.99437095412321</v>
+      </c>
+      <c r="M52" t="n">
+        <v>79.52783502169258</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>5.410184223599325</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-9725.398204445482</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>41.91804808806228</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.00000000000074e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8214255365798371</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1440.428</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8216026415802481</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1803.824320401841</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8482210342175857</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.39585e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-62.784</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1506641366223918</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6927304964538441</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.541446208112873</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1709.757999999496</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5.868388573956533</v>
+      </c>
+      <c r="M53" t="n">
+        <v>78.76880552389031</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>5.035977400135164</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-8935.4587760678</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>42.03165298647559</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8217033429359762</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1432.094</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8168490291713463</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1786.397904458126</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.84002652636707</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.41123e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-63.066</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.4281138790035462</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.312233285917384</v>
+      </c>
+      <c r="J54" t="n">
+        <v>330.6118887823631</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.687955993051528</v>
+      </c>
+      <c r="L54" t="n">
+        <v>7.493623451193612</v>
+      </c>
+      <c r="M54" t="n">
+        <v>73.43323657420989</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>3.36155452585845</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-5674.162228133481</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>41.95780956185206</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8219854570824879</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1409.932</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8042080934614729</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1768.064040311933</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8314053047595111</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.42596e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-63.348</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1232914923291428</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.36311569301263</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.32188019966725</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.030746267733815</v>
+      </c>
+      <c r="M55" t="n">
+        <v>72.71956515545914</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>3.214496065197946</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-5368.021292083731</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>42.43710023149026</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000000098e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8222747325284969</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1382.546</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7885874515812007</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1753.319651352848</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.824471979429362</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.44129e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-63.608</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3254041570438689</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.3886494252873395</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8826548672566261</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.520977011494161</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>74.58429760798448</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>3.626594717795229</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-6107.818877749405</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>41.47710627657625</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8225724399148835</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1377.792</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7858758277040805</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1738.683644521344</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8175896191512453</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.4564e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-63.88</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.0791935483870929</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.2133555926544215</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.383493810178837</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5.333103540397866</v>
+      </c>
+      <c r="M57" t="n">
+        <v>65.83595470154087</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.228840598736393</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-3482.671990874283</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>40.56075168671248</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000000794e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8228728451387118</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1367.065</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7797572771508898</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1724.426549022601</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8108854361817039</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.47052e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-64.137</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1811463046757076</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8685601056803796</v>
+      </c>
+      <c r="J58" t="n">
+        <v>909.962827225143</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.242078364565547</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6.378344915662903</v>
+      </c>
+      <c r="M58" t="n">
+        <v>27.52461027105345</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.5211131013699194</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-328.387019495245</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>39.28078343082097</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8231814522867867</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1350.783</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7704702220462892</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1709.964800342826</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.804085018157059</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.48488e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-64.378</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1554809843400395</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.020277777777849</v>
+      </c>
+      <c r="J59" t="n">
+        <v>8482.382926825059</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.414725069897545</v>
+      </c>
+      <c r="L59" t="n">
+        <v>6.430423228090625</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-17.26249288163301</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-0.3107473341642026</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1172.469699247953</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>38.05545982776903</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8234970103522875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1328.941</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7580118104509886</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1694.678436318947</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7968968372709779</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.49741e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-64.628</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.6134433962264116</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1633245382585726</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.052777777777718</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5.007588279310649</v>
+      </c>
+      <c r="M60" t="n">
+        <v>45.25799158971661</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.009046400662567</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-1235.474705142059</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>37.41296396813527</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8238135155774827</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1322.094</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7541063647869916</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1681.721232432731</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7908039086212045</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.51216e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-64.874</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0715821812595967</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.831372549019604</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.336851520572438</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.518871021079078</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-64.57295199316155</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-2.103431817874846</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4320.004066215066</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>35.55419782203069</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8241244208803208</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1298.512</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.740655478318702</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1665.57084197461</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7832094324061629</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.52769e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-65.133</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.115000000000002</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.3848120300751967</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1.489920424403127</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5.90649180316512</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-59.11177625396401</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-1.6716578646309</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>3490.250535860603</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>35.40077587396183</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8244536716799277</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1291.598</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7367118166682162</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1652.465363569323</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7770467799121703</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.541e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-65.38500000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.4890322580645503</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.490776699029215</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.044499178981979</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.954561668839922</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-75.71666965056761</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-3.927930591105219</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>7403.073278594797</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>33.60535885843967</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8247730757494215</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1271.381</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7251802853422299</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1641.802406376534</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7720326859809664</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.55412e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-65.63500000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.3913953488371869</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3852.91098901098</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.114653784219079</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.333633093525165</v>
+      </c>
+      <c r="L64" t="n">
+        <v>5.83198675839066</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-73.08906196034226</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-3.289129958966575</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>6199.55822260074</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>31.1387846866362</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8251086426222195</v>
       </c>
     </row>
@@ -17826,7 +25706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19091,6 +26971,566 @@
         <v>0.8205033760807476</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1483.47</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1977.782049581569</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.32062e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-56.251</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1442961165048552</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8743421052631835</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.258320000000041</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.044751908397064</v>
+      </c>
+      <c r="L22" t="n">
+        <v>18.95192980577479</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.02635672175349</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.556651234098043</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-18661.78018724119</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-30.45258394690745</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.818023149798667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1220.564</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8227763284731069</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1663.140752445626</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.840912047309505</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.56222e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-62.968</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.02130365659776961</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1078549848942542</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9628620102213769</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.452154398563648</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24.19664631545549</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.37214446279282</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.35369719285699</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-20851.07949251159</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>22.0081394783989</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8186695257787544</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1161.111</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7826993468017553</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1634.600441853732</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8264815843583762</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.5748e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-64.93000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1555066079295477</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1941068139962854</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8233979135617905</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.791917591125088</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9.064672098686874</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.37694364448107</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.15670254258108</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-16414.50398004065</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>8.163650472296581</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000001192e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8188227417856027</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1131.448</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7627036610110078</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1572.237990248534</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7949500758089931</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.57369e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-65.857</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.02426850258175494</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.405607476635465</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9432282003710352</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.630025445292553</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.13626690366171</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.307641982282108</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-13082.17204302591</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>27.55211690899466</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000005129e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8189578561440372</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1115.07</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7516633298954478</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1549.099945604063</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7832510897405504</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.57601e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-66.48099999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7377094972066865</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.084462151394417</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.873888091822141</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.207916986933048</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>81.33681676392436</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6.563232418309902</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10050.72522303196</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>27.12387230050228</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.51883301213593e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.7890356792397567</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1082.491</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7297019825139706</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1521.60734588161</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7693503670960761</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.58108e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-66.998</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03327932475838208</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5479498530074235</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.668420172831819</v>
+      </c>
+      <c r="K27" t="n">
+        <v>12.90349678608272</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.41854747130174</v>
+      </c>
+      <c r="M27" t="n">
+        <v>80.50229486478456</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>5.977235050476501</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8986.067495305362</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>29.25768452454258</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8192865498640411</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1065.059</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7179511550621178</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1506.247946124453</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7615843952285458</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.59288e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-67.44</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2589958158995792</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2702702702702569</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9154981549814504</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.917049180327905</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>78.18563593405783</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4.780742256901767</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-6965.624355708699</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>24.78772807217729</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8195503098821437</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1043.966</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7037324650987213</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1486.815582339048</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7517590639745201</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.60394e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-67.877</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3961240310077724</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.393096234309656</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.317835671342571</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.687535816618758</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>74.6982300161572</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>3.654940738289015</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-5118.32328526468</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>21.8539550443561</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8198595087628128</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1020.695</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6880455957990387</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1468.108193694099</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.742300292393037</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.61266e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-68.25700000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3763157894736899</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8636363636364613</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8702460850112506</v>
+      </c>
+      <c r="K30" t="n">
+        <v>543.2853695324141</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.653156911152102</v>
+      </c>
+      <c r="M30" t="n">
+        <v>71.57503328686998</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.001743117900863</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-4046.337269879557</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>19.49638783254318</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8201887806134781</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1003.49</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6764477879566152</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1455.300307597462</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7358244089157112</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.62456e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-68.602</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.102197802197874</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4770562770562493</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.239691714836004</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1316.630291970661</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.73206022516489</v>
+      </c>
+      <c r="M31" t="n">
+        <v>62.55343621990598</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.925364211937832</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-2373.947858626498</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>14.1544318291119</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.00000000000007e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8205033760807476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
